--- a/카드_아키타입/07_페이스·바디오일.xlsx
+++ b/카드_아키타입/07_페이스·바디오일.xlsx
@@ -1531,7 +1531,7 @@
       <row>119</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="990600" cy="1047750"/>
+    <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
         <cNvPr id="54" name="Image 54" descr="Picture"/>
@@ -2331,7 +2331,7 @@
       <row>173</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="86" name="Image 86" descr="Picture"/>
@@ -2606,7 +2606,7 @@
       <row>196</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="847725"/>
+    <ext cx="1047750" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="97" name="Image 97" descr="Picture"/>

--- a/카드_아키타입/07_페이스·바디오일.xlsx
+++ b/카드_아키타입/07_페이스·바디오일.xlsx
@@ -278,7 +278,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -303,7 +303,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -328,7 +328,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="790575" cy="1047750"/>
@@ -353,7 +353,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -378,7 +378,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>52</row>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -403,8 +403,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>52</row>
-      <rowOff>1085850</rowOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -428,8 +428,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>52</row>
-      <rowOff>1085850</rowOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -453,8 +453,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>52</row>
-      <rowOff>1085850</rowOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -478,8 +478,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>52</row>
-      <rowOff>1085850</rowOff>
+      <row>54</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -503,7 +503,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -528,7 +528,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>64</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="885825" cy="1047750"/>
@@ -553,7 +553,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>64</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -578,7 +578,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>64</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -603,7 +603,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>64</row>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -628,8 +628,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>64</row>
-      <rowOff>1085850</rowOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -653,8 +653,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>64</row>
-      <rowOff>1085850</rowOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -678,8 +678,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>64</row>
-      <rowOff>1085850</rowOff>
+      <row>69</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -703,7 +703,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>74</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -728,7 +728,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>74</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -753,7 +753,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>74</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -778,7 +778,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="733425"/>
@@ -803,7 +803,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>86</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="952500"/>
@@ -828,7 +828,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>86</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="952500"/>
@@ -853,7 +853,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>86</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="952500"/>
@@ -878,7 +878,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>86</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="952500"/>
@@ -903,8 +903,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>1085850</rowOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="952500"/>
     <pic>
@@ -928,8 +928,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>86</row>
-      <rowOff>1085850</rowOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="952500"/>
     <pic>
@@ -953,8 +953,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>86</row>
-      <rowOff>1085850</rowOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -978,8 +978,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>86</row>
-      <rowOff>1085850</rowOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -1003,8 +1003,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>86</row>
-      <rowOff>1085850</rowOff>
+      <row>93</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -1028,8 +1028,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>86</row>
-      <rowOff>2171700</rowOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -1053,8 +1053,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>86</row>
-      <rowOff>2171700</rowOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -1078,8 +1078,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>86</row>
-      <rowOff>2171700</rowOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -1103,7 +1103,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="819150"/>
@@ -1128,7 +1128,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>98</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="952500"/>
@@ -1153,7 +1153,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>98</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="952500"/>
@@ -1178,7 +1178,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>98</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="952500"/>
@@ -1203,7 +1203,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>98</row>
+      <row>106</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
@@ -1228,8 +1228,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
-      <rowOff>1085850</rowOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -1253,8 +1253,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>98</row>
-      <rowOff>1085850</rowOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
     <pic>
@@ -1278,8 +1278,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>98</row>
-      <rowOff>1085850</rowOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1303,8 +1303,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>98</row>
-      <rowOff>1085850</rowOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1328,8 +1328,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>98</row>
-      <rowOff>1085850</rowOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1353,8 +1353,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>98</row>
-      <rowOff>2171700</rowOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1378,8 +1378,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>98</row>
-      <rowOff>2171700</rowOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1389,81 +1389,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId48"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId49"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId50"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>109</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1000125" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId51"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1484,11 +1409,11 @@
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId52"/>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId49"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1506,14 +1431,14 @@
       <row>119</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="933450"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId53"/>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId50"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1534,6 +1459,81 @@
     <ext cx="1000125" cy="1047750"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId51"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId52"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="933450"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId53"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1000125" cy="1047750"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="54" name="Image 54" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1553,7 +1553,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>133</row>
+      <row>144</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -1578,7 +1578,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>133</row>
+      <row>144</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1603,7 +1603,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>133</row>
+      <row>144</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1628,7 +1628,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>133</row>
+      <row>144</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1653,7 +1653,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>133</row>
+      <row>144</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1678,8 +1678,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1703,8 +1703,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1728,8 +1728,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1753,8 +1753,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1778,8 +1778,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>133</row>
-      <rowOff>1085850</rowOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1789,81 +1789,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId64"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>133</row>
-      <rowOff>2171700</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId65"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>133</row>
-      <rowOff>2171700</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId66"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>133</row>
-      <rowOff>2171700</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId67"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1881,14 +1806,14 @@
       <row>146</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId68"/>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId65"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1909,11 +1834,11 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId69"/>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId66"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1934,6 +1859,81 @@
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId67"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId68"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId69"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="70" name="Image 70" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -1953,7 +1953,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>146</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1978,7 +1978,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>146</row>
+      <row>160</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2003,8 +2003,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>146</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2028,8 +2028,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>146</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2053,8 +2053,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>146</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2078,8 +2078,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>146</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2103,8 +2103,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>146</row>
-      <rowOff>1085850</rowOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2128,8 +2128,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>146</row>
-      <rowOff>2171700</rowOff>
+      <row>162</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2153,7 +2153,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>159</row>
+      <row>175</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -2178,7 +2178,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>159</row>
+      <row>175</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="895350"/>
@@ -2203,7 +2203,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>159</row>
+      <row>175</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2228,7 +2228,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>159</row>
+      <row>175</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2253,7 +2253,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>159</row>
+      <row>175</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2278,8 +2278,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>159</row>
-      <rowOff>1085850</rowOff>
+      <row>176</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2303,7 +2303,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>190</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -2328,7 +2328,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>173</row>
+      <row>190</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="781050"/>
@@ -2353,7 +2353,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>173</row>
+      <row>190</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2378,7 +2378,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>173</row>
+      <row>190</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2403,7 +2403,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>173</row>
+      <row>190</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2428,7 +2428,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>185</row>
+      <row>202</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2453,7 +2453,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>185</row>
+      <row>202</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2478,7 +2478,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>185</row>
+      <row>202</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2503,7 +2503,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>185</row>
+      <row>202</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2528,7 +2528,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>185</row>
+      <row>202</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2553,8 +2553,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>185</row>
-      <rowOff>1085850</rowOff>
+      <row>203</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2578,8 +2578,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>185</row>
-      <rowOff>1085850</rowOff>
+      <row>203</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2603,10 +2603,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>196</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="857250"/>
+      <row>215</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="847725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="97" name="Image 97" descr="Picture"/>
@@ -2628,7 +2628,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>196</row>
+      <row>215</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="819150"/>
@@ -2653,7 +2653,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>210</row>
+      <row>229</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2678,7 +2678,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>210</row>
+      <row>229</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2703,7 +2703,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>210</row>
+      <row>229</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2728,7 +2728,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>210</row>
+      <row>229</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2753,7 +2753,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>226</row>
+      <row>246</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2778,7 +2778,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>226</row>
+      <row>246</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2803,7 +2803,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>226</row>
+      <row>246</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2828,7 +2828,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>226</row>
+      <row>246</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2853,7 +2853,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>238</row>
+      <row>258</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2878,7 +2878,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>238</row>
+      <row>258</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="904875"/>
@@ -2903,7 +2903,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>238</row>
+      <row>258</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="904875"/>
@@ -2928,7 +2928,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>238</row>
+      <row>258</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="904875"/>
@@ -2953,7 +2953,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>249</row>
+      <row>269</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -2978,7 +2978,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>249</row>
+      <row>269</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="733425"/>
@@ -3003,7 +3003,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>249</row>
+      <row>269</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -3028,7 +3028,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>249</row>
+      <row>269</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -3053,7 +3053,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>249</row>
+      <row>269</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -3078,7 +3078,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>260</row>
+      <row>280</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -3103,7 +3103,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>260</row>
+      <row>280</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="942975" cy="1047750"/>
@@ -3128,7 +3128,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>260</row>
+      <row>280</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -3153,7 +3153,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>260</row>
+      <row>280</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -3178,7 +3178,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>260</row>
+      <row>280</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -3203,7 +3203,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>272</row>
+      <row>292</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -3228,7 +3228,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>272</row>
+      <row>292</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="838200"/>
@@ -3253,7 +3253,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>272</row>
+      <row>292</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -3278,7 +3278,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>272</row>
+      <row>292</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -3303,7 +3303,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>272</row>
+      <row>292</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -3328,8 +3328,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>272</row>
-      <rowOff>1085850</rowOff>
+      <row>293</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
     <pic>
@@ -3353,8 +3353,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>272</row>
-      <rowOff>1085850</rowOff>
+      <row>293</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
     <pic>
@@ -3378,8 +3378,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>272</row>
-      <rowOff>1085850</rowOff>
+      <row>293</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
     <pic>
@@ -3403,7 +3403,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>283</row>
+      <row>304</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -3428,7 +3428,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>283</row>
+      <row>304</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="876300"/>
@@ -3453,7 +3453,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>283</row>
+      <row>304</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3478,7 +3478,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>294</row>
+      <row>315</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -3503,7 +3503,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>294</row>
+      <row>315</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="819150"/>
@@ -3528,7 +3528,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>294</row>
+      <row>315</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -3553,7 +3553,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>294</row>
+      <row>315</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -3578,7 +3578,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>294</row>
+      <row>315</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -3603,7 +3603,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>305</row>
+      <row>326</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="685800" cy="1047750"/>
@@ -3628,7 +3628,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>323</row>
+      <row>344</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="647700" cy="1047750"/>
@@ -3653,7 +3653,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>340</row>
+      <row>361</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="647700" cy="1047750"/>
@@ -3678,7 +3678,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>351</row>
+      <row>372</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="685800" cy="1047750"/>
@@ -3703,7 +3703,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>364</row>
+      <row>386</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -3728,7 +3728,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>364</row>
+      <row>386</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="876300"/>
@@ -3753,7 +3753,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>364</row>
+      <row>386</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -3778,7 +3778,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>364</row>
+      <row>386</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -3803,7 +3803,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>364</row>
+      <row>386</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -3828,8 +3828,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>364</row>
-      <rowOff>1085850</rowOff>
+      <row>387</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3853,8 +3853,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>364</row>
-      <rowOff>1085850</rowOff>
+      <row>387</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3878,8 +3878,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>364</row>
-      <rowOff>1085850</rowOff>
+      <row>387</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3903,8 +3903,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>364</row>
-      <rowOff>1085850</rowOff>
+      <row>387</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3928,8 +3928,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>364</row>
-      <rowOff>1085850</rowOff>
+      <row>387</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3953,8 +3953,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>364</row>
-      <rowOff>2171700</rowOff>
+      <row>388</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3978,7 +3978,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>378</row>
+      <row>402</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="619125" cy="1047750"/>
@@ -4003,7 +4003,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>392</row>
+      <row>416</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4028,7 +4028,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>392</row>
+      <row>416</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4053,7 +4053,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>392</row>
+      <row>416</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4078,7 +4078,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>392</row>
+      <row>416</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4103,7 +4103,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>408</row>
+      <row>433</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4128,7 +4128,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>408</row>
+      <row>433</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4153,7 +4153,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>408</row>
+      <row>433</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4178,7 +4178,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>408</row>
+      <row>433</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4491,7 +4491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D409"/>
+  <dimension ref="A1:D434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4532,7 +4532,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>골덴호호바오일</t>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>유칼립투스에센셜오일</t>
@@ -4576,7 +4576,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1">
+    <row r="5" ht="16" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
@@ -4598,7 +4598,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>편백에센셜오일</t>
@@ -4620,7 +4620,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="75" customHeight="1">
+    <row r="7" ht="80" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>레몬에센셜오일</t>
@@ -4652,7 +4652,7 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
     </row>
-    <row r="9" ht="45" customHeight="1">
+    <row r="9" ht="48" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>[ 사용방법 ]
@@ -4671,7 +4671,7 @@
       <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
     </row>
-    <row r="11" ht="60" customHeight="1">
+    <row r="11" ht="64" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
           <t>만들기 방법
@@ -4725,7 +4725,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
+    <row r="17" ht="32" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
           <t>골덴호호바오일</t>
@@ -4747,7 +4747,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="60" customHeight="1">
+    <row r="18" ht="64" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
+    <row r="19" ht="16" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
           <t>마조람에센셜오일</t>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="60" customHeight="1">
+    <row r="20" ht="64" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
           <t>로먼카모마일에센셜오일</t>
@@ -4813,7 +4813,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
+    <row r="21" ht="32" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>스윗오렌지에센셜오일</t>
@@ -4845,7 +4845,7 @@
       <c r="C22" s="6" t="n"/>
       <c r="D22" s="6" t="n"/>
     </row>
-    <row r="23" ht="45" customHeight="1">
+    <row r="23" ht="48" customHeight="1">
       <c r="A23" s="9" t="inlineStr">
         <is>
           <t>[ 사용방법 ]
@@ -4867,7 +4867,7 @@
       <c r="C24" s="6" t="n"/>
       <c r="D24" s="6" t="n"/>
     </row>
-    <row r="25" ht="60" customHeight="1">
+    <row r="25" ht="64" customHeight="1">
       <c r="A25" s="9" t="inlineStr">
         <is>
           <t>만들기 방법
@@ -4929,7 +4929,7 @@
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="32" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
           <t>골덴호호바오일</t>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="32" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
           <t>로즈마리에센셜오일</t>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
+    <row r="33" ht="16" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
           <t>페파민트에센셜오일</t>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="75" customHeight="1">
+    <row r="34" ht="80" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>레몬에센셜오일</t>
@@ -5027,7 +5027,7 @@
       <c r="C35" s="6" t="n"/>
       <c r="D35" s="6" t="n"/>
     </row>
-    <row r="36" ht="45" customHeight="1">
+    <row r="36" ht="48" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
           <t>[ 사용방법 ]
@@ -5046,7 +5046,7 @@
       <c r="C37" s="6" t="n"/>
       <c r="D37" s="6" t="n"/>
     </row>
-    <row r="38" ht="60" customHeight="1">
+    <row r="38" ht="64" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
           <t>만들기 방법
@@ -5100,7 +5100,7 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="45" customHeight="1">
+    <row r="44" ht="48" customHeight="1">
       <c r="A44" s="8" t="inlineStr">
         <is>
           <t>비정제 사카잉키오일</t>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="D44" s="8" t="n"/>
     </row>
-    <row r="45" ht="75" customHeight="1">
+    <row r="45" ht="80" customHeight="1">
       <c r="A45" s="8" t="inlineStr">
         <is>
           <t>(유기농) / 마카다미아넛오일</t>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="30" customHeight="1">
+    <row r="46" ht="32" customHeight="1">
       <c r="A46" s="8" t="inlineStr">
         <is>
           <t>로즈우드EO</t>
@@ -5162,7 +5162,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
+    <row r="47" ht="32" customHeight="1">
       <c r="A47" s="8" t="inlineStr">
         <is>
           <t>프랑킨센스EO</t>
@@ -5194,7 +5194,7 @@
       <c r="C48" s="6" t="n"/>
       <c r="D48" s="6" t="n"/>
     </row>
-    <row r="49" ht="480" customHeight="1">
+    <row r="49" ht="384" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
           <t>사카잉키 페이셜트리트먼트오일입니다. 피부를 건강하고 가꾸어주고 외부유해환경으로부터 피부를 보호하는데 도움을 줍니다. 단 한방울 매끄럽고 촉촉하고 밝고 고른 피부로 가꿔줍니다. 수분손실을 막아줄 뿐아니라 세월의 흔적인 얼룩덜룩한 피부톤과 피부쳐짐을 관리하는데 도움을 줍니다.
@@ -5217,8 +5217,17 @@
 신의 3일은 인간에게 30년이였기 때문입니다.
 긴 기다림에 아름다움을 잃어버린 그녀를 본 신은 가슴 아파했고
 그녀의 젊음을 되돌려주기 위해
-가장 빛나는 하늘의 별을 따다 땅에 심어주었습니다.
-그렇게 탄생한 열매가 '사카잉키'...
+가장 빛나는 하늘의 별을 따다 땅에 심어주었습니다.</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+    </row>
+    <row r="50" ht="128" customHeight="1">
+      <c r="A50" s="9" t="inlineStr">
+        <is>
+          <t>그렇게 탄생한 열매가 '사카잉키'...
 그녀는 열매를 먹고 잠이 들었고 다음날 물가에 나와 깜짝 놀랐습니다.
 물에 비친 얼굴은 30년전 젊고 아름다웠던 자신의 모습이었기 때문입니다.
 이렇게 다시 젊음을 되찾은 그녀는 영운한 아름다움을 간직한 채
@@ -5228,22 +5237,22 @@
 로즈우드와 프랑킨센스에센셜오일로 아로마테라피효과도 함께 볼 수 있습니다.</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n"/>
-      <c r="C49" s="10" t="n"/>
-      <c r="D49" s="10" t="n"/>
-    </row>
-    <row r="50" ht="14" customHeight="1">
-      <c r="A50" s="5" t="inlineStr">
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+    </row>
+    <row r="51" ht="14" customHeight="1">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="6" t="n"/>
-    </row>
-    <row r="51" ht="105" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+    </row>
+    <row r="52" ht="112" customHeight="1">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>간단 만들기과정
 1.재료를 계량하세요. 순서에 관계없이. 사카잉키오일
@@ -5254,137 +5263,143 @@
 6..단 한방울의 오일로 다양한 효과를~</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n"/>
-      <c r="C51" s="10" t="n"/>
-      <c r="D51" s="10" t="n"/>
-    </row>
-    <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+    </row>
+    <row r="53" ht="14" customHeight="1">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-    </row>
-    <row r="53" ht="171" customHeight="1">
-      <c r="A53" s="10" t="n"/>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="10" t="n"/>
-      <c r="D53" s="10" t="n"/>
-    </row>
-    <row r="54" ht="6" customHeight="1"/>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="1" t="inlineStr">
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n"/>
+      <c r="D53" s="6" t="n"/>
+    </row>
+    <row r="54" ht="85.5" customHeight="1">
+      <c r="A54" s="10" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+    </row>
+    <row r="55" ht="85.5" customHeight="1">
+      <c r="A55" s="10" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+    </row>
+    <row r="56" ht="6" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1">
+      <c r="A57" s="1" t="inlineStr">
         <is>
           <t>페이셜트리트먼트오일(민감베이비)    [베이스, / 캐리어오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-    </row>
-    <row r="56" ht="15" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="B57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B58" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="C58" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="D58" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="75" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="59" ht="80" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>오트밀오일</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B59" s="4" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C59" s="4" t="inlineStr">
         <is>
           <t>오트밀 용매추출, 오트밀 특유의 향이 그대로, 자극없이 흡수 촉촉함이 오래, 건성피부개선. 비타민E, 오메가-6, 오메가-9 풍부 항산화, 보습, 진정효과</t>
         </is>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D59" s="4" t="inlineStr">
         <is>
           <t>아르간, 바오밥오일 등 다양한 오일</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
+    <row r="60" ht="48" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>버진 동백오일 / (야생, 제주)</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비, / 민감 성피부</t>
         </is>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>아르간오일, 호호바오일, 마카다미아넛오일 등</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
+    <row r="61" ht="48" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>로먼캐모마일 / 에센셜오일</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B61" s="4" t="inlineStr">
         <is>
           <t>3~6방울</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C61" s="4" t="inlineStr">
         <is>
           <t>국화과 허브, 진정효과 탁월, 민감 신생아 영유아 사용 / 넣지 않고 사용하면 오트밀오일 자체향.</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D61" s="4" t="inlineStr">
         <is>
           <t>라벤더에센셜오일 / 네롤리에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="14" customHeight="1">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="62" ht="14" customHeight="1">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B60" s="6" t="n"/>
-      <c r="C60" s="6" t="n"/>
-      <c r="D60" s="6" t="n"/>
-    </row>
-    <row r="61" ht="600" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+    </row>
+    <row r="63" ht="384" customHeight="1">
+      <c r="A63" s="7" t="inlineStr">
         <is>
           <t>버진동백오일과 오트밀오일은
 민감한 피부나 어린 아이들의 연약한 피부를 위한 최고의 배합입니다.
@@ -5409,8 +5424,14 @@
 ....
 동백오일은 이름에서도 알 수 있듯
 찬바람이 부는 겨울에 꽃망울을 터뜨리며 흐드러지게 피어나는 꽃입니다.
-동백은 제주도와 우리나라의 남해안에 자생하는 우리나라의 대표적인 수종입니다.
-예로부터 여인네들의 머릿기름과 식용으로 널리 사용됐으며
+동백은 제주도와 우리나라의 남해안에 자생하는 우리나라의 대표적인 수종입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="336" customHeight="1">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>예로부터 여인네들의 머릿기름과 식용으로 널리 사용됐으며
 제주에서는 결혼식 음식을 만들 때만 사용될 정도로 귀하게 여겨진 기름이기도 합니다.
 피부 보습은 물론 천식 등의 치료용으로도 사용됐습니다.
 또한 동백기름은 다른 식물성 기름과는 달리 산패가 잘 되지 않고 안정한 특성 때문에 공업용으로도 사용되었습니다
@@ -5424,23 +5445,29 @@
 1.건조할 때 얼굴에 올라온 각질케어 2.윤기나는 눈썹정돈 및 영양공급 3.4계절 내내 촉촉하게 입술 보호
 4.코, 입가 주변 하얗게 튼 곳을 촉촉하게 5.부슬부슬 갈라진 머리 끝을 촉촉하게, 영양공급 6.미스트 뿌린 후 덧 발라주면 촉촉함이 오래 7.BB크림, 파운데이션과 섞어 바르면 꿀광피부 8.촉촉하고 예쁜 손끝, 큐티클 관리 9.핸드로션 대용
 10.건조하기 쉬운 손발에 크림+밤+랩핑으로 스페셜케어 11.팔꿈치를 매끈하게 12.딱딱하게 굳은 살을 부드럽게
-13.갈라지고 건조한 발꿈치 각질케어 14.발 마사지할때 15.매일 아침 거슬리는 잔머리, 곱슬머리 정돈
-16.로션,크림에 섞어서 더 촉촉하게 17.헤어 팩과 섞어서 사용 18.메이크업 마무리 단계에서 건조한 부위에 가볍게 눌러주듯 발라 유수분 발란스조절 19.편안한 향취 20.제모 후 자극 받은 피부에 21.욕실에 놓고 세안 후 바로 사용해 3초 보습 이외에도 영유아 바디페이셜 오일로 다양하게 활용하세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="14" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
+13.갈라지고 건조한 발꿈치 각질케어 14.발 마사지할때 15.매일 아침 거슬리는 잔머리, 곱슬머리 정돈</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="64" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>16.로션,크림에 섞어서 더 촉촉하게 17.헤어 팩과 섞어서 사용 18.메이크업 마무리 단계에서 건조한 부위에 가볍게 눌러주듯 발라 유수분 발란스조절 19.편안한 향취 20.제모 후 자극 받은 피부에 21.욕실에 놓고 세안 후 바로 사용해 3초 보습 이외에도 영유아 바디페이셜 오일로 다양하게 활용하세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="14" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B62" s="6" t="n"/>
-      <c r="C62" s="6" t="n"/>
-      <c r="D62" s="6" t="n"/>
-    </row>
-    <row r="63" ht="105" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n"/>
+    </row>
+    <row r="67" ht="112" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>간단 만들기과정
 1.재료를 계량하세요. 오트밀오일을 계량하고
@@ -5452,80 +5479,81 @@
         </is>
       </c>
     </row>
-    <row r="64" ht="14" customHeight="1">
-      <c r="A64" s="5" t="inlineStr">
+    <row r="68" ht="14" customHeight="1">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B64" s="6" t="n"/>
-      <c r="C64" s="6" t="n"/>
-      <c r="D64" s="6" t="n"/>
-    </row>
-    <row r="65" ht="171" customHeight="1"/>
-    <row r="66" ht="6" customHeight="1"/>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="1" t="inlineStr">
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n"/>
+      <c r="D68" s="6" t="n"/>
+    </row>
+    <row r="69" ht="85.5" customHeight="1"/>
+    <row r="70" ht="85.5" customHeight="1"/>
+    <row r="71" ht="6" customHeight="1"/>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="1" t="inlineStr">
         <is>
           <t>오미자 래핑오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B67" s="2" t="n"/>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n"/>
-    </row>
-    <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="B72" s="2" t="n"/>
+      <c r="C72" s="2" t="n"/>
+      <c r="D72" s="2" t="n"/>
+    </row>
+    <row r="73" ht="15" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B73" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C73" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D73" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="150" customHeight="1">
-      <c r="A69" s="8" t="inlineStr">
+    <row r="74" ht="176" customHeight="1">
+      <c r="A74" s="8" t="inlineStr">
         <is>
           <t>오미자씨 오일</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
+      <c r="B74" s="8" t="inlineStr">
         <is>
           <t>20ml / (18g)</t>
         </is>
       </c>
-      <c r="C69" s="8" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>오미자 과육에서 순수 분리된 원형 그대로의 오미자씨를 이용하였습니다. 과육에서 분리된 씨앗의 변질을 막기 위해 냉동 후 냉풍 건조합니다. 유효성분의 변화를 최소화하기 위하며 저온 압착추출 방법으로 추출하였고 / 최소한의 정제과정만을 거친 / extra virgin type oil입니다. / 생오미자 1000kg(1톤)에서 얻을 수 있는 오미자오일은 1~2%정도입니다.</t>
         </is>
       </c>
-      <c r="D69" s="8" t="n"/>
-    </row>
-    <row r="70" ht="14" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
+      <c r="D74" s="8" t="n"/>
+    </row>
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="6" t="n"/>
-    </row>
-    <row r="71" ht="495" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+    </row>
+    <row r="76" ht="384" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
         <is>
           <t>날씨가 건조하고 차가워질수록 우리 피부는 촉촉한 오일이 필요합니다.
 우리 몸은 오일(피지, 개기름^^)을 생성해
@@ -5549,8 +5577,17 @@
 오직 국내(문경) 오미자 과육에서 순수 분리된 원형 그대로의 오미자씨를 이용하였습니다.
 과육에서 분리된 씨앗의 변질을 막기 위해 냉동 후 냉풍 건조합니다.
 유효성분의 변화를 최소화하기 위하며 저온 압착추출 방법으로 추출하였고
-최소한의 정제과정만을 거친 extra virgin type oil입니다.
-생오미자 1000kg(1톤)에서 얻을 수 있는 오미자오일은 1~2%정도입니다.
+최소한의 정제과정만을 거친 extra virgin type oil입니다.</t>
+        </is>
+      </c>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+    </row>
+    <row r="77" ht="144" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>생오미자 1000kg(1톤)에서 얻을 수 있는 오미자오일은 1~2%정도입니다.
 엑스트라버진 오미자오일은 피부를 건강하게 만드는
 팔마틱산(Palmitic acid)을 비롯 다양한 불포화 지방산을 풍부하게 함유하고 있고
 그 외 다양한 정유 성분이 포함되어 있습니다.
@@ -5561,22 +5598,22 @@
 오~~~~미자 래핑 오일 100% 활용하기</t>
         </is>
       </c>
-      <c r="B71" s="10" t="n"/>
-      <c r="C71" s="10" t="n"/>
-      <c r="D71" s="10" t="n"/>
-    </row>
-    <row r="72" ht="14" customHeight="1">
-      <c r="A72" s="5" t="inlineStr">
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
+    </row>
+    <row r="78" ht="14" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6" t="n"/>
-    </row>
-    <row r="73" ht="210" customHeight="1">
-      <c r="A73" s="9" t="inlineStr">
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+    </row>
+    <row r="79" ht="224" customHeight="1">
+      <c r="A79" s="9" t="inlineStr">
         <is>
           <t>1.스킨 케어 마지막 단계에서
 손바닥에 한두방울 덜어
@@ -5594,137 +5631,137 @@
 8. 싱그러운 오미자 향기 테라피효과.</t>
         </is>
       </c>
-      <c r="B73" s="10" t="n"/>
-      <c r="C73" s="10" t="n"/>
-      <c r="D73" s="10" t="n"/>
-    </row>
-    <row r="74" ht="14" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+    </row>
+    <row r="80" ht="14" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="6" t="n"/>
-    </row>
-    <row r="75" ht="85.5" customHeight="1">
-      <c r="A75" s="10" t="n"/>
-      <c r="B75" s="10" t="n"/>
-      <c r="C75" s="10" t="n"/>
-      <c r="D75" s="10" t="n"/>
-    </row>
-    <row r="76" ht="6" customHeight="1"/>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="1" t="inlineStr">
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+    </row>
+    <row r="81" ht="85.5" customHeight="1">
+      <c r="A81" s="10" t="n"/>
+      <c r="B81" s="10" t="n"/>
+      <c r="C81" s="10" t="n"/>
+      <c r="D81" s="10" t="n"/>
+    </row>
+    <row r="82" ht="6" customHeight="1"/>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="1" t="inlineStr">
         <is>
           <t>아르간페이셜세럼    ↗ 원본</t>
         </is>
       </c>
-      <c r="B77" s="2" t="n"/>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n"/>
-    </row>
-    <row r="78" ht="15" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="B83" s="2" t="n"/>
+      <c r="C83" s="2" t="n"/>
+      <c r="D83" s="2" t="n"/>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B78" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C78" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D78" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="45" customHeight="1">
-      <c r="A79" s="4" t="inlineStr">
+    <row r="85" ht="64" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>아르간오일</t>
         </is>
       </c>
-      <c r="B79" s="4" t="inlineStr">
+      <c r="B85" s="4" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C85" s="4" t="inlineStr">
         <is>
           <t>모로코에서만 나는 아르간나무열매, 토코페롤, 폴리페놀, 스쿠알렌 등 다량함유, 노화, 민감, 재생 등 사용</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D85" s="4" t="inlineStr">
         <is>
           <t>로즈힙, 달맞이, 햄프씨드, 동백, 호호바 등 원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="90" customHeight="1">
-      <c r="A80" s="4" t="inlineStr">
+    <row r="86" ht="96" customHeight="1">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B80" s="4" t="inlineStr">
+      <c r="B86" s="4" t="inlineStr">
         <is>
           <t>8g(튜브에 담을경우) / 또는 / 10g (크림용기담을경우)</t>
         </is>
       </c>
-      <c r="C80" s="4" t="inlineStr">
+      <c r="C86" s="4" t="inlineStr">
         <is>
           <t>물과오일 분리되지 않도록 잡아주는 유화제 겸 단단하게 굳게 만드는 경화제, 자체보습력, 올리브오일로 만든 유화제</t>
         </is>
       </c>
-      <c r="D80" s="4" t="inlineStr">
+      <c r="D86" s="4" t="inlineStr">
         <is>
           <t>몬타왁스,이멀시파잉왁스</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="75" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="87" ht="80" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>네롤리에센셜오일</t>
         </is>
       </c>
-      <c r="B81" s="4" t="inlineStr">
+      <c r="B87" s="4" t="inlineStr">
         <is>
           <t>5방울(10방울)</t>
         </is>
       </c>
-      <c r="C81" s="4" t="inlineStr">
+      <c r="C87" s="4" t="inlineStr">
         <is>
           <t>오렌지블라썸, 비터오렌지꽃에센셜오일, 이탈리아의 네롤리공주가 즐겨 사용했다해서 네롤리에센셜오일라고도 부른다. 재생, 민감 피부사용, 임산부튼살예방관리에도 사용</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D87" s="4" t="inlineStr">
         <is>
           <t>로즈, 자스민, 프랑킨센스, 로먼캐모마일, 라벤더 등 원하는에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="14" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
+    <row r="88" ht="14" customHeight="1">
+      <c r="A88" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="6" t="n"/>
-      <c r="D82" s="6" t="n"/>
-    </row>
-    <row r="83" ht="135" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
+      <c r="B88" s="6" t="n"/>
+      <c r="C88" s="6" t="n"/>
+      <c r="D88" s="6" t="n"/>
+    </row>
+    <row r="89" ht="144" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
         <is>
           <t>초보자들이 도전해볼만하고 만들기하고 있는 분들도 간단 재료,
 간단 만들기, 효과는 오래오래라 호감가는 레시피가 되겠습니다.
@@ -5738,18 +5775,18 @@
         </is>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
+    <row r="90" ht="14" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="D84" s="6" t="n"/>
-    </row>
-    <row r="85" ht="225" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
+      <c r="B90" s="6" t="n"/>
+      <c r="C90" s="6" t="n"/>
+      <c r="D90" s="6" t="n"/>
+    </row>
+    <row r="91" ht="240" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>1.아르간오일계량하기
 2.올리브유화왁스계량하기
@@ -5768,128 +5805,130 @@
         </is>
       </c>
     </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+    <row r="92" ht="14" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6" t="n"/>
-    </row>
-    <row r="87" ht="256.5" customHeight="1"/>
-    <row r="88" ht="6" customHeight="1"/>
-    <row r="89" ht="22" customHeight="1">
-      <c r="A89" s="1" t="inlineStr">
+      <c r="B92" s="6" t="n"/>
+      <c r="C92" s="6" t="n"/>
+      <c r="D92" s="6" t="n"/>
+    </row>
+    <row r="93" ht="85.5" customHeight="1"/>
+    <row r="94" ht="85.5" customHeight="1"/>
+    <row r="95" ht="85.5" customHeight="1"/>
+    <row r="96" ht="6" customHeight="1"/>
+    <row r="97" ht="22" customHeight="1">
+      <c r="A97" s="1" t="inlineStr">
         <is>
           <t>아토 캐모마일 세럼    ↗ 원본</t>
         </is>
       </c>
-      <c r="B89" s="2" t="n"/>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n"/>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="B97" s="2" t="n"/>
+      <c r="C97" s="2" t="n"/>
+      <c r="D97" s="2" t="n"/>
+    </row>
+    <row r="98" ht="15" customHeight="1">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr">
+      <c r="B98" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C90" s="3" t="inlineStr">
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D90" s="3" t="inlineStr">
+      <c r="D98" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="45" customHeight="1">
-      <c r="A91" s="8" t="inlineStr">
+    <row r="99" ht="48" customHeight="1">
+      <c r="A99" s="8" t="inlineStr">
         <is>
           <t>캐모마일오일 / (인퓨즈오일)</t>
         </is>
       </c>
-      <c r="B91" s="8" t="inlineStr">
+      <c r="B99" s="8" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C91" s="8" t="inlineStr">
+      <c r="C99" s="8" t="inlineStr">
         <is>
           <t>올리브오일에 카모마일을 인퓨즈하여 만든오일, 올리브오일의 보습, 카모마일의 진정효과 함께 볼수 있다</t>
         </is>
       </c>
-      <c r="D91" s="8" t="inlineStr">
+      <c r="D99" s="8" t="inlineStr">
         <is>
           <t>햄프씨드오일, 보리지,달맞이,동백, 카렌듈라, 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="45" customHeight="1">
-      <c r="A92" s="8" t="inlineStr">
+    <row r="100" ht="48" customHeight="1">
+      <c r="A100" s="8" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B92" s="8" t="inlineStr">
+      <c r="B100" s="8" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C92" s="8" t="inlineStr">
+      <c r="C100" s="8" t="inlineStr">
         <is>
           <t>올리브오일로 만든 경화제, 물과 오일이 분리되지 않도록 하는 유화제. 자극없음</t>
         </is>
       </c>
-      <c r="D92" s="8" t="inlineStr">
+      <c r="D100" s="8" t="inlineStr">
         <is>
           <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="60" customHeight="1">
-      <c r="A93" s="8" t="inlineStr">
+    <row r="101" ht="64" customHeight="1">
+      <c r="A101" s="8" t="inlineStr">
         <is>
           <t>로먼카모마일</t>
         </is>
       </c>
-      <c r="B93" s="8" t="inlineStr">
+      <c r="B101" s="8" t="inlineStr">
         <is>
           <t>5-10방울</t>
         </is>
       </c>
-      <c r="C93" s="8" t="inlineStr">
+      <c r="C101" s="8" t="inlineStr">
         <is>
           <t>0.5-1%에 해당하는 양, 국화과허브, 심신진정, 항염증 등</t>
         </is>
       </c>
-      <c r="D93" s="8" t="inlineStr">
+      <c r="D101" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일, 저먼카모마일(을 사용할 경우 양을 반으로 줄여야함.강한향)</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="14" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="102" ht="14" customHeight="1">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="6" t="n"/>
-      <c r="D94" s="6" t="n"/>
-    </row>
-    <row r="95" ht="90" customHeight="1">
-      <c r="A95" s="9" t="inlineStr">
+      <c r="B102" s="6" t="n"/>
+      <c r="C102" s="6" t="n"/>
+      <c r="D102" s="6" t="n"/>
+    </row>
+    <row r="103" ht="96" customHeight="1">
+      <c r="A103" s="9" t="inlineStr">
         <is>
           <t>땅위에서 나는 사과라는 뜻의 카모마일.
 달콤한 사과향이 나서 정서 안정은 물론 피부진정효과도 있어요.
@@ -5899,22 +5938,22 @@
 만들기방법</t>
         </is>
       </c>
-      <c r="B95" s="10" t="n"/>
-      <c r="C95" s="10" t="n"/>
-      <c r="D95" s="10" t="n"/>
-    </row>
-    <row r="96" ht="14" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
+      <c r="B103" s="10" t="n"/>
+      <c r="C103" s="10" t="n"/>
+      <c r="D103" s="10" t="n"/>
+    </row>
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="6" t="n"/>
-      <c r="D96" s="6" t="n"/>
-    </row>
-    <row r="97" ht="240" customHeight="1">
-      <c r="A97" s="9" t="inlineStr">
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+    </row>
+    <row r="105" ht="256" customHeight="1">
+      <c r="A105" s="9" t="inlineStr">
         <is>
           <t>1.아르간오일계량하기
 2.올리브유화왁스계량하기
@@ -5931,115 +5970,127 @@
 골고루 비벼주시면 되요. 촉촉함이 오래오래~</t>
         </is>
       </c>
-      <c r="B97" s="10" t="n"/>
-      <c r="C97" s="10" t="n"/>
-      <c r="D97" s="10" t="n"/>
-    </row>
-    <row r="98" ht="14" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
+      <c r="B105" s="10" t="n"/>
+      <c r="C105" s="10" t="n"/>
+      <c r="D105" s="10" t="n"/>
+    </row>
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B98" s="6" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6" t="n"/>
-    </row>
-    <row r="99" ht="256.5" customHeight="1">
-      <c r="A99" s="10" t="n"/>
-      <c r="B99" s="10" t="n"/>
-      <c r="C99" s="10" t="n"/>
-      <c r="D99" s="10" t="n"/>
-    </row>
-    <row r="100" ht="6" customHeight="1"/>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="1" t="inlineStr">
+      <c r="B106" s="6" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="n"/>
+    </row>
+    <row r="107" ht="85.5" customHeight="1">
+      <c r="A107" s="10" t="n"/>
+      <c r="B107" s="10" t="n"/>
+      <c r="C107" s="10" t="n"/>
+      <c r="D107" s="10" t="n"/>
+    </row>
+    <row r="108" ht="85.5" customHeight="1">
+      <c r="A108" s="10" t="n"/>
+      <c r="B108" s="10" t="n"/>
+      <c r="C108" s="10" t="n"/>
+      <c r="D108" s="10" t="n"/>
+    </row>
+    <row r="109" ht="85.5" customHeight="1">
+      <c r="A109" s="10" t="n"/>
+      <c r="B109" s="10" t="n"/>
+      <c r="C109" s="10" t="n"/>
+      <c r="D109" s="10" t="n"/>
+    </row>
+    <row r="110" ht="6" customHeight="1"/>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="1" t="inlineStr">
         <is>
           <t>발효마유 페이셜&amp;바디오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B101" s="2" t="n"/>
-      <c r="C101" s="2" t="n"/>
-      <c r="D101" s="2" t="n"/>
-    </row>
-    <row r="102" ht="15" customHeight="1">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="B111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n"/>
+    </row>
+    <row r="112" ht="15" customHeight="1">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr">
+      <c r="B112" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C102" s="3" t="inlineStr">
+      <c r="C112" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D102" s="3" t="inlineStr">
+      <c r="D112" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="60" customHeight="1">
-      <c r="A103" s="4" t="inlineStr">
+    <row r="113" ht="64" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>발효 마유</t>
         </is>
       </c>
-      <c r="B103" s="4" t="inlineStr">
+      <c r="B113" s="4" t="inlineStr">
         <is>
           <t>30ml / (27g)</t>
         </is>
       </c>
-      <c r="C103" s="4" t="inlineStr">
+      <c r="C113" s="4" t="inlineStr">
         <is>
           <t>제주산 발효 마유, / 마유 중 비중이 가벼운 부분 , / 팔마톨레익산 등 불포화지방산 풍부, / 특이취 거의 없음</t>
         </is>
       </c>
-      <c r="D103" s="4" t="inlineStr">
+      <c r="D113" s="4" t="inlineStr">
         <is>
           <t>호호바오일, 동백오일 / 아르간오일 등</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="45" customHeight="1">
-      <c r="A104" s="4" t="inlineStr">
+    <row r="114" ht="48" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>네롤리 에센셜오일</t>
         </is>
       </c>
-      <c r="B104" s="4" t="inlineStr">
+      <c r="B114" s="4" t="inlineStr">
         <is>
           <t>2~5방울</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C114" s="4" t="inlineStr">
         <is>
           <t>오렌지꽃오일, 수증기 증류법으로 / 추출, 고농축, 민감, 노화피부에 사용</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D114" s="4" t="inlineStr">
         <is>
           <t>로즈, 자스민 / 에센셜오일등</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="14" customHeight="1">
-      <c r="A105" s="5" t="inlineStr">
+    <row r="115" ht="14" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B105" s="6" t="n"/>
-      <c r="C105" s="6" t="n"/>
-      <c r="D105" s="6" t="n"/>
-    </row>
-    <row r="106" ht="90" customHeight="1">
-      <c r="A106" s="7" t="inlineStr">
+      <c r="B115" s="6" t="n"/>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+    </row>
+    <row r="116" ht="96" customHeight="1">
+      <c r="A116" s="7" t="inlineStr">
         <is>
           <t>이전에 제주산 발효 마유 자체가 효과가 너무 좋아
 유상, 수상, 첨가물을 최소화하여 발효 마유 미니멈 크림레시피를 안내해드렸습니다.
@@ -6050,18 +6101,18 @@
         </is>
       </c>
     </row>
-    <row r="107" ht="14" customHeight="1">
-      <c r="A107" s="5" t="inlineStr">
+    <row r="117" ht="14" customHeight="1">
+      <c r="A117" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B107" s="6" t="n"/>
-      <c r="C107" s="6" t="n"/>
-      <c r="D107" s="6" t="n"/>
-    </row>
-    <row r="108" ht="165" customHeight="1">
-      <c r="A108" s="7" t="inlineStr">
+      <c r="B117" s="6" t="n"/>
+      <c r="C117" s="6" t="n"/>
+      <c r="D117" s="6" t="n"/>
+    </row>
+    <row r="118" ht="176" customHeight="1">
+      <c r="A118" s="7" t="inlineStr">
         <is>
           <t>1. 로션이나 수분크림까지 바르고 난 뒤 스킨케어 마지막 단계에서 한두 방울 정도 체온으로 녹여 손바닥에 펴발라주세요.
 2. 그다음 손바닥으로 얼굴을 감싸듯 마사지합니다. 오일이 얼굴전체에 코팅을 해주어 수분이 증발하지 않도록 보호하고 촉촉함을 유지해줍니다.
@@ -6074,105 +6125,105 @@
         </is>
       </c>
     </row>
-    <row r="109" ht="14" customHeight="1">
-      <c r="A109" s="5" t="inlineStr">
+    <row r="119" ht="14" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B109" s="6" t="n"/>
-      <c r="C109" s="6" t="n"/>
-      <c r="D109" s="6" t="n"/>
-    </row>
-    <row r="110" ht="85.5" customHeight="1"/>
-    <row r="111" ht="6" customHeight="1"/>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="1" t="inlineStr">
+      <c r="B119" s="6" t="n"/>
+      <c r="C119" s="6" t="n"/>
+      <c r="D119" s="6" t="n"/>
+    </row>
+    <row r="120" ht="85.5" customHeight="1"/>
+    <row r="121" ht="6" customHeight="1"/>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="1" t="inlineStr">
         <is>
           <t>버진코코넛 오일 폴링    ↗ 원본</t>
         </is>
       </c>
-      <c r="B112" s="2" t="n"/>
-      <c r="C112" s="2" t="n"/>
-      <c r="D112" s="2" t="n"/>
-    </row>
-    <row r="113" ht="15" customHeight="1">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="B122" s="2" t="n"/>
+      <c r="C122" s="2" t="n"/>
+      <c r="D122" s="2" t="n"/>
+    </row>
+    <row r="123" ht="15" customHeight="1">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B113" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C113" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D113" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="45" customHeight="1">
-      <c r="A114" s="8" t="inlineStr">
+    <row r="124" ht="48" customHeight="1">
+      <c r="A124" s="8" t="inlineStr">
         <is>
           <t>버진 코코넛오일</t>
         </is>
       </c>
-      <c r="B114" s="8" t="inlineStr">
+      <c r="B124" s="8" t="inlineStr">
         <is>
           <t>90g</t>
         </is>
       </c>
-      <c r="C114" s="8" t="inlineStr">
+      <c r="C124" s="8" t="inlineStr">
         <is>
           <t>주성분 라우릭산(Lauric Acid), / 중사슬 지방산인 분자구조가 단순해 / 끈적임이 없습니다.</t>
         </is>
       </c>
-      <c r="D114" s="8" t="inlineStr">
+      <c r="D124" s="8" t="inlineStr">
         <is>
           <t>포도씨오일, 해바라기오일 등</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="14" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
+    <row r="125" ht="14" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B115" s="6" t="n"/>
-      <c r="C115" s="6" t="n"/>
-      <c r="D115" s="6" t="n"/>
-    </row>
-    <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="9" t="inlineStr">
+      <c r="B125" s="6" t="n"/>
+      <c r="C125" s="6" t="n"/>
+      <c r="D125" s="6" t="n"/>
+    </row>
+    <row r="126" ht="32" customHeight="1">
+      <c r="A126" s="9" t="inlineStr">
         <is>
           <t>'오일풀링(oil-pulling)'이란
 공복 상태에서 식물성 오일을 한 숟가락 정도 입안에 머금고</t>
         </is>
       </c>
-      <c r="B116" s="10" t="n"/>
-      <c r="C116" s="10" t="n"/>
-      <c r="D116" s="10" t="n"/>
-    </row>
-    <row r="117" ht="14" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="B126" s="10" t="n"/>
+      <c r="C126" s="10" t="n"/>
+      <c r="D126" s="10" t="n"/>
+    </row>
+    <row r="127" ht="14" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B117" s="6" t="n"/>
-      <c r="C117" s="6" t="n"/>
-      <c r="D117" s="6" t="n"/>
-    </row>
-    <row r="118" ht="465" customHeight="1">
-      <c r="A118" s="9" t="inlineStr">
+      <c r="B127" s="6" t="n"/>
+      <c r="C127" s="6" t="n"/>
+      <c r="D127" s="6" t="n"/>
+    </row>
+    <row r="128" ht="384" customHeight="1">
+      <c r="A128" s="9" t="inlineStr">
         <is>
           <t>15~20분간 가글한 뒤 뱉어내는 구강관리법을 이야기합니다.
 힌두교 경전에 의해 전승된
@@ -6194,8 +6245,17 @@
 오일풀링에 주로 사용되는 오일은 입자가 적은 코코넛 오일을 추천해드립니다.
 비롯해 올리브오일, 포도씨오일, 해바라기오일 등도 가능합니다.
 손쉬운 코코넛 오일 폴링으로 건강한 구강을 가꾸세요.
-오일 폴링(oil-pulling)하는 방법 .
-입속에서 박테리아가 가장 활발하게 번식하는 아침 기상 직후
+오일 폴링(oil-pulling)하는 방법 .</t>
+        </is>
+      </c>
+      <c r="B128" s="10" t="n"/>
+      <c r="C128" s="10" t="n"/>
+      <c r="D128" s="10" t="n"/>
+    </row>
+    <row r="129" ht="112" customHeight="1">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>입속에서 박테리아가 가장 활발하게 번식하는 아침 기상 직후
 공복에 실행하는 것이 효과적입니다.
 10분정도 오일을 2숟갈 정도 입에 넣어 머금고 뱉어냅니다.
 다음에는 혀에 남아있는 오일 잔여물을 꼼꼼히 닦아내는 것이 중요합니다.
@@ -6203,173 +6263,173 @@
 1. 가글 중에 세균 찌꺼기가 섞인 오일이 목구멍으로 넘어가지 않도록 유의해야 한다. 2. 치과 치료 등으로 구강 내에 상처가 있을 경우에는 감염의 위험이 있습니다.</t>
         </is>
       </c>
-      <c r="B118" s="10" t="n"/>
-      <c r="C118" s="10" t="n"/>
-      <c r="D118" s="10" t="n"/>
-    </row>
-    <row r="119" ht="14" customHeight="1">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="B129" s="10" t="n"/>
+      <c r="C129" s="10" t="n"/>
+      <c r="D129" s="10" t="n"/>
+    </row>
+    <row r="130" ht="14" customHeight="1">
+      <c r="A130" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B119" s="6" t="n"/>
-      <c r="C119" s="6" t="n"/>
-      <c r="D119" s="6" t="n"/>
-    </row>
-    <row r="120" ht="85.5" customHeight="1">
-      <c r="A120" s="10" t="n"/>
-      <c r="B120" s="10" t="n"/>
-      <c r="C120" s="10" t="n"/>
-      <c r="D120" s="10" t="n"/>
-    </row>
-    <row r="121" ht="6" customHeight="1"/>
-    <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="1" t="inlineStr">
+      <c r="B130" s="6" t="n"/>
+      <c r="C130" s="6" t="n"/>
+      <c r="D130" s="6" t="n"/>
+    </row>
+    <row r="131" ht="85.5" customHeight="1">
+      <c r="A131" s="10" t="n"/>
+      <c r="B131" s="10" t="n"/>
+      <c r="C131" s="10" t="n"/>
+      <c r="D131" s="10" t="n"/>
+    </row>
+    <row r="132" ht="6" customHeight="1"/>
+    <row r="133" ht="22" customHeight="1">
+      <c r="A133" s="1" t="inlineStr">
         <is>
           <t>자초 립에센스(스무디)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B122" s="2" t="n"/>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n"/>
-    </row>
-    <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="B133" s="2" t="n"/>
+      <c r="C133" s="2" t="n"/>
+      <c r="D133" s="2" t="n"/>
+    </row>
+    <row r="134" ht="15" customHeight="1">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B134" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C134" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D134" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="45" customHeight="1">
-      <c r="A124" s="4" t="inlineStr">
+    <row r="135" ht="48" customHeight="1">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>(진한) 자초 인퓨즈오일</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B135" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C135" s="4" t="inlineStr">
         <is>
           <t>자초(식물)의 뿌리를 오일에 우려냄,민감, 트러블 피부 관리에 효과, 지용성 천연 붉은 색소 함유.</t>
         </is>
       </c>
-      <c r="D124" s="4" t="n"/>
-    </row>
-    <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
+      <c r="D135" s="4" t="n"/>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
         <is>
           <t>유기농 코포아수버터</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="B136" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C136" s="4" t="inlineStr">
         <is>
           <t>고체 상태, 식물성 버터, 고보습</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="D136" s="4" t="inlineStr">
         <is>
           <t>버터류</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="30" customHeight="1">
-      <c r="A126" s="4" t="inlineStr">
+    <row r="137" ht="32" customHeight="1">
+      <c r="A137" s="4" t="inlineStr">
         <is>
           <t>에코 바세린</t>
         </is>
       </c>
-      <c r="B126" s="4" t="inlineStr">
+      <c r="B137" s="4" t="inlineStr">
         <is>
           <t>23g</t>
         </is>
       </c>
-      <c r="C126" s="4" t="inlineStr">
+      <c r="C137" s="4" t="inlineStr">
         <is>
           <t>석유계 바세린 대체, 유기농 인증, 해바라기오일 주성분. 젤타입.</t>
         </is>
       </c>
-      <c r="D126" s="4" t="n"/>
-    </row>
-    <row r="127" ht="45" customHeight="1">
-      <c r="A127" s="4" t="inlineStr">
+      <c r="D137" s="4" t="n"/>
+    </row>
+    <row r="138" ht="48" customHeight="1">
+      <c r="A138" s="4" t="inlineStr">
         <is>
           <t>(비타민E)</t>
         </is>
       </c>
-      <c r="B127" s="4" t="inlineStr">
+      <c r="B138" s="4" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="C127" s="4" t="inlineStr">
+      <c r="C138" s="4" t="inlineStr">
         <is>
           <t>지용성 보존제, 고보습,생략가능.</t>
         </is>
       </c>
-      <c r="D127" s="4" t="inlineStr">
+      <c r="D138" s="4" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="30" customHeight="1">
-      <c r="A128" s="4" t="inlineStr">
+    <row r="139" ht="48" customHeight="1">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>딸기플레이버오일</t>
         </is>
       </c>
-      <c r="B128" s="4" t="inlineStr">
+      <c r="B139" s="4" t="inlineStr">
         <is>
           <t>6방울 내외</t>
         </is>
       </c>
-      <c r="C128" s="4" t="inlineStr">
+      <c r="C139" s="4" t="inlineStr">
         <is>
           <t>넣지 않으면 코코넛향이 은은함 / 강한 향을 원하면 원하는 식향을 추가</t>
         </is>
       </c>
-      <c r="D128" s="4" t="inlineStr">
+      <c r="D139" s="4" t="inlineStr">
         <is>
           <t>원하는 / 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="14" customHeight="1">
-      <c r="A129" s="5" t="inlineStr">
+    <row r="140" ht="14" customHeight="1">
+      <c r="A140" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B129" s="6" t="n"/>
-      <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6" t="n"/>
-    </row>
-    <row r="130" ht="165" customHeight="1">
-      <c r="A130" s="7" t="inlineStr">
+      <c r="B140" s="6" t="n"/>
+      <c r="C140" s="6" t="n"/>
+      <c r="D140" s="6" t="n"/>
+    </row>
+    <row r="141" ht="176" customHeight="1">
+      <c r="A141" s="7" t="inlineStr">
         <is>
           <t>부드러움과 촉촉함이 남 다른
 '자초 립에센스' 스무디 타입을 소개해드립니다.
@@ -6385,18 +6445,18 @@
         </is>
       </c>
     </row>
-    <row r="131" ht="14" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="142" ht="14" customHeight="1">
+      <c r="A142" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B131" s="6" t="n"/>
-      <c r="C131" s="6" t="n"/>
-      <c r="D131" s="6" t="n"/>
-    </row>
-    <row r="132" ht="150" customHeight="1">
-      <c r="A132" s="7" t="inlineStr">
+      <c r="B142" s="6" t="n"/>
+      <c r="C142" s="6" t="n"/>
+      <c r="D142" s="6" t="n"/>
+    </row>
+    <row r="143" ht="160" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
         <is>
           <t>1. 에코바세린
 2. 자초인퓨즈오일
@@ -6409,146 +6469,148 @@
         </is>
       </c>
     </row>
-    <row r="133" ht="14" customHeight="1">
-      <c r="A133" s="5" t="inlineStr">
+    <row r="144" ht="14" customHeight="1">
+      <c r="A144" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B133" s="6" t="n"/>
-      <c r="C133" s="6" t="n"/>
-      <c r="D133" s="6" t="n"/>
-    </row>
-    <row r="134" ht="256.5" customHeight="1"/>
-    <row r="135" ht="6" customHeight="1"/>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="1" t="inlineStr">
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+    </row>
+    <row r="145" ht="85.5" customHeight="1"/>
+    <row r="146" ht="85.5" customHeight="1"/>
+    <row r="147" ht="85.5" customHeight="1"/>
+    <row r="148" ht="6" customHeight="1"/>
+    <row r="149" ht="22" customHeight="1">
+      <c r="A149" s="1" t="inlineStr">
         <is>
           <t>만능 내추럴 바세린    ↗ 원본</t>
         </is>
       </c>
-      <c r="B136" s="2" t="n"/>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n"/>
-    </row>
-    <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="B149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n"/>
+    </row>
+    <row r="150" ht="15" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B137" s="3" t="inlineStr">
+      <c r="B150" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C137" s="3" t="inlineStr">
+      <c r="C150" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D137" s="3" t="inlineStr">
+      <c r="D150" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="30" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
+    <row r="151" ht="32" customHeight="1">
+      <c r="A151" s="8" t="inlineStr">
         <is>
           <t>골든 호호바오일</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B151" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C138" s="8" t="inlineStr">
+      <c r="C151" s="8" t="inlineStr">
         <is>
           <t>피지 성분 비슷. / 콩과식물, 액상왁스구조</t>
         </is>
       </c>
-      <c r="D138" s="8" t="inlineStr">
+      <c r="D151" s="8" t="inlineStr">
         <is>
           <t>동백, 아르간오일</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="15" customHeight="1">
-      <c r="A139" s="8" t="inlineStr">
+    <row r="152" ht="16" customHeight="1">
+      <c r="A152" s="8" t="inlineStr">
         <is>
           <t>망고버터</t>
         </is>
       </c>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="B152" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C139" s="8" t="inlineStr">
+      <c r="C152" s="8" t="inlineStr">
         <is>
           <t>고보습. 경화제 역할</t>
         </is>
       </c>
-      <c r="D139" s="8" t="inlineStr">
+      <c r="D152" s="8" t="inlineStr">
         <is>
           <t>버터류 등</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="30" customHeight="1">
-      <c r="A140" s="8" t="inlineStr">
+    <row r="153" ht="32" customHeight="1">
+      <c r="A153" s="8" t="inlineStr">
         <is>
           <t>내추럴 바세린</t>
         </is>
       </c>
-      <c r="B140" s="8" t="inlineStr">
+      <c r="B153" s="8" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C140" s="8" t="inlineStr">
+      <c r="C153" s="8" t="inlineStr">
         <is>
           <t>해바라기오일로 만든 젤타입 . 석유계 바세린 대체</t>
         </is>
       </c>
-      <c r="D140" s="8" t="n"/>
-    </row>
-    <row r="141" ht="45" customHeight="1">
-      <c r="A141" s="8" t="inlineStr">
+      <c r="D153" s="8" t="n"/>
+    </row>
+    <row r="154" ht="48" customHeight="1">
+      <c r="A154" s="8" t="inlineStr">
         <is>
           <t>버가못오일(FCF)</t>
         </is>
       </c>
-      <c r="B141" s="8" t="inlineStr">
+      <c r="B154" s="8" t="inlineStr">
         <is>
           <t>30~50방울</t>
         </is>
       </c>
-      <c r="C141" s="8" t="inlineStr">
+      <c r="C154" s="8" t="inlineStr">
         <is>
           <t>감귤류 버가못 껍질오일. / 감광성 무(버갑텐프리)</t>
         </is>
       </c>
-      <c r="D141" s="8" t="inlineStr">
+      <c r="D154" s="8" t="inlineStr">
         <is>
           <t>레몬, 라벤더, 유칼립투스 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+    <row r="155" ht="14" customHeight="1">
+      <c r="A155" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B142" s="6" t="n"/>
-      <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6" t="n"/>
-    </row>
-    <row r="143" ht="360" customHeight="1">
-      <c r="A143" s="9" t="inlineStr">
+      <c r="B155" s="6" t="n"/>
+      <c r="C155" s="6" t="n"/>
+      <c r="D155" s="6" t="n"/>
+    </row>
+    <row r="156" ht="384" customHeight="1">
+      <c r="A156" s="9" t="inlineStr">
         <is>
           <t>겨울철 필수품 바세린.
 피부에 발랐을 때 폐쇄성이 우수합니다.
@@ -6576,22 +6638,22 @@
 내추럴 바세린 깨알 활용팁!</t>
         </is>
       </c>
-      <c r="B143" s="10" t="n"/>
-      <c r="C143" s="10" t="n"/>
-      <c r="D143" s="10" t="n"/>
-    </row>
-    <row r="144" ht="14" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
+      <c r="B156" s="10" t="n"/>
+      <c r="C156" s="10" t="n"/>
+      <c r="D156" s="10" t="n"/>
+    </row>
+    <row r="157" ht="14" customHeight="1">
+      <c r="A157" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B144" s="6" t="n"/>
-      <c r="C144" s="6" t="n"/>
-      <c r="D144" s="6" t="n"/>
-    </row>
-    <row r="145" ht="435" customHeight="1">
-      <c r="A145" s="9" t="inlineStr">
+      <c r="B157" s="6" t="n"/>
+      <c r="C157" s="6" t="n"/>
+      <c r="D157" s="6" t="n"/>
+    </row>
+    <row r="158" ht="384" customHeight="1">
+      <c r="A158" s="9" t="inlineStr">
         <is>
           <t>1.건조할 때 얼굴에 올라온 각질케어
 2.윤기나는 눈썹정돈 및 영양공급
@@ -6616,163 +6678,184 @@
 21.욕실에 놓고 세안 후 바로 사용해 3초 보습
 초정밀 과정
 1. 재료를 계량합니다.
-2. 먼저 으깨듯 섞어주세요.
-3. 잘 녹도록 섞으면서
+2. 먼저 으깨듯 섞어주세요.</t>
+        </is>
+      </c>
+      <c r="B158" s="10" t="n"/>
+      <c r="C158" s="10" t="n"/>
+      <c r="D158" s="10" t="n"/>
+    </row>
+    <row r="159" ht="80" customHeight="1">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>3. 잘 녹도록 섞으면서
 가열해주세요.
 4.원하는 에센셜오일을 넣고 섞어주세요.
 5. 용기에 부어주세요.
 6. 굳으면 완성.</t>
         </is>
       </c>
-      <c r="B145" s="10" t="n"/>
-      <c r="C145" s="10" t="n"/>
-      <c r="D145" s="10" t="n"/>
-    </row>
-    <row r="146" ht="14" customHeight="1">
-      <c r="A146" s="5" t="inlineStr">
+      <c r="B159" s="10" t="n"/>
+      <c r="C159" s="10" t="n"/>
+      <c r="D159" s="10" t="n"/>
+    </row>
+    <row r="160" ht="14" customHeight="1">
+      <c r="A160" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B146" s="6" t="n"/>
-      <c r="C146" s="6" t="n"/>
-      <c r="D146" s="6" t="n"/>
-    </row>
-    <row r="147" ht="256.5" customHeight="1">
-      <c r="A147" s="10" t="n"/>
-      <c r="B147" s="10" t="n"/>
-      <c r="C147" s="10" t="n"/>
-      <c r="D147" s="10" t="n"/>
-    </row>
-    <row r="148" ht="6" customHeight="1"/>
-    <row r="149" ht="22" customHeight="1">
-      <c r="A149" s="1" t="inlineStr">
+      <c r="B160" s="6" t="n"/>
+      <c r="C160" s="6" t="n"/>
+      <c r="D160" s="6" t="n"/>
+    </row>
+    <row r="161" ht="85.5" customHeight="1">
+      <c r="A161" s="10" t="n"/>
+      <c r="B161" s="10" t="n"/>
+      <c r="C161" s="10" t="n"/>
+      <c r="D161" s="10" t="n"/>
+    </row>
+    <row r="162" ht="85.5" customHeight="1">
+      <c r="A162" s="10" t="n"/>
+      <c r="B162" s="10" t="n"/>
+      <c r="C162" s="10" t="n"/>
+      <c r="D162" s="10" t="n"/>
+    </row>
+    <row r="163" ht="85.5" customHeight="1">
+      <c r="A163" s="10" t="n"/>
+      <c r="B163" s="10" t="n"/>
+      <c r="C163" s="10" t="n"/>
+      <c r="D163" s="10" t="n"/>
+    </row>
+    <row r="164" ht="6" customHeight="1"/>
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="1" t="inlineStr">
         <is>
           <t>매끄니 발크림    ↗ 원본</t>
         </is>
       </c>
-      <c r="B149" s="2" t="n"/>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n"/>
-    </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="B165" s="2" t="n"/>
+      <c r="C165" s="2" t="n"/>
+      <c r="D165" s="2" t="n"/>
+    </row>
+    <row r="166" ht="15" customHeight="1">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr">
+      <c r="B166" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C150" s="3" t="inlineStr">
+      <c r="C166" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D150" s="3" t="inlineStr">
+      <c r="D166" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="30" customHeight="1">
-      <c r="A151" s="4" t="inlineStr">
+    <row r="167" ht="32" customHeight="1">
+      <c r="A167" s="4" t="inlineStr">
         <is>
           <t>내추럴 바세린</t>
         </is>
       </c>
-      <c r="B151" s="4" t="inlineStr">
+      <c r="B167" s="4" t="inlineStr">
         <is>
           <t>56.61%</t>
         </is>
       </c>
-      <c r="C151" s="4" t="inlineStr">
+      <c r="C167" s="4" t="inlineStr">
         <is>
           <t>석유계 바세린 대체, 유기농 인증, 해바라기오일 주성분. 젤타입.</t>
         </is>
       </c>
-      <c r="D151" s="4" t="n"/>
-    </row>
-    <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="4" t="inlineStr">
+      <c r="D167" s="4" t="n"/>
+    </row>
+    <row r="168" ht="16" customHeight="1">
+      <c r="A168" s="4" t="inlineStr">
         <is>
           <t>율무추출물</t>
         </is>
       </c>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="B168" s="4" t="inlineStr">
         <is>
           <t>28.3%</t>
         </is>
       </c>
-      <c r="C152" s="4" t="inlineStr">
+      <c r="C168" s="4" t="inlineStr">
         <is>
           <t>피부를 밝고 매끈하게</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr">
+      <c r="D168" s="4" t="inlineStr">
         <is>
           <t>로먼캐모마일워터</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="4" t="inlineStr">
+    <row r="169" ht="32" customHeight="1">
+      <c r="A169" s="4" t="inlineStr">
         <is>
           <t>식물성오일</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B169" s="4" t="inlineStr">
         <is>
           <t>14.15%</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C169" s="4" t="inlineStr">
         <is>
           <t>식물 유래 오일, 보습·에몰리언트</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="D169" s="4" t="inlineStr">
         <is>
           <t>호호바오일, 올리브오일</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="30" customHeight="1">
-      <c r="A154" s="4" t="inlineStr">
+    <row r="170" ht="32" customHeight="1">
+      <c r="A170" s="4" t="inlineStr">
         <is>
           <t>페퍼민트오일</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>0.94%</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
         <is>
           <t>허브의 고농축오일, / 시원, 커피와 시너지효과</t>
         </is>
       </c>
-      <c r="D154" s="4" t="inlineStr">
+      <c r="D170" s="4" t="inlineStr">
         <is>
           <t>티트리(항균), / 스피아민트 등</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="14" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
+    <row r="171" ht="14" customHeight="1">
+      <c r="A171" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B155" s="6" t="n"/>
-      <c r="C155" s="6" t="n"/>
-      <c r="D155" s="6" t="n"/>
-    </row>
-    <row r="156" ht="315" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
+      <c r="B171" s="6" t="n"/>
+      <c r="C171" s="6" t="n"/>
+      <c r="D171" s="6" t="n"/>
+    </row>
+    <row r="172" ht="336" customHeight="1">
+      <c r="A172" s="7" t="inlineStr">
         <is>
           <t>각질 &amp; 갈라짐 한번에 해결!
 만물상표 매끄니 발크림
@@ -6798,18 +6881,18 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="14" customHeight="1">
-      <c r="A157" s="5" t="inlineStr">
+    <row r="173" ht="14" customHeight="1">
+      <c r="A173" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B157" s="6" t="n"/>
-      <c r="C157" s="6" t="n"/>
-      <c r="D157" s="6" t="n"/>
-    </row>
-    <row r="158" ht="330" customHeight="1">
-      <c r="A158" s="7" t="inlineStr">
+      <c r="B173" s="6" t="n"/>
+      <c r="C173" s="6" t="n"/>
+      <c r="D173" s="6" t="n"/>
+    </row>
+    <row r="174" ht="352" customHeight="1">
+      <c r="A174" s="7" t="inlineStr">
         <is>
           <t>1.5스푼 (0.5)
 생략 가능
@@ -6834,172 +6917,173 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="14" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
+    <row r="175" ht="14" customHeight="1">
+      <c r="A175" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B159" s="6" t="n"/>
-      <c r="C159" s="6" t="n"/>
-      <c r="D159" s="6" t="n"/>
-    </row>
-    <row r="160" ht="171" customHeight="1"/>
-    <row r="161" ht="6" customHeight="1"/>
-    <row r="162" ht="22" customHeight="1">
-      <c r="A162" s="1" t="inlineStr">
+      <c r="B175" s="6" t="n"/>
+      <c r="C175" s="6" t="n"/>
+      <c r="D175" s="6" t="n"/>
+    </row>
+    <row r="176" ht="85.5" customHeight="1"/>
+    <row r="177" ht="85.5" customHeight="1"/>
+    <row r="178" ht="6" customHeight="1"/>
+    <row r="179" ht="22" customHeight="1">
+      <c r="A179" s="1" t="inlineStr">
         <is>
           <t>호호바 만능오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B162" s="2" t="n"/>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n"/>
-    </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="3" t="inlineStr">
+      <c r="B179" s="2" t="n"/>
+      <c r="C179" s="2" t="n"/>
+      <c r="D179" s="2" t="n"/>
+    </row>
+    <row r="180" ht="15" customHeight="1">
+      <c r="A180" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B180" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="C180" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D180" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="45" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
+    <row r="181" ht="48" customHeight="1">
+      <c r="A181" s="8" t="inlineStr">
         <is>
           <t>골든 호호바오일</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B181" s="8" t="inlineStr">
         <is>
           <t>50ml</t>
         </is>
       </c>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="C181" s="8" t="inlineStr">
         <is>
           <t>피지성분과 비슷, / 빠른흡수</t>
         </is>
       </c>
-      <c r="D164" s="8" t="inlineStr">
+      <c r="D181" s="8" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="30" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
+    <row r="182" ht="32" customHeight="1">
+      <c r="A182" s="8" t="inlineStr">
         <is>
           <t>브라이트닝 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B182" s="8" t="inlineStr">
         <is>
           <t>5~10방울</t>
         </is>
       </c>
-      <c r="C165" s="8" t="inlineStr">
+      <c r="C182" s="8" t="inlineStr">
         <is>
           <t>네롤리, 일링일랑, 프랑킨센스,버가못FCF 블랜딩</t>
         </is>
       </c>
-      <c r="D165" s="8" t="inlineStr">
+      <c r="D182" s="8" t="inlineStr">
         <is>
           <t>버가못에센셜오일, / 레몬쥬스블렌딩오일</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="30" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
+    <row r="183" ht="32" customHeight="1">
+      <c r="A183" s="8" t="inlineStr">
         <is>
           <t>베베보 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B183" s="8" t="inlineStr">
         <is>
           <t>5~10방울</t>
         </is>
       </c>
-      <c r="C166" s="8" t="inlineStr">
+      <c r="C183" s="8" t="inlineStr">
         <is>
           <t>로먼 캐모마일, 라벤더, 만다린 블렌딩</t>
         </is>
       </c>
-      <c r="D166" s="8" t="inlineStr">
+      <c r="D183" s="8" t="inlineStr">
         <is>
           <t>브라이트닝. / 로즈파워 블렌딩오일</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="30" customHeight="1">
-      <c r="A167" s="8" t="inlineStr">
+    <row r="184" ht="32" customHeight="1">
+      <c r="A184" s="8" t="inlineStr">
         <is>
           <t>로즈파워 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B184" s="8" t="inlineStr">
         <is>
           <t>5~10방울</t>
         </is>
       </c>
-      <c r="C167" s="8" t="inlineStr">
+      <c r="C184" s="8" t="inlineStr">
         <is>
           <t>로즈앱솔루트, 로즈제라늄,로즈우드, 프랑킨센스 블렌딩</t>
         </is>
       </c>
-      <c r="D167" s="8" t="inlineStr">
+      <c r="D184" s="8" t="inlineStr">
         <is>
           <t>브라이트닝 / 블랜딩오일 등</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="45" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
+    <row r="185" ht="48" customHeight="1">
+      <c r="A185" s="8" t="inlineStr">
         <is>
           <t>레몬쥬스 / 블렌딩오일</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B185" s="8" t="inlineStr">
         <is>
           <t>5~10방울</t>
         </is>
       </c>
-      <c r="C168" s="8" t="inlineStr">
+      <c r="C185" s="8" t="inlineStr">
         <is>
           <t>레몬, 레몬글라스, 로즈우드 블렌딩</t>
         </is>
       </c>
-      <c r="D168" s="8" t="inlineStr">
+      <c r="D185" s="8" t="inlineStr">
         <is>
           <t>레몬, 만다린, 그레이프푸룻, 라임, 오렌지에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="14" customHeight="1">
-      <c r="A169" s="5" t="inlineStr">
+    <row r="186" ht="14" customHeight="1">
+      <c r="A186" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B169" s="6" t="n"/>
-      <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6" t="n"/>
-    </row>
-    <row r="170" ht="180" customHeight="1">
-      <c r="A170" s="9" t="inlineStr">
+      <c r="B186" s="6" t="n"/>
+      <c r="C186" s="6" t="n"/>
+      <c r="D186" s="6" t="n"/>
+    </row>
+    <row r="187" ht="192" customHeight="1">
+      <c r="A187" s="9" t="inlineStr">
         <is>
           <t>제일 대중적인 식물성 오일을 꼽으라면 단연
 호호바오일입니다.
@@ -7015,155 +7099,155 @@
 초정밀 과정</t>
         </is>
       </c>
-      <c r="B170" s="10" t="n"/>
-      <c r="C170" s="10" t="n"/>
-      <c r="D170" s="10" t="n"/>
-    </row>
-    <row r="171" ht="14" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="B187" s="10" t="n"/>
+      <c r="C187" s="10" t="n"/>
+      <c r="D187" s="10" t="n"/>
+    </row>
+    <row r="188" ht="14" customHeight="1">
+      <c r="A188" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B171" s="6" t="n"/>
-      <c r="C171" s="6" t="n"/>
-      <c r="D171" s="6" t="n"/>
-    </row>
-    <row r="172" ht="45" customHeight="1">
-      <c r="A172" s="9" t="inlineStr">
+      <c r="B188" s="6" t="n"/>
+      <c r="C188" s="6" t="n"/>
+      <c r="D188" s="6" t="n"/>
+    </row>
+    <row r="189" ht="48" customHeight="1">
+      <c r="A189" s="9" t="inlineStr">
         <is>
           <t>1. 골든호호바오일과
 2. 블렌딩오일을 넣고
 3. 골고루 잘 섞어주면 완성.</t>
         </is>
       </c>
-      <c r="B172" s="10" t="n"/>
-      <c r="C172" s="10" t="n"/>
-      <c r="D172" s="10" t="n"/>
-    </row>
-    <row r="173" ht="14" customHeight="1">
-      <c r="A173" s="5" t="inlineStr">
+      <c r="B189" s="10" t="n"/>
+      <c r="C189" s="10" t="n"/>
+      <c r="D189" s="10" t="n"/>
+    </row>
+    <row r="190" ht="14" customHeight="1">
+      <c r="A190" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B173" s="6" t="n"/>
-      <c r="C173" s="6" t="n"/>
-      <c r="D173" s="6" t="n"/>
-    </row>
-    <row r="174" ht="85.5" customHeight="1">
-      <c r="A174" s="10" t="n"/>
-      <c r="B174" s="10" t="n"/>
-      <c r="C174" s="10" t="n"/>
-      <c r="D174" s="10" t="n"/>
-    </row>
-    <row r="175" ht="6" customHeight="1"/>
-    <row r="176" ht="22" customHeight="1">
-      <c r="A176" s="1" t="inlineStr">
+      <c r="B190" s="6" t="n"/>
+      <c r="C190" s="6" t="n"/>
+      <c r="D190" s="6" t="n"/>
+    </row>
+    <row r="191" ht="85.5" customHeight="1">
+      <c r="A191" s="10" t="n"/>
+      <c r="B191" s="10" t="n"/>
+      <c r="C191" s="10" t="n"/>
+      <c r="D191" s="10" t="n"/>
+    </row>
+    <row r="192" ht="6" customHeight="1"/>
+    <row r="193" ht="22" customHeight="1">
+      <c r="A193" s="1" t="inlineStr">
         <is>
           <t>코코넛 립에센스(스무디)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B176" s="2" t="n"/>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n"/>
-    </row>
-    <row r="177" ht="15" customHeight="1">
-      <c r="A177" s="3" t="inlineStr">
+      <c r="B193" s="2" t="n"/>
+      <c r="C193" s="2" t="n"/>
+      <c r="D193" s="2" t="n"/>
+    </row>
+    <row r="194" ht="15" customHeight="1">
+      <c r="A194" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B194" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr">
+      <c r="C194" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="D194" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="45" customHeight="1">
-      <c r="A178" s="4" t="inlineStr">
+    <row r="195" ht="48" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
         <is>
           <t>엑스트라 버진 코코넛오일</t>
         </is>
       </c>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="B195" s="4" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr">
+      <c r="C195" s="4" t="inlineStr">
         <is>
           <t>모유에 들어있는 라우릭산이 / 자연식품 중에서는 가장 많이 들어있음. 달콤한 향</t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="D195" s="4" t="inlineStr">
         <is>
           <t>포도씨오일, 해바라기오일 등</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="15" customHeight="1">
-      <c r="A179" s="4" t="inlineStr">
+    <row r="196" ht="16" customHeight="1">
+      <c r="A196" s="4" t="inlineStr">
         <is>
           <t>유기농코포아수버터</t>
         </is>
       </c>
-      <c r="B179" s="4" t="inlineStr">
+      <c r="B196" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C179" s="4" t="inlineStr">
+      <c r="C196" s="4" t="inlineStr">
         <is>
           <t>식물성버터, 고보습</t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
+      <c r="D196" s="4" t="inlineStr">
         <is>
           <t>시어버터</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="30" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
+    <row r="197" ht="32" customHeight="1">
+      <c r="A197" s="4" t="inlineStr">
         <is>
           <t>내추럴 바세린</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="B197" s="4" t="inlineStr">
         <is>
           <t>21g</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C197" s="4" t="inlineStr">
         <is>
           <t>석유계 바세린 대체, / 해바라기오일 주성분. 젤타입.</t>
         </is>
       </c>
-      <c r="D180" s="4" t="n"/>
-    </row>
-    <row r="181" ht="14" customHeight="1">
-      <c r="A181" s="5" t="inlineStr">
+      <c r="D197" s="4" t="n"/>
+    </row>
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B181" s="6" t="n"/>
-      <c r="C181" s="6" t="n"/>
-      <c r="D181" s="6" t="n"/>
-    </row>
-    <row r="182" ht="285" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
+      <c r="B198" s="6" t="n"/>
+      <c r="C198" s="6" t="n"/>
+      <c r="D198" s="6" t="n"/>
+    </row>
+    <row r="199" ht="304" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -7187,18 +7271,18 @@
         </is>
       </c>
     </row>
-    <row r="183" ht="14" customHeight="1">
-      <c r="A183" s="5" t="inlineStr">
+    <row r="200" ht="14" customHeight="1">
+      <c r="A200" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B183" s="6" t="n"/>
-      <c r="C183" s="6" t="n"/>
-      <c r="D183" s="6" t="n"/>
-    </row>
-    <row r="184" ht="90" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
+      <c r="B200" s="6" t="n"/>
+      <c r="C200" s="6" t="n"/>
+      <c r="D200" s="6" t="n"/>
+    </row>
+    <row r="201" ht="96" customHeight="1">
+      <c r="A201" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 |
@@ -7209,106 +7293,107 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="14" customHeight="1">
-      <c r="A185" s="5" t="inlineStr">
+    <row r="202" ht="14" customHeight="1">
+      <c r="A202" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="n"/>
-      <c r="D185" s="6" t="n"/>
-    </row>
-    <row r="186" ht="171" customHeight="1"/>
-    <row r="187" ht="6" customHeight="1"/>
-    <row r="188" ht="22" customHeight="1">
-      <c r="A188" s="1" t="inlineStr">
+      <c r="B202" s="6" t="n"/>
+      <c r="C202" s="6" t="n"/>
+      <c r="D202" s="6" t="n"/>
+    </row>
+    <row r="203" ht="85.5" customHeight="1"/>
+    <row r="204" ht="85.5" customHeight="1"/>
+    <row r="205" ht="6" customHeight="1"/>
+    <row r="206" ht="22" customHeight="1">
+      <c r="A206" s="1" t="inlineStr">
         <is>
           <t>버가못 바디오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B188" s="2" t="n"/>
-      <c r="C188" s="2" t="n"/>
-      <c r="D188" s="2" t="n"/>
-    </row>
-    <row r="189" ht="15" customHeight="1">
-      <c r="A189" s="3" t="inlineStr">
+      <c r="B206" s="2" t="n"/>
+      <c r="C206" s="2" t="n"/>
+      <c r="D206" s="2" t="n"/>
+    </row>
+    <row r="207" ht="15" customHeight="1">
+      <c r="A207" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B189" s="3" t="inlineStr">
+      <c r="B207" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C189" s="3" t="inlineStr">
+      <c r="C207" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D189" s="3" t="inlineStr">
+      <c r="D207" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="190" ht="30" customHeight="1">
-      <c r="A190" s="8" t="inlineStr">
+    <row r="208" ht="32" customHeight="1">
+      <c r="A208" s="8" t="inlineStr">
         <is>
           <t>골든 호호바오일</t>
         </is>
       </c>
-      <c r="B190" s="8" t="inlineStr">
+      <c r="B208" s="8" t="inlineStr">
         <is>
           <t>100ml</t>
         </is>
       </c>
-      <c r="C190" s="8" t="inlineStr">
+      <c r="C208" s="8" t="inlineStr">
         <is>
           <t>콩과식물, 사람피지와 비슷한 구조, 사용감이 가볍고 흡수력이 탁월</t>
         </is>
       </c>
-      <c r="D190" s="8" t="inlineStr">
+      <c r="D208" s="8" t="inlineStr">
         <is>
           <t>마카다미아넛오일, 아몬드, 동백오일 등</t>
         </is>
       </c>
     </row>
-    <row r="191" ht="45" customHeight="1">
-      <c r="A191" s="8" t="inlineStr">
+    <row r="209" ht="48" customHeight="1">
+      <c r="A209" s="8" t="inlineStr">
         <is>
           <t>버가못에센셜오일</t>
         </is>
       </c>
-      <c r="B191" s="8" t="inlineStr">
+      <c r="B209" s="8" t="inlineStr">
         <is>
           <t>20방울(1%) / ~60방울(3%)</t>
         </is>
       </c>
-      <c r="C191" s="8" t="inlineStr">
+      <c r="C209" s="8" t="inlineStr">
         <is>
           <t>상큼하고 신선한 향, 버가못껍질을 냉압착 추출, 소화</t>
         </is>
       </c>
-      <c r="D191" s="8" t="inlineStr">
+      <c r="D209" s="8" t="inlineStr">
         <is>
           <t>라벤더, 오렌지 등 원하는 에센셜오일 동량</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="14" customHeight="1">
-      <c r="A192" s="5" t="inlineStr">
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B192" s="6" t="n"/>
-      <c r="C192" s="6" t="n"/>
-      <c r="D192" s="6" t="n"/>
-    </row>
-    <row r="193" ht="375" customHeight="1">
-      <c r="A193" s="9" t="inlineStr">
+      <c r="B210" s="6" t="n"/>
+      <c r="C210" s="6" t="n"/>
+      <c r="D210" s="6" t="n"/>
+    </row>
+    <row r="211" ht="384" customHeight="1">
+      <c r="A211" s="9" t="inlineStr">
         <is>
           <t>상큼하고 촉촉하게 온가족이 사용할 수 있는~
 버가못바디오일
@@ -7332,26 +7417,35 @@
 사람피지성분과 비슷한 골덴호호바오일이 수분막을 형성하여 산뜻하면서
 촉촉함이 오래가게 만들어줍니다.
 버가못은 상큼하면서 신선한 감귤향입니다.
-또 감귤류 에센셜오일 중에서는 고급스러운 향이기도 하구요.
-베이스오일에 원하는 에센셜오일을 떨어뜨려 흔들어 골고루 섞이기만 하면 된답니다.</t>
-        </is>
-      </c>
-      <c r="B193" s="10" t="n"/>
-      <c r="C193" s="10" t="n"/>
-      <c r="D193" s="10" t="n"/>
-    </row>
-    <row r="194" ht="14" customHeight="1">
-      <c r="A194" s="5" t="inlineStr">
+또 감귤류 에센셜오일 중에서는 고급스러운 향이기도 하구요.</t>
+        </is>
+      </c>
+      <c r="B211" s="10" t="n"/>
+      <c r="C211" s="10" t="n"/>
+      <c r="D211" s="10" t="n"/>
+    </row>
+    <row r="212" ht="16" customHeight="1">
+      <c r="A212" s="9" t="inlineStr">
+        <is>
+          <t>베이스오일에 원하는 에센셜오일을 떨어뜨려 흔들어 골고루 섞이기만 하면 된답니다.</t>
+        </is>
+      </c>
+      <c r="B212" s="10" t="n"/>
+      <c r="C212" s="10" t="n"/>
+      <c r="D212" s="10" t="n"/>
+    </row>
+    <row r="213" ht="14" customHeight="1">
+      <c r="A213" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B194" s="6" t="n"/>
-      <c r="C194" s="6" t="n"/>
-      <c r="D194" s="6" t="n"/>
-    </row>
-    <row r="195" ht="75" customHeight="1">
-      <c r="A195" s="9" t="inlineStr">
+      <c r="B213" s="6" t="n"/>
+      <c r="C213" s="6" t="n"/>
+      <c r="D213" s="6" t="n"/>
+    </row>
+    <row r="214" ht="80" customHeight="1">
+      <c r="A214" s="9" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 오일을 계량하고
@@ -7360,181 +7454,181 @@
 4. 용기에 붓기</t>
         </is>
       </c>
-      <c r="B195" s="10" t="n"/>
-      <c r="C195" s="10" t="n"/>
-      <c r="D195" s="10" t="n"/>
-    </row>
-    <row r="196" ht="14" customHeight="1">
-      <c r="A196" s="5" t="inlineStr">
+      <c r="B214" s="10" t="n"/>
+      <c r="C214" s="10" t="n"/>
+      <c r="D214" s="10" t="n"/>
+    </row>
+    <row r="215" ht="14" customHeight="1">
+      <c r="A215" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B196" s="6" t="n"/>
-      <c r="C196" s="6" t="n"/>
-      <c r="D196" s="6" t="n"/>
-    </row>
-    <row r="197" ht="85.5" customHeight="1">
-      <c r="A197" s="10" t="n"/>
-      <c r="B197" s="10" t="n"/>
-      <c r="C197" s="10" t="n"/>
-      <c r="D197" s="10" t="n"/>
-    </row>
-    <row r="198" ht="6" customHeight="1"/>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="1" t="inlineStr">
+      <c r="B215" s="6" t="n"/>
+      <c r="C215" s="6" t="n"/>
+      <c r="D215" s="6" t="n"/>
+    </row>
+    <row r="216" ht="85.5" customHeight="1">
+      <c r="A216" s="10" t="n"/>
+      <c r="B216" s="10" t="n"/>
+      <c r="C216" s="10" t="n"/>
+      <c r="D216" s="10" t="n"/>
+    </row>
+    <row r="217" ht="6" customHeight="1"/>
+    <row r="218" ht="22" customHeight="1">
+      <c r="A218" s="1" t="inlineStr">
         <is>
           <t>스쿠알란 바디오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B199" s="2" t="n"/>
-      <c r="C199" s="2" t="n"/>
-      <c r="D199" s="2" t="n"/>
-    </row>
-    <row r="200" ht="15" customHeight="1">
-      <c r="A200" s="3" t="inlineStr">
+      <c r="B218" s="2" t="n"/>
+      <c r="C218" s="2" t="n"/>
+      <c r="D218" s="2" t="n"/>
+    </row>
+    <row r="219" ht="15" customHeight="1">
+      <c r="A219" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B200" s="3" t="inlineStr">
+      <c r="B219" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C200" s="3" t="inlineStr">
+      <c r="C219" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D200" s="3" t="inlineStr">
+      <c r="D219" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="45" customHeight="1">
-      <c r="A201" s="4" t="inlineStr">
+    <row r="220" ht="48" customHeight="1">
+      <c r="A220" s="4" t="inlineStr">
         <is>
           <t>유기농 스쿠알란</t>
         </is>
       </c>
-      <c r="B201" s="4" t="inlineStr">
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>45g</t>
         </is>
       </c>
-      <c r="C201" s="4" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr">
         <is>
           <t>피지의 약 12%를 구성하는 성분, / 스쿠알렌을 수소첨가하여 안정화한 성분</t>
         </is>
       </c>
-      <c r="D201" s="4" t="inlineStr">
+      <c r="D220" s="4" t="inlineStr">
         <is>
           <t>녹차씨오일</t>
         </is>
       </c>
     </row>
-    <row r="202" ht="60" customHeight="1">
-      <c r="A202" s="4" t="inlineStr">
+    <row r="221" ht="64" customHeight="1">
+      <c r="A221" s="4" t="inlineStr">
         <is>
           <t>카프릴릭 카프릭트리글리세라이드 (MCT)</t>
         </is>
       </c>
-      <c r="B202" s="4" t="inlineStr">
+      <c r="B221" s="4" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C202" s="4" t="inlineStr">
+      <c r="C221" s="4" t="inlineStr">
         <is>
           <t>코코넛, 팜 등에서 유래, / 카프릴릭산(C8)와 카프릭산(C10)을 / 글리세린과 합성시켜 만든 원료, / 가볍고 빠른 흡수력</t>
         </is>
       </c>
-      <c r="D202" s="4" t="inlineStr">
+      <c r="D221" s="4" t="inlineStr">
         <is>
           <t>유기농 세티올 / 에스터오일</t>
         </is>
       </c>
     </row>
-    <row r="203" ht="15" customHeight="1">
-      <c r="A203" s="4" t="inlineStr">
+    <row r="222" ht="16" customHeight="1">
+      <c r="A222" s="4" t="inlineStr">
         <is>
           <t>호호바오일(골든)</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
+      <c r="B222" s="4" t="inlineStr">
         <is>
           <t>19.2g</t>
         </is>
       </c>
-      <c r="C203" s="4" t="inlineStr">
+      <c r="C222" s="4" t="inlineStr">
         <is>
           <t>피지성분과 비슷, / 빠른흡수</t>
         </is>
       </c>
-      <c r="D203" s="4" t="inlineStr">
+      <c r="D222" s="4" t="inlineStr">
         <is>
           <t>동백오일, 아르간오일</t>
         </is>
       </c>
     </row>
-    <row r="204" ht="30" customHeight="1">
-      <c r="A204" s="4" t="inlineStr">
+    <row r="223" ht="32" customHeight="1">
+      <c r="A223" s="4" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B204" s="4" t="inlineStr">
+      <c r="B223" s="4" t="inlineStr">
         <is>
           <t>0.5g(10방울)</t>
         </is>
       </c>
-      <c r="C204" s="4" t="inlineStr">
+      <c r="C223" s="4" t="inlineStr">
         <is>
           <t>산화방지</t>
         </is>
       </c>
-      <c r="D204" s="4" t="inlineStr">
+      <c r="D223" s="4" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="15" customHeight="1">
-      <c r="A205" s="4" t="inlineStr">
+    <row r="224" ht="16" customHeight="1">
+      <c r="A224" s="4" t="inlineStr">
         <is>
           <t>버가못FCF</t>
         </is>
       </c>
-      <c r="B205" s="4" t="inlineStr">
+      <c r="B224" s="4" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C205" s="4" t="inlineStr">
+      <c r="C224" s="4" t="inlineStr">
         <is>
           <t>감귤류, 피부진정, / 광독성 없음</t>
         </is>
       </c>
-      <c r="D205" s="4" t="inlineStr">
+      <c r="D224" s="4" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="14" customHeight="1">
-      <c r="A206" s="5" t="inlineStr">
+    <row r="225" ht="14" customHeight="1">
+      <c r="A225" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B206" s="6" t="n"/>
-      <c r="C206" s="6" t="n"/>
-      <c r="D206" s="6" t="n"/>
-    </row>
-    <row r="207" ht="255" customHeight="1">
-      <c r="A207" s="7" t="inlineStr">
+      <c r="B225" s="6" t="n"/>
+      <c r="C225" s="6" t="n"/>
+      <c r="D225" s="6" t="n"/>
+    </row>
+    <row r="226" ht="272" customHeight="1">
+      <c r="A226" s="7" t="inlineStr">
         <is>
           <t>샤워 후 촉촉함 그대로, 끈적임 없는!
 스쿠알란 바디오일
@@ -7556,18 +7650,18 @@
         </is>
       </c>
     </row>
-    <row r="208" ht="14" customHeight="1">
-      <c r="A208" s="5" t="inlineStr">
+    <row r="227" ht="14" customHeight="1">
+      <c r="A227" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B208" s="6" t="n"/>
-      <c r="C208" s="6" t="n"/>
-      <c r="D208" s="6" t="n"/>
-    </row>
-    <row r="209" ht="75" customHeight="1">
-      <c r="A209" s="7" t="inlineStr">
+      <c r="B227" s="6" t="n"/>
+      <c r="C227" s="6" t="n"/>
+      <c r="D227" s="6" t="n"/>
+    </row>
+    <row r="228" ht="80" customHeight="1">
+      <c r="A228" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 150ml 용기에 모든 재료를 계량해주세요.
@@ -7577,216 +7671,216 @@
         </is>
       </c>
     </row>
-    <row r="210" ht="14" customHeight="1">
-      <c r="A210" s="5" t="inlineStr">
+    <row r="229" ht="14" customHeight="1">
+      <c r="A229" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B210" s="6" t="n"/>
-      <c r="C210" s="6" t="n"/>
-      <c r="D210" s="6" t="n"/>
-    </row>
-    <row r="211" ht="85.5" customHeight="1"/>
-    <row r="212" ht="6" customHeight="1"/>
-    <row r="213" ht="22" customHeight="1">
-      <c r="A213" s="1" t="inlineStr">
+      <c r="B229" s="6" t="n"/>
+      <c r="C229" s="6" t="n"/>
+      <c r="D229" s="6" t="n"/>
+    </row>
+    <row r="230" ht="85.5" customHeight="1"/>
+    <row r="231" ht="6" customHeight="1"/>
+    <row r="232" ht="22" customHeight="1">
+      <c r="A232" s="1" t="inlineStr">
         <is>
           <t>스쿠알란 슬로우 앰플(오일)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B213" s="2" t="n"/>
-      <c r="C213" s="2" t="n"/>
-      <c r="D213" s="2" t="n"/>
-    </row>
-    <row r="214" ht="15" customHeight="1">
-      <c r="A214" s="3" t="inlineStr">
+      <c r="B232" s="2" t="n"/>
+      <c r="C232" s="2" t="n"/>
+      <c r="D232" s="2" t="n"/>
+    </row>
+    <row r="233" ht="15" customHeight="1">
+      <c r="A233" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B214" s="3" t="inlineStr">
+      <c r="B233" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C214" s="3" t="inlineStr">
+      <c r="C233" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D214" s="3" t="inlineStr">
+      <c r="D233" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="215" ht="45" customHeight="1">
-      <c r="A215" s="8" t="inlineStr">
+    <row r="234" ht="48" customHeight="1">
+      <c r="A234" s="8" t="inlineStr">
         <is>
           <t>유기농 스쿠알란</t>
         </is>
       </c>
-      <c r="B215" s="8" t="inlineStr">
+      <c r="B234" s="8" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C215" s="8" t="inlineStr">
+      <c r="C234" s="8" t="inlineStr">
         <is>
           <t>피지의 약 12%를 구성하는 성분, / 스쿠알렌을 수소첨가하여 안정화한 성분</t>
         </is>
       </c>
-      <c r="D215" s="8" t="inlineStr">
+      <c r="D234" s="8" t="inlineStr">
         <is>
           <t>세라마이드(지용성)</t>
         </is>
       </c>
     </row>
-    <row r="216" ht="60" customHeight="1">
-      <c r="A216" s="8" t="inlineStr">
+    <row r="235" ht="64" customHeight="1">
+      <c r="A235" s="8" t="inlineStr">
         <is>
           <t>카프릴릭 카프릭트리글리세라이드 (MCT)</t>
         </is>
       </c>
-      <c r="B216" s="8" t="inlineStr">
+      <c r="B235" s="8" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C216" s="8" t="inlineStr">
+      <c r="C235" s="8" t="inlineStr">
         <is>
           <t>코코넛, 팜 등에서 유래, / 카프릴릭산(C8)와 카프릭산(C10)을 / 글리세린과 합성시켜 만든 원료, / 가볍고 빠른 흡수력</t>
         </is>
       </c>
-      <c r="D216" s="8" t="inlineStr">
+      <c r="D235" s="8" t="inlineStr">
         <is>
           <t>유기농 세티올 / 에스터오일</t>
         </is>
       </c>
     </row>
-    <row r="217" ht="45" customHeight="1">
-      <c r="A217" s="8" t="inlineStr">
+    <row r="236" ht="64" customHeight="1">
+      <c r="A236" s="8" t="inlineStr">
         <is>
           <t>보르피린</t>
         </is>
       </c>
-      <c r="B217" s="8" t="inlineStr">
+      <c r="B236" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C217" s="8" t="inlineStr">
+      <c r="C236" s="8" t="inlineStr">
         <is>
           <t>지모추출, 지방증식 볼륨업</t>
         </is>
       </c>
-      <c r="D217" s="8" t="inlineStr">
+      <c r="D236" s="8" t="inlineStr">
         <is>
           <t>10 g(10%)을 원한다면 로즈워터를 5g 줄여서 40g이 되도록 해주세요.</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="45" customHeight="1">
-      <c r="A218" s="8" t="inlineStr">
+    <row r="237" ht="48" customHeight="1">
+      <c r="A237" s="8" t="inlineStr">
         <is>
           <t>(정제) 호호바오일</t>
         </is>
       </c>
-      <c r="B218" s="8" t="inlineStr">
+      <c r="B237" s="8" t="inlineStr">
         <is>
           <t>19g</t>
         </is>
       </c>
-      <c r="C218" s="8" t="inlineStr">
+      <c r="C237" s="8" t="inlineStr">
         <is>
           <t>피지성분과 비슷, 빠른 흡수 / ※ 호호바오일(골든) 사용 시 완성품이 노란빛을 띨 수 있습니다.</t>
         </is>
       </c>
-      <c r="D218" s="8" t="inlineStr">
+      <c r="D237" s="8" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="15" customHeight="1">
-      <c r="A219" s="8" t="inlineStr">
+    <row r="238" ht="16" customHeight="1">
+      <c r="A238" s="8" t="inlineStr">
         <is>
           <t>알파비사보롤</t>
         </is>
       </c>
-      <c r="B219" s="8" t="inlineStr">
+      <c r="B238" s="8" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C219" s="8" t="inlineStr">
+      <c r="C238" s="8" t="inlineStr">
         <is>
           <t>식약처 미백고시 원료</t>
         </is>
       </c>
-      <c r="D219" s="8" t="inlineStr">
+      <c r="D238" s="8" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="45" customHeight="1">
-      <c r="A220" s="8" t="inlineStr">
+    <row r="239" ht="48" customHeight="1">
+      <c r="A239" s="8" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B220" s="8" t="inlineStr">
+      <c r="B239" s="8" t="inlineStr">
         <is>
           <t>0.5g</t>
         </is>
       </c>
-      <c r="C220" s="8" t="inlineStr">
+      <c r="C239" s="8" t="inlineStr">
         <is>
           <t>산화방지</t>
         </is>
       </c>
-      <c r="D220" s="8" t="inlineStr">
+      <c r="D239" s="8" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="30" customHeight="1">
-      <c r="A221" s="8" t="inlineStr">
+    <row r="240" ht="32" customHeight="1">
+      <c r="A240" s="8" t="inlineStr">
         <is>
           <t>로즈파워 블렌딩오일</t>
         </is>
       </c>
-      <c r="B221" s="8" t="inlineStr">
+      <c r="B240" s="8" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C221" s="8" t="inlineStr">
+      <c r="C240" s="8" t="inlineStr">
         <is>
           <t>로즈앱솔루트, 로즈제라늄, / 로즈우드, 프랑킨센스 블렌딩오일</t>
         </is>
       </c>
-      <c r="D221" s="8" t="inlineStr">
+      <c r="D240" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="14" customHeight="1">
-      <c r="A222" s="5" t="inlineStr">
+    <row r="241" ht="14" customHeight="1">
+      <c r="A241" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B222" s="6" t="n"/>
-      <c r="C222" s="6" t="n"/>
-      <c r="D222" s="6" t="n"/>
-    </row>
-    <row r="223" ht="510" customHeight="1">
-      <c r="A223" s="9" t="inlineStr">
+      <c r="B241" s="6" t="n"/>
+      <c r="C241" s="6" t="n"/>
+      <c r="D241" s="6" t="n"/>
+    </row>
+    <row r="242" ht="384" customHeight="1">
+      <c r="A242" s="9" t="inlineStr">
         <is>
           <t>꺼진 볼륨 · 윤광 집중 솔루션
 스쿠알란 슬로우 앰플(오일)
@@ -7811,8 +7905,17 @@
 ▷이마 주름 케어
 이마에 오일 바른 뒤, 검지와 중지로 원을 그리거나
 촘촘한 'X'자 모양을 그리며 근육을 부드럽게 풀어주세요.
-▷눈가 주름 케어
-눈가 주름을 예방하고 개선하려면 피부에 마찰을 주지 않는 것이 핵심입니다.
+▷눈가 주름 케어</t>
+        </is>
+      </c>
+      <c r="B242" s="10" t="n"/>
+      <c r="C242" s="10" t="n"/>
+      <c r="D242" s="10" t="n"/>
+    </row>
+    <row r="243" ht="160" customHeight="1">
+      <c r="A243" s="9" t="inlineStr">
+        <is>
+          <t>눈가 주름을 예방하고 개선하려면 피부에 마찰을 주지 않는 것이 핵심입니다.
 오일을 바른 후, 가장 힘이 약한 약지를 이용해 혈점을 가볍게 누르고
 근육을 부드럽게 풀어주세요
 ▷팔자 주름 케어
@@ -7824,22 +7927,22 @@
 건조한 손/끝과 손톱 부위에 발라 촉촉하게 만들어주세요.</t>
         </is>
       </c>
-      <c r="B223" s="10" t="n"/>
-      <c r="C223" s="10" t="n"/>
-      <c r="D223" s="10" t="n"/>
-    </row>
-    <row r="224" ht="14" customHeight="1">
-      <c r="A224" s="5" t="inlineStr">
+      <c r="B243" s="10" t="n"/>
+      <c r="C243" s="10" t="n"/>
+      <c r="D243" s="10" t="n"/>
+    </row>
+    <row r="244" ht="14" customHeight="1">
+      <c r="A244" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B224" s="6" t="n"/>
-      <c r="C224" s="6" t="n"/>
-      <c r="D224" s="6" t="n"/>
-    </row>
-    <row r="225" ht="75" customHeight="1">
-      <c r="A225" s="9" t="inlineStr">
+      <c r="B244" s="6" t="n"/>
+      <c r="C244" s="6" t="n"/>
+      <c r="D244" s="6" t="n"/>
+    </row>
+    <row r="245" ht="80" customHeight="1">
+      <c r="A245" s="9" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 150ml 용기에 모든 재료를 계량해주세요.
@@ -7848,137 +7951,137 @@
 ※150ml에 내용물을 담으면 가득 차지 않습니다.</t>
         </is>
       </c>
-      <c r="B225" s="10" t="n"/>
-      <c r="C225" s="10" t="n"/>
-      <c r="D225" s="10" t="n"/>
-    </row>
-    <row r="226" ht="14" customHeight="1">
-      <c r="A226" s="5" t="inlineStr">
+      <c r="B245" s="10" t="n"/>
+      <c r="C245" s="10" t="n"/>
+      <c r="D245" s="10" t="n"/>
+    </row>
+    <row r="246" ht="14" customHeight="1">
+      <c r="A246" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B226" s="6" t="n"/>
-      <c r="C226" s="6" t="n"/>
-      <c r="D226" s="6" t="n"/>
-    </row>
-    <row r="227" ht="85.5" customHeight="1">
-      <c r="A227" s="10" t="n"/>
-      <c r="B227" s="10" t="n"/>
-      <c r="C227" s="10" t="n"/>
-      <c r="D227" s="10" t="n"/>
-    </row>
-    <row r="228" ht="6" customHeight="1"/>
-    <row r="229" ht="22" customHeight="1">
-      <c r="A229" s="1" t="inlineStr">
+      <c r="B246" s="6" t="n"/>
+      <c r="C246" s="6" t="n"/>
+      <c r="D246" s="6" t="n"/>
+    </row>
+    <row r="247" ht="85.5" customHeight="1">
+      <c r="A247" s="10" t="n"/>
+      <c r="B247" s="10" t="n"/>
+      <c r="C247" s="10" t="n"/>
+      <c r="D247" s="10" t="n"/>
+    </row>
+    <row r="248" ht="6" customHeight="1"/>
+    <row r="249" ht="22" customHeight="1">
+      <c r="A249" s="1" t="inlineStr">
         <is>
           <t>아르간페이셜오일    [오일류]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B229" s="2" t="n"/>
-      <c r="C229" s="2" t="n"/>
-      <c r="D229" s="2" t="n"/>
-    </row>
-    <row r="230" ht="15" customHeight="1">
-      <c r="A230" s="3" t="inlineStr">
+      <c r="B249" s="2" t="n"/>
+      <c r="C249" s="2" t="n"/>
+      <c r="D249" s="2" t="n"/>
+    </row>
+    <row r="250" ht="15" customHeight="1">
+      <c r="A250" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B230" s="3" t="inlineStr">
+      <c r="B250" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C230" s="3" t="inlineStr">
+      <c r="C250" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D230" s="3" t="inlineStr">
+      <c r="D250" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="231" ht="60" customHeight="1">
-      <c r="A231" s="4" t="inlineStr">
+    <row r="251" ht="64" customHeight="1">
+      <c r="A251" s="4" t="inlineStr">
         <is>
           <t>아르간오일</t>
         </is>
       </c>
-      <c r="B231" s="4" t="inlineStr">
+      <c r="B251" s="4" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C231" s="4" t="inlineStr">
+      <c r="C251" s="4" t="inlineStr">
         <is>
           <t>모로코에서만 나는 아르간나무열매에서 채취, 토코페롤, 폴리페놀, 스쿠알렌 등 다량함유, 노화, 민감피부등 사용</t>
         </is>
       </c>
-      <c r="D231" s="4" t="inlineStr">
+      <c r="D251" s="4" t="inlineStr">
         <is>
           <t>로즈힙오일</t>
         </is>
       </c>
     </row>
-    <row r="232" ht="30" customHeight="1">
-      <c r="A232" s="4" t="inlineStr">
+    <row r="252" ht="32" customHeight="1">
+      <c r="A252" s="4" t="inlineStr">
         <is>
           <t>로즈힙오일</t>
         </is>
       </c>
-      <c r="B232" s="4" t="inlineStr">
+      <c r="B252" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C232" s="4" t="inlineStr">
+      <c r="C252" s="4" t="inlineStr">
         <is>
           <t>들장미열매 압착 혹은 용매추출, 주름, 노화피부관리에사용함</t>
         </is>
       </c>
-      <c r="D232" s="4" t="inlineStr">
+      <c r="D252" s="4" t="inlineStr">
         <is>
           <t>마카다미아넛, 아보카도</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="45" customHeight="1">
-      <c r="A233" s="4" t="inlineStr">
+    <row r="253" ht="48" customHeight="1">
+      <c r="A253" s="4" t="inlineStr">
         <is>
           <t>네롤리에센셜오일</t>
         </is>
       </c>
-      <c r="B233" s="4" t="inlineStr">
+      <c r="B253" s="4" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C233" s="4" t="inlineStr">
+      <c r="C253" s="4" t="inlineStr">
         <is>
           <t>오렌지꽃에서 추출, 고농축, 최고급향, 민감, 노화, 어린이사용가능, 아로마테라피효과</t>
         </is>
       </c>
-      <c r="D233" s="4" t="inlineStr">
+      <c r="D253" s="4" t="inlineStr">
         <is>
           <t>로즈우드, 로즈, 자스민</t>
         </is>
       </c>
     </row>
-    <row r="234" ht="14" customHeight="1">
-      <c r="A234" s="5" t="inlineStr">
+    <row r="254" ht="14" customHeight="1">
+      <c r="A254" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B234" s="6" t="n"/>
-      <c r="C234" s="6" t="n"/>
-      <c r="D234" s="6" t="n"/>
-    </row>
-    <row r="235" ht="165" customHeight="1">
-      <c r="A235" s="7" t="inlineStr">
+      <c r="B254" s="6" t="n"/>
+      <c r="C254" s="6" t="n"/>
+      <c r="D254" s="6" t="n"/>
+    </row>
+    <row r="255" ht="176" customHeight="1">
+      <c r="A255" s="7" t="inlineStr">
         <is>
           <t>수분에 얇은 막을 입혀주는 3초오일 보습법
 세안직후 피부의 수분이 급속도로 빼앗기기 때문에 3초안에 보습을 해줘야 피부의 수분함량이 많아져 촉촉한 피부를 유지할수 있게 되는 원리입니다. 피부의 보습 최적의 상태는 물과 피지의 비율이 7:3 일때라고 하는데 다양한 오일을 피부타입에 맞게 활용하셔도 되지만 보습과 재생을 동시에 도와줄 수 있는 아르간오일과 로즈힙오일을 이용한 럭셔리 페이셜오일을 소개합니다.
@@ -7986,18 +8089,18 @@
         </is>
       </c>
     </row>
-    <row r="236" ht="14" customHeight="1">
-      <c r="A236" s="5" t="inlineStr">
+    <row r="256" ht="14" customHeight="1">
+      <c r="A256" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B236" s="6" t="n"/>
-      <c r="C236" s="6" t="n"/>
-      <c r="D236" s="6" t="n"/>
-    </row>
-    <row r="237" ht="60" customHeight="1">
-      <c r="A237" s="7" t="inlineStr">
+      <c r="B256" s="6" t="n"/>
+      <c r="C256" s="6" t="n"/>
+      <c r="D256" s="6" t="n"/>
+    </row>
+    <row r="257" ht="64" customHeight="1">
+      <c r="A257" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 오일을 계량한다
@@ -8006,106 +8109,106 @@
         </is>
       </c>
     </row>
-    <row r="238" ht="14" customHeight="1">
-      <c r="A238" s="5" t="inlineStr">
+    <row r="258" ht="14" customHeight="1">
+      <c r="A258" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B238" s="6" t="n"/>
-      <c r="C238" s="6" t="n"/>
-      <c r="D238" s="6" t="n"/>
-    </row>
-    <row r="239" ht="85.5" customHeight="1"/>
-    <row r="240" ht="6" customHeight="1"/>
-    <row r="241" ht="22" customHeight="1">
-      <c r="A241" s="1" t="inlineStr">
+      <c r="B258" s="6" t="n"/>
+      <c r="C258" s="6" t="n"/>
+      <c r="D258" s="6" t="n"/>
+    </row>
+    <row r="259" ht="85.5" customHeight="1"/>
+    <row r="260" ht="6" customHeight="1"/>
+    <row r="261" ht="22" customHeight="1">
+      <c r="A261" s="1" t="inlineStr">
         <is>
           <t>자초인퓨즈오일 (골든호호바)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B241" s="2" t="n"/>
-      <c r="C241" s="2" t="n"/>
-      <c r="D241" s="2" t="n"/>
-    </row>
-    <row r="242" ht="15" customHeight="1">
-      <c r="A242" s="3" t="inlineStr">
+      <c r="B261" s="2" t="n"/>
+      <c r="C261" s="2" t="n"/>
+      <c r="D261" s="2" t="n"/>
+    </row>
+    <row r="262" ht="15" customHeight="1">
+      <c r="A262" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B242" s="3" t="inlineStr">
+      <c r="B262" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C242" s="3" t="inlineStr">
+      <c r="C262" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D242" s="3" t="inlineStr">
+      <c r="D262" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="243" ht="75" customHeight="1">
-      <c r="A243" s="8" t="inlineStr">
+    <row r="263" ht="80" customHeight="1">
+      <c r="A263" s="8" t="inlineStr">
         <is>
           <t>자초근</t>
         </is>
       </c>
-      <c r="B243" s="8" t="inlineStr">
+      <c r="B263" s="8" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C243" s="8" t="inlineStr">
+      <c r="C263" s="8" t="inlineStr">
         <is>
           <t>한약재, 자초, 지치의 뿌리, 자주색을 띈다하여 자초, 뿌리는 굵고 자주색, 오일에는 붉은 색이 우러나지만 알콜, 물에는 갈변합니다. 천연염색, 민간 약재로 사용</t>
         </is>
       </c>
-      <c r="D243" s="8" t="inlineStr">
+      <c r="D263" s="8" t="inlineStr">
         <is>
           <t>자운고 오일</t>
         </is>
       </c>
     </row>
-    <row r="244" ht="45" customHeight="1">
-      <c r="A244" s="8" t="inlineStr">
+    <row r="264" ht="48" customHeight="1">
+      <c r="A264" s="8" t="inlineStr">
         <is>
           <t>골덴호호바오일</t>
         </is>
       </c>
-      <c r="B244" s="8" t="inlineStr">
+      <c r="B264" s="8" t="inlineStr">
         <is>
           <t>85g(100ml)</t>
         </is>
       </c>
-      <c r="C244" s="8" t="inlineStr">
+      <c r="C264" s="8" t="inlineStr">
         <is>
           <t>사람피지성분과 비슷, 흡수력탁월, 액상왁스구조로 산패가 되지 않음, 보존기간길다.</t>
         </is>
       </c>
-      <c r="D244" s="8" t="inlineStr">
+      <c r="D264" s="8" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="245" ht="14" customHeight="1">
-      <c r="A245" s="5" t="inlineStr">
+    <row r="265" ht="14" customHeight="1">
+      <c r="A265" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B245" s="6" t="n"/>
-      <c r="C245" s="6" t="n"/>
-      <c r="D245" s="6" t="n"/>
-    </row>
-    <row r="246" ht="135" customHeight="1">
-      <c r="A246" s="9" t="inlineStr">
+      <c r="B265" s="6" t="n"/>
+      <c r="C265" s="6" t="n"/>
+      <c r="D265" s="6" t="n"/>
+    </row>
+    <row r="266" ht="144" customHeight="1">
+      <c r="A266" s="9" t="inlineStr">
         <is>
           <t>자초(紫草)
 한겨울 눈 쌓인 깊은 산 속에 자초는 그 주위의 눈을 새빨갛게 물들인다.
@@ -8118,22 +8221,22 @@
 빨간색때문에 염색시 염료로도 많이 사용되어왔습니다.</t>
         </is>
       </c>
-      <c r="B246" s="10" t="n"/>
-      <c r="C246" s="10" t="n"/>
-      <c r="D246" s="10" t="n"/>
-    </row>
-    <row r="247" ht="14" customHeight="1">
-      <c r="A247" s="5" t="inlineStr">
+      <c r="B266" s="10" t="n"/>
+      <c r="C266" s="10" t="n"/>
+      <c r="D266" s="10" t="n"/>
+    </row>
+    <row r="267" ht="14" customHeight="1">
+      <c r="A267" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B247" s="6" t="n"/>
-      <c r="C247" s="6" t="n"/>
-      <c r="D247" s="6" t="n"/>
-    </row>
-    <row r="248" ht="60" customHeight="1">
-      <c r="A248" s="9" t="inlineStr">
+      <c r="B267" s="6" t="n"/>
+      <c r="C267" s="6" t="n"/>
+      <c r="D267" s="6" t="n"/>
+    </row>
+    <row r="268" ht="64" customHeight="1">
+      <c r="A268" s="9" t="inlineStr">
         <is>
           <t>만들기과정
 1.쨈병을 깨끗하게 소독한 후 자초근50g과 (골덴호호바)오일을 넣어주세요.
@@ -8141,115 +8244,115 @@
 3. 색이 충분히 우러났으면 걸러서 보관하세요.</t>
         </is>
       </c>
-      <c r="B248" s="10" t="n"/>
-      <c r="C248" s="10" t="n"/>
-      <c r="D248" s="10" t="n"/>
-    </row>
-    <row r="249" ht="14" customHeight="1">
-      <c r="A249" s="5" t="inlineStr">
+      <c r="B268" s="10" t="n"/>
+      <c r="C268" s="10" t="n"/>
+      <c r="D268" s="10" t="n"/>
+    </row>
+    <row r="269" ht="14" customHeight="1">
+      <c r="A269" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B249" s="6" t="n"/>
-      <c r="C249" s="6" t="n"/>
-      <c r="D249" s="6" t="n"/>
-    </row>
-    <row r="250" ht="85.5" customHeight="1">
-      <c r="A250" s="10" t="n"/>
-      <c r="B250" s="10" t="n"/>
-      <c r="C250" s="10" t="n"/>
-      <c r="D250" s="10" t="n"/>
-    </row>
-    <row r="251" ht="6" customHeight="1"/>
-    <row r="252" ht="22" customHeight="1">
-      <c r="A252" s="1" t="inlineStr">
+      <c r="B269" s="6" t="n"/>
+      <c r="C269" s="6" t="n"/>
+      <c r="D269" s="6" t="n"/>
+    </row>
+    <row r="270" ht="85.5" customHeight="1">
+      <c r="A270" s="10" t="n"/>
+      <c r="B270" s="10" t="n"/>
+      <c r="C270" s="10" t="n"/>
+      <c r="D270" s="10" t="n"/>
+    </row>
+    <row r="271" ht="6" customHeight="1"/>
+    <row r="272" ht="22" customHeight="1">
+      <c r="A272" s="1" t="inlineStr">
         <is>
           <t>유기농 동백마사지오일    [베이스오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B252" s="2" t="n"/>
-      <c r="C252" s="2" t="n"/>
-      <c r="D252" s="2" t="n"/>
-    </row>
-    <row r="253" ht="15" customHeight="1">
-      <c r="A253" s="3" t="inlineStr">
+      <c r="B272" s="2" t="n"/>
+      <c r="C272" s="2" t="n"/>
+      <c r="D272" s="2" t="n"/>
+    </row>
+    <row r="273" ht="15" customHeight="1">
+      <c r="A273" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B253" s="3" t="inlineStr">
+      <c r="B273" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C253" s="3" t="inlineStr">
+      <c r="C273" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D253" s="3" t="inlineStr">
+      <c r="D273" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="254" ht="30" customHeight="1">
-      <c r="A254" s="4" t="inlineStr">
+    <row r="274" ht="32" customHeight="1">
+      <c r="A274" s="4" t="inlineStr">
         <is>
           <t>유기농비정제동백오일</t>
         </is>
       </c>
-      <c r="B254" s="4" t="inlineStr">
+      <c r="B274" s="4" t="inlineStr">
         <is>
           <t>50ml / (46g)</t>
         </is>
       </c>
-      <c r="C254" s="4" t="inlineStr">
+      <c r="C274" s="4" t="inlineStr">
         <is>
           <t>보습성분인 다량의 올레인산함유</t>
         </is>
       </c>
-      <c r="D254" s="4" t="inlineStr">
+      <c r="D274" s="4" t="inlineStr">
         <is>
           <t>아보카도, / 골든 호호바등</t>
         </is>
       </c>
     </row>
-    <row r="255" ht="30" customHeight="1">
-      <c r="A255" s="4" t="inlineStr">
+    <row r="275" ht="32" customHeight="1">
+      <c r="A275" s="4" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B255" s="4" t="inlineStr">
+      <c r="B275" s="4" t="inlineStr">
         <is>
           <t>5~10방울</t>
         </is>
       </c>
-      <c r="C255" s="4" t="inlineStr">
+      <c r="C275" s="4" t="inlineStr">
         <is>
           <t>영유아임산부도 사용가능, / 모든피부연령, / 아로마테라피의 기본</t>
         </is>
       </c>
-      <c r="D255" s="4" t="inlineStr">
+      <c r="D275" s="4" t="inlineStr">
         <is>
           <t>만다린에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="14" customHeight="1">
-      <c r="A256" s="5" t="inlineStr">
+    <row r="276" ht="14" customHeight="1">
+      <c r="A276" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B256" s="6" t="n"/>
-      <c r="C256" s="6" t="n"/>
-      <c r="D256" s="6" t="n"/>
-    </row>
-    <row r="257" ht="165" customHeight="1">
-      <c r="A257" s="7" t="inlineStr">
+      <c r="B276" s="6" t="n"/>
+      <c r="C276" s="6" t="n"/>
+      <c r="D276" s="6" t="n"/>
+    </row>
+    <row r="277" ht="176" customHeight="1">
+      <c r="A277" s="7" t="inlineStr">
         <is>
           <t>동백나무는
 제주도와 남해안 일대에서 자생하는 우리나라의 대표적인 나무입니다.
@@ -8264,18 +8367,18 @@
         </is>
       </c>
     </row>
-    <row r="258" ht="14" customHeight="1">
-      <c r="A258" s="5" t="inlineStr">
+    <row r="278" ht="14" customHeight="1">
+      <c r="A278" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B258" s="6" t="n"/>
-      <c r="C258" s="6" t="n"/>
-      <c r="D258" s="6" t="n"/>
-    </row>
-    <row r="259" ht="60" customHeight="1">
-      <c r="A259" s="7" t="inlineStr">
+      <c r="B278" s="6" t="n"/>
+      <c r="C278" s="6" t="n"/>
+      <c r="D278" s="6" t="n"/>
+    </row>
+    <row r="279" ht="64" customHeight="1">
+      <c r="A279" s="7" t="inlineStr">
         <is>
           <t>만들기과정
 1.오일을 계량한 후
@@ -8284,128 +8387,128 @@
         </is>
       </c>
     </row>
-    <row r="260" ht="14" customHeight="1">
-      <c r="A260" s="5" t="inlineStr">
+    <row r="280" ht="14" customHeight="1">
+      <c r="A280" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B260" s="6" t="n"/>
-      <c r="C260" s="6" t="n"/>
-      <c r="D260" s="6" t="n"/>
-    </row>
-    <row r="261" ht="85.5" customHeight="1"/>
-    <row r="262" ht="6" customHeight="1"/>
-    <row r="263" ht="22" customHeight="1">
-      <c r="A263" s="1" t="inlineStr">
+      <c r="B280" s="6" t="n"/>
+      <c r="C280" s="6" t="n"/>
+      <c r="D280" s="6" t="n"/>
+    </row>
+    <row r="281" ht="85.5" customHeight="1"/>
+    <row r="282" ht="6" customHeight="1"/>
+    <row r="283" ht="22" customHeight="1">
+      <c r="A283" s="1" t="inlineStr">
         <is>
           <t>네일촉촉에센스    [오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B263" s="2" t="n"/>
-      <c r="C263" s="2" t="n"/>
-      <c r="D263" s="2" t="n"/>
-    </row>
-    <row r="264" ht="15" customHeight="1">
-      <c r="A264" s="3" t="inlineStr">
+      <c r="B283" s="2" t="n"/>
+      <c r="C283" s="2" t="n"/>
+      <c r="D283" s="2" t="n"/>
+    </row>
+    <row r="284" ht="15" customHeight="1">
+      <c r="A284" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B264" s="3" t="inlineStr">
+      <c r="B284" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C264" s="3" t="inlineStr">
+      <c r="C284" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D264" s="3" t="inlineStr">
+      <c r="D284" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="265" ht="30" customHeight="1">
-      <c r="A265" s="8" t="inlineStr">
+    <row r="285" ht="32" customHeight="1">
+      <c r="A285" s="8" t="inlineStr">
         <is>
           <t>로즈힙오일</t>
         </is>
       </c>
-      <c r="B265" s="8" t="inlineStr">
+      <c r="B285" s="8" t="inlineStr">
         <is>
           <t>6g</t>
         </is>
       </c>
-      <c r="C265" s="8" t="inlineStr">
+      <c r="C285" s="8" t="inlineStr">
         <is>
           <t>들장미열매압착, 용매추출, 비타민성분 많이 함유, 건성노화관리</t>
         </is>
       </c>
-      <c r="D265" s="8" t="inlineStr">
+      <c r="D285" s="8" t="inlineStr">
         <is>
           <t>원하는 베이스오일.</t>
         </is>
       </c>
     </row>
-    <row r="266" ht="45" customHeight="1">
-      <c r="A266" s="8" t="inlineStr">
+    <row r="286" ht="48" customHeight="1">
+      <c r="A286" s="8" t="inlineStr">
         <is>
           <t>(자초인퓨즈) / 호호바오일</t>
         </is>
       </c>
-      <c r="B266" s="8" t="inlineStr">
+      <c r="B286" s="8" t="inlineStr">
         <is>
           <t>6g</t>
         </is>
       </c>
-      <c r="C266" s="8" t="inlineStr">
+      <c r="C286" s="8" t="inlineStr">
         <is>
           <t>자초근을 담궈 우려낸 골든호호바오일. 호호바오일은 사람의 피지성분과 같고 흡수력이 좋다.</t>
         </is>
       </c>
-      <c r="D266" s="8" t="inlineStr">
+      <c r="D286" s="8" t="inlineStr">
         <is>
           <t>원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="267" ht="45" customHeight="1">
-      <c r="A267" s="8" t="inlineStr">
+    <row r="287" ht="48" customHeight="1">
+      <c r="A287" s="8" t="inlineStr">
         <is>
           <t>일랑일랑EO</t>
         </is>
       </c>
-      <c r="B267" s="8" t="inlineStr">
+      <c r="B287" s="8" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C267" s="8" t="inlineStr">
+      <c r="C287" s="8" t="inlineStr">
         <is>
           <t>목련과 꽃. 일랑일랑은 말레이어로 꽃중의 꽃이라는 뜻. 최음제, 항우울,피지조절 등</t>
         </is>
       </c>
-      <c r="D267" s="8" t="inlineStr">
+      <c r="D287" s="8" t="inlineStr">
         <is>
           <t>원하는 아로마오일.</t>
         </is>
       </c>
     </row>
-    <row r="268" ht="14" customHeight="1">
-      <c r="A268" s="5" t="inlineStr">
+    <row r="288" ht="14" customHeight="1">
+      <c r="A288" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B268" s="6" t="n"/>
-      <c r="C268" s="6" t="n"/>
-      <c r="D268" s="6" t="n"/>
-    </row>
-    <row r="269" ht="255" customHeight="1">
-      <c r="A269" s="9" t="inlineStr">
+      <c r="B288" s="6" t="n"/>
+      <c r="C288" s="6" t="n"/>
+      <c r="D288" s="6" t="n"/>
+    </row>
+    <row r="289" ht="272" customHeight="1">
+      <c r="A289" s="9" t="inlineStr">
         <is>
           <t>요즈음은 네일샵도 미용실처럼 흔하고
 네일케어를 정기적으로 받는 마니아들이 주변에 많이 있습니다.
@@ -8426,22 +8529,22 @@
 수시로 바르고 흡수시키면 건강하고 생기있는 손톱을 만들어 줄 수 있습니다. ^^</t>
         </is>
       </c>
-      <c r="B269" s="10" t="n"/>
-      <c r="C269" s="10" t="n"/>
-      <c r="D269" s="10" t="n"/>
-    </row>
-    <row r="270" ht="14" customHeight="1">
-      <c r="A270" s="5" t="inlineStr">
+      <c r="B289" s="10" t="n"/>
+      <c r="C289" s="10" t="n"/>
+      <c r="D289" s="10" t="n"/>
+    </row>
+    <row r="290" ht="14" customHeight="1">
+      <c r="A290" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B270" s="6" t="n"/>
-      <c r="C270" s="6" t="n"/>
-      <c r="D270" s="6" t="n"/>
-    </row>
-    <row r="271" ht="120" customHeight="1">
-      <c r="A271" s="9" t="inlineStr">
+      <c r="B290" s="6" t="n"/>
+      <c r="C290" s="6" t="n"/>
+      <c r="D290" s="6" t="n"/>
+    </row>
+    <row r="291" ht="128" customHeight="1">
+      <c r="A291" s="9" t="inlineStr">
         <is>
           <t>만들기과정
 1 소독된 용기에 로즈힙오일, (자초인퓨즈)호호바오일을 계량한다.
@@ -8453,115 +8556,121 @@
 3. 색이 충분히 우러났으면 걸러서 보관하세요.</t>
         </is>
       </c>
-      <c r="B271" s="10" t="n"/>
-      <c r="C271" s="10" t="n"/>
-      <c r="D271" s="10" t="n"/>
-    </row>
-    <row r="272" ht="14" customHeight="1">
-      <c r="A272" s="5" t="inlineStr">
+      <c r="B291" s="10" t="n"/>
+      <c r="C291" s="10" t="n"/>
+      <c r="D291" s="10" t="n"/>
+    </row>
+    <row r="292" ht="14" customHeight="1">
+      <c r="A292" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B272" s="6" t="n"/>
-      <c r="C272" s="6" t="n"/>
-      <c r="D272" s="6" t="n"/>
-    </row>
-    <row r="273" ht="171" customHeight="1">
-      <c r="A273" s="10" t="n"/>
-      <c r="B273" s="10" t="n"/>
-      <c r="C273" s="10" t="n"/>
-      <c r="D273" s="10" t="n"/>
-    </row>
-    <row r="274" ht="6" customHeight="1"/>
-    <row r="275" ht="22" customHeight="1">
-      <c r="A275" s="1" t="inlineStr">
+      <c r="B292" s="6" t="n"/>
+      <c r="C292" s="6" t="n"/>
+      <c r="D292" s="6" t="n"/>
+    </row>
+    <row r="293" ht="85.5" customHeight="1">
+      <c r="A293" s="10" t="n"/>
+      <c r="B293" s="10" t="n"/>
+      <c r="C293" s="10" t="n"/>
+      <c r="D293" s="10" t="n"/>
+    </row>
+    <row r="294" ht="85.5" customHeight="1">
+      <c r="A294" s="10" t="n"/>
+      <c r="B294" s="10" t="n"/>
+      <c r="C294" s="10" t="n"/>
+      <c r="D294" s="10" t="n"/>
+    </row>
+    <row r="295" ht="6" customHeight="1"/>
+    <row r="296" ht="22" customHeight="1">
+      <c r="A296" s="1" t="inlineStr">
         <is>
           <t>허브 페이셜&amp;바디오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B275" s="2" t="n"/>
-      <c r="C275" s="2" t="n"/>
-      <c r="D275" s="2" t="n"/>
-    </row>
-    <row r="276" ht="15" customHeight="1">
-      <c r="A276" s="3" t="inlineStr">
+      <c r="B296" s="2" t="n"/>
+      <c r="C296" s="2" t="n"/>
+      <c r="D296" s="2" t="n"/>
+    </row>
+    <row r="297" ht="15" customHeight="1">
+      <c r="A297" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B276" s="3" t="inlineStr">
+      <c r="B297" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C276" s="3" t="inlineStr">
+      <c r="C297" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D276" s="3" t="inlineStr">
+      <c r="D297" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="277" ht="30" customHeight="1">
-      <c r="A277" s="4" t="inlineStr">
+    <row r="298" ht="32" customHeight="1">
+      <c r="A298" s="4" t="inlineStr">
         <is>
           <t>골든 호호바오일</t>
         </is>
       </c>
-      <c r="B277" s="4" t="inlineStr">
+      <c r="B298" s="4" t="inlineStr">
         <is>
           <t>85g / (100ml)</t>
         </is>
       </c>
-      <c r="C277" s="4" t="inlineStr">
+      <c r="C298" s="4" t="inlineStr">
         <is>
           <t>액상왁스, 사람피지성분과 비슷, 흡수력탁월</t>
         </is>
       </c>
-      <c r="D277" s="4" t="inlineStr">
+      <c r="D298" s="4" t="inlineStr">
         <is>
           <t>(유기농) 마카다미아넛오일</t>
         </is>
       </c>
     </row>
-    <row r="278" ht="30" customHeight="1">
-      <c r="A278" s="4" t="inlineStr">
+    <row r="299" ht="32" customHeight="1">
+      <c r="A299" s="4" t="inlineStr">
         <is>
           <t>로즈우드, 라벤더, 버가못 등 에센셜오일</t>
         </is>
       </c>
-      <c r="B278" s="4" t="inlineStr">
+      <c r="B299" s="4" t="inlineStr">
         <is>
           <t>10~30방울</t>
         </is>
       </c>
-      <c r="C278" s="4" t="inlineStr">
+      <c r="C299" s="4" t="inlineStr">
         <is>
           <t>아로마테라피</t>
         </is>
       </c>
-      <c r="D278" s="4" t="inlineStr">
+      <c r="D299" s="4" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="279" ht="14" customHeight="1">
-      <c r="A279" s="5" t="inlineStr">
+    <row r="300" ht="14" customHeight="1">
+      <c r="A300" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B279" s="6" t="n"/>
-      <c r="C279" s="6" t="n"/>
-      <c r="D279" s="6" t="n"/>
-    </row>
-    <row r="280" ht="105" customHeight="1">
-      <c r="A280" s="7" t="inlineStr">
+      <c r="B300" s="6" t="n"/>
+      <c r="C300" s="6" t="n"/>
+      <c r="D300" s="6" t="n"/>
+    </row>
+    <row r="301" ht="112" customHeight="1">
+      <c r="A301" s="7" t="inlineStr">
         <is>
           <t>호호바오일은
 사람피지성분과 흡사한 성분입니다
@@ -8573,18 +8682,18 @@
         </is>
       </c>
     </row>
-    <row r="281" ht="14" customHeight="1">
-      <c r="A281" s="5" t="inlineStr">
+    <row r="302" ht="14" customHeight="1">
+      <c r="A302" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B281" s="6" t="n"/>
-      <c r="C281" s="6" t="n"/>
-      <c r="D281" s="6" t="n"/>
-    </row>
-    <row r="282" ht="75" customHeight="1">
-      <c r="A282" s="7" t="inlineStr">
+      <c r="B302" s="6" t="n"/>
+      <c r="C302" s="6" t="n"/>
+      <c r="D302" s="6" t="n"/>
+    </row>
+    <row r="303" ht="80" customHeight="1">
+      <c r="A303" s="7" t="inlineStr">
         <is>
           <t>만들기과정
 주의!
@@ -8593,106 +8702,106 @@
         </is>
       </c>
     </row>
-    <row r="283" ht="14" customHeight="1">
-      <c r="A283" s="5" t="inlineStr">
+    <row r="304" ht="14" customHeight="1">
+      <c r="A304" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B283" s="6" t="n"/>
-      <c r="C283" s="6" t="n"/>
-      <c r="D283" s="6" t="n"/>
-    </row>
-    <row r="284" ht="85.5" customHeight="1"/>
-    <row r="285" ht="6" customHeight="1"/>
-    <row r="286" ht="22" customHeight="1">
-      <c r="A286" s="1" t="inlineStr">
+      <c r="B304" s="6" t="n"/>
+      <c r="C304" s="6" t="n"/>
+      <c r="D304" s="6" t="n"/>
+    </row>
+    <row r="305" ht="85.5" customHeight="1"/>
+    <row r="306" ht="6" customHeight="1"/>
+    <row r="307" ht="22" customHeight="1">
+      <c r="A307" s="1" t="inlineStr">
         <is>
           <t>아르간베이비오일    [오일]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B286" s="2" t="n"/>
-      <c r="C286" s="2" t="n"/>
-      <c r="D286" s="2" t="n"/>
-    </row>
-    <row r="287" ht="15" customHeight="1">
-      <c r="A287" s="3" t="inlineStr">
+      <c r="B307" s="2" t="n"/>
+      <c r="C307" s="2" t="n"/>
+      <c r="D307" s="2" t="n"/>
+    </row>
+    <row r="308" ht="15" customHeight="1">
+      <c r="A308" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B287" s="3" t="inlineStr">
+      <c r="B308" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C287" s="3" t="inlineStr">
+      <c r="C308" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D287" s="3" t="inlineStr">
+      <c r="D308" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="288" ht="45" customHeight="1">
-      <c r="A288" s="8" t="inlineStr">
+    <row r="309" ht="48" customHeight="1">
+      <c r="A309" s="8" t="inlineStr">
         <is>
           <t>유기농아르간오일</t>
         </is>
       </c>
-      <c r="B288" s="8" t="inlineStr">
+      <c r="B309" s="8" t="inlineStr">
         <is>
           <t>18g(20ml)</t>
         </is>
       </c>
-      <c r="C288" s="8" t="inlineStr">
+      <c r="C309" s="8" t="inlineStr">
         <is>
           <t>보습성분인 올레인산, / 리놀렌산이 다량함유.</t>
         </is>
       </c>
-      <c r="D288" s="8" t="inlineStr">
+      <c r="D309" s="8" t="inlineStr">
         <is>
           <t>동백, 마카다미아넛오일 등 / 식물성오일이면 OK</t>
         </is>
       </c>
     </row>
-    <row r="289" ht="45" customHeight="1">
-      <c r="A289" s="8" t="inlineStr">
+    <row r="310" ht="48" customHeight="1">
+      <c r="A310" s="8" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B289" s="8" t="inlineStr">
+      <c r="B310" s="8" t="inlineStr">
         <is>
           <t>2방울</t>
         </is>
       </c>
-      <c r="C289" s="8" t="inlineStr">
+      <c r="C310" s="8" t="inlineStr">
         <is>
           <t>허브의 여왕, 몸과 마음을 진정, / 영유아 민감트러블피부에 사용</t>
         </is>
       </c>
-      <c r="D289" s="8" t="inlineStr">
+      <c r="D310" s="8" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="290" ht="14" customHeight="1">
-      <c r="A290" s="5" t="inlineStr">
+    <row r="311" ht="14" customHeight="1">
+      <c r="A311" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B290" s="6" t="n"/>
-      <c r="C290" s="6" t="n"/>
-      <c r="D290" s="6" t="n"/>
-    </row>
-    <row r="291" ht="180" customHeight="1">
-      <c r="A291" s="9" t="inlineStr">
+      <c r="B311" s="6" t="n"/>
+      <c r="C311" s="6" t="n"/>
+      <c r="D311" s="6" t="n"/>
+    </row>
+    <row r="312" ht="192" customHeight="1">
+      <c r="A312" s="9" t="inlineStr">
         <is>
           <t>모로코가 원산지인 아르간나무는 높이가 6~10m 정도되는 향이 강한 상록수입니다.
 수명은 150년~200년 정도이고 1925년 이후로 그 수가 점점 줄어들면서
@@ -8708,22 +8817,22 @@
 인정받고 있으며, 특히 리놀레산은 피부를 부드럽게 하고 건강하게 하는데 효과적입니다.</t>
         </is>
       </c>
-      <c r="B291" s="10" t="n"/>
-      <c r="C291" s="10" t="n"/>
-      <c r="D291" s="10" t="n"/>
-    </row>
-    <row r="292" ht="14" customHeight="1">
-      <c r="A292" s="5" t="inlineStr">
+      <c r="B312" s="10" t="n"/>
+      <c r="C312" s="10" t="n"/>
+      <c r="D312" s="10" t="n"/>
+    </row>
+    <row r="313" ht="14" customHeight="1">
+      <c r="A313" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B292" s="6" t="n"/>
-      <c r="C292" s="6" t="n"/>
-      <c r="D292" s="6" t="n"/>
-    </row>
-    <row r="293" ht="90" customHeight="1">
-      <c r="A293" s="9" t="inlineStr">
+      <c r="B313" s="6" t="n"/>
+      <c r="C313" s="6" t="n"/>
+      <c r="D313" s="6" t="n"/>
+    </row>
+    <row r="314" ht="96" customHeight="1">
+      <c r="A314" s="9" t="inlineStr">
         <is>
           <t>만들기과정
 1. 오일을 계량한다.
@@ -8732,159 +8841,159 @@
 [사용법] 건조한 부분에 수시로 발라주고 세안이나 목욕 후 물기가 있을 때 사용하면 얇은 오일막이 촉촉함이 오래가게 만들어준다.</t>
         </is>
       </c>
-      <c r="B293" s="10" t="n"/>
-      <c r="C293" s="10" t="n"/>
-      <c r="D293" s="10" t="n"/>
-    </row>
-    <row r="294" ht="14" customHeight="1">
-      <c r="A294" s="5" t="inlineStr">
+      <c r="B314" s="10" t="n"/>
+      <c r="C314" s="10" t="n"/>
+      <c r="D314" s="10" t="n"/>
+    </row>
+    <row r="315" ht="14" customHeight="1">
+      <c r="A315" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B294" s="6" t="n"/>
-      <c r="C294" s="6" t="n"/>
-      <c r="D294" s="6" t="n"/>
-    </row>
-    <row r="295" ht="85.5" customHeight="1">
-      <c r="A295" s="10" t="n"/>
-      <c r="B295" s="10" t="n"/>
-      <c r="C295" s="10" t="n"/>
-      <c r="D295" s="10" t="n"/>
-    </row>
-    <row r="296" ht="6" customHeight="1"/>
-    <row r="297" ht="22" customHeight="1">
-      <c r="A297" s="1" t="inlineStr">
+      <c r="B315" s="6" t="n"/>
+      <c r="C315" s="6" t="n"/>
+      <c r="D315" s="6" t="n"/>
+    </row>
+    <row r="316" ht="85.5" customHeight="1">
+      <c r="A316" s="10" t="n"/>
+      <c r="B316" s="10" t="n"/>
+      <c r="C316" s="10" t="n"/>
+      <c r="D316" s="10" t="n"/>
+    </row>
+    <row r="317" ht="6" customHeight="1"/>
+    <row r="318" ht="22" customHeight="1">
+      <c r="A318" s="1" t="inlineStr">
         <is>
           <t>캐모마일 아토베이비 오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B297" s="2" t="n"/>
-      <c r="C297" s="2" t="n"/>
-      <c r="D297" s="2" t="n"/>
-    </row>
-    <row r="298" ht="15" customHeight="1">
-      <c r="A298" s="3" t="inlineStr">
+      <c r="B318" s="2" t="n"/>
+      <c r="C318" s="2" t="n"/>
+      <c r="D318" s="2" t="n"/>
+    </row>
+    <row r="319" ht="15" customHeight="1">
+      <c r="A319" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B298" s="3" t="inlineStr">
+      <c r="B319" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C298" s="3" t="inlineStr">
+      <c r="C319" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D298" s="3" t="inlineStr">
+      <c r="D319" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="45" customHeight="1">
-      <c r="A299" s="4" t="inlineStr">
+    <row r="320" ht="48" customHeight="1">
+      <c r="A320" s="4" t="inlineStr">
         <is>
           <t>카렌듈라오일</t>
         </is>
       </c>
-      <c r="B299" s="4" t="inlineStr">
+      <c r="B320" s="4" t="inlineStr">
         <is>
           <t>41.88%</t>
         </is>
       </c>
-      <c r="C299" s="4" t="inlineStr">
+      <c r="C320" s="4" t="inlineStr">
         <is>
           <t>금잔화오일을 호호바오일에 담궈 유효성분을 추출함. 보습효과 +진정, 항**효과 등</t>
         </is>
       </c>
-      <c r="D299" s="4" t="inlineStr">
+      <c r="D320" s="4" t="inlineStr">
         <is>
           <t>아르간, 로즈힙 등..</t>
         </is>
       </c>
     </row>
-    <row r="300" ht="75" customHeight="1">
-      <c r="A300" s="4" t="inlineStr">
+    <row r="321" ht="80" customHeight="1">
+      <c r="A321" s="4" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B300" s="4" t="inlineStr">
+      <c r="B321" s="4" t="inlineStr">
         <is>
           <t>57.6%</t>
         </is>
       </c>
-      <c r="C300" s="4" t="inlineStr">
+      <c r="C321" s="4" t="inlineStr">
         <is>
           <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
-      <c r="D300" s="4" t="inlineStr">
+      <c r="D321" s="4" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="301" ht="45" customHeight="1">
-      <c r="A301" s="4" t="inlineStr">
+    <row r="322" ht="48" customHeight="1">
+      <c r="A322" s="4" t="inlineStr">
         <is>
           <t>버가못 에센셜오일(FCF)</t>
         </is>
       </c>
-      <c r="B301" s="4" t="inlineStr">
+      <c r="B322" s="4" t="inlineStr">
         <is>
           <t>0.31%</t>
         </is>
       </c>
-      <c r="C301" s="4" t="inlineStr">
+      <c r="C322" s="4" t="inlineStr">
         <is>
           <t>장미향 나는 제라늄, 균형의 오일 / 피지균형 등 모든 피부</t>
         </is>
       </c>
-      <c r="D301" s="4" t="inlineStr">
+      <c r="D322" s="4" t="inlineStr">
         <is>
           <t>레몬, 라벤더, 유칼립투스 등 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="302" ht="60" customHeight="1">
-      <c r="A302" s="4" t="inlineStr">
+    <row r="323" ht="64" customHeight="1">
+      <c r="A323" s="4" t="inlineStr">
         <is>
           <t>로먼 캐모마일EO</t>
         </is>
       </c>
-      <c r="B302" s="4" t="inlineStr">
+      <c r="B323" s="4" t="inlineStr">
         <is>
           <t>0.21%</t>
         </is>
       </c>
-      <c r="C302" s="4" t="inlineStr">
+      <c r="C323" s="4" t="inlineStr">
         <is>
           <t>국화과 허브, 진정효과 탁월, 민감 신생아 영유아 사용 / 넣지 않고 사용하면 오트밀오일 자체향.</t>
         </is>
       </c>
-      <c r="D302" s="4" t="inlineStr">
+      <c r="D323" s="4" t="inlineStr">
         <is>
           <t>라벤더에센셜오일, 저먼카모마일(을 사용할 경우 양을 반으로 줄여야함.강한향)</t>
         </is>
       </c>
     </row>
-    <row r="303" ht="14" customHeight="1">
-      <c r="A303" s="5" t="inlineStr">
+    <row r="324" ht="14" customHeight="1">
+      <c r="A324" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B303" s="6" t="n"/>
-      <c r="C303" s="6" t="n"/>
-      <c r="D303" s="6" t="n"/>
-    </row>
-    <row r="304" ht="60" customHeight="1">
-      <c r="A304" s="7" t="inlineStr">
+      <c r="B324" s="6" t="n"/>
+      <c r="C324" s="6" t="n"/>
+      <c r="D324" s="6" t="n"/>
+    </row>
+    <row r="325" ht="64" customHeight="1">
+      <c r="A325" s="7" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 오일계량합니다.
@@ -8893,252 +9002,252 @@
         </is>
       </c>
     </row>
-    <row r="305" ht="14" customHeight="1">
-      <c r="A305" s="5" t="inlineStr">
+    <row r="326" ht="14" customHeight="1">
+      <c r="A326" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B305" s="6" t="n"/>
-      <c r="C305" s="6" t="n"/>
-      <c r="D305" s="6" t="n"/>
-    </row>
-    <row r="306" ht="85.5" customHeight="1"/>
-    <row r="307" ht="6" customHeight="1"/>
-    <row r="308" ht="22" customHeight="1">
-      <c r="A308" s="1" t="inlineStr">
+      <c r="B326" s="6" t="n"/>
+      <c r="C326" s="6" t="n"/>
+      <c r="D326" s="6" t="n"/>
+    </row>
+    <row r="327" ht="85.5" customHeight="1"/>
+    <row r="328" ht="6" customHeight="1"/>
+    <row r="329" ht="22" customHeight="1">
+      <c r="A329" s="1" t="inlineStr">
         <is>
           <t>자운고 인퓨즈 오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B308" s="2" t="n"/>
-      <c r="C308" s="2" t="n"/>
-      <c r="D308" s="2" t="n"/>
-    </row>
-    <row r="309" ht="15" customHeight="1">
-      <c r="A309" s="3" t="inlineStr">
+      <c r="B329" s="2" t="n"/>
+      <c r="C329" s="2" t="n"/>
+      <c r="D329" s="2" t="n"/>
+    </row>
+    <row r="330" ht="15" customHeight="1">
+      <c r="A330" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B309" s="3" t="inlineStr">
+      <c r="B330" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C309" s="3" t="inlineStr">
+      <c r="C330" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D309" s="3" t="inlineStr">
+      <c r="D330" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="310" ht="45" customHeight="1">
-      <c r="A310" s="8" t="inlineStr">
+    <row r="331" ht="48" customHeight="1">
+      <c r="A331" s="8" t="inlineStr">
         <is>
           <t>감초</t>
         </is>
       </c>
-      <c r="B310" s="8" t="inlineStr">
+      <c r="B331" s="8" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="C310" s="8" t="inlineStr">
+      <c r="C331" s="8" t="inlineStr">
         <is>
           <t>감초의 수/지용성성분추출물.</t>
         </is>
       </c>
-      <c r="D310" s="8" t="inlineStr">
+      <c r="D331" s="8" t="inlineStr">
         <is>
           <t>카렌듈라, 카모마일, 오이추출물, 병풀, 브로콜리, 파프리카 등</t>
         </is>
       </c>
     </row>
-    <row r="311" ht="30" customHeight="1">
-      <c r="A311" s="8" t="inlineStr">
+    <row r="332" ht="32" customHeight="1">
+      <c r="A332" s="8" t="inlineStr">
         <is>
           <t>황금</t>
         </is>
       </c>
-      <c r="B311" s="8" t="inlineStr">
+      <c r="B332" s="8" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="C311" s="8" t="inlineStr">
+      <c r="C332" s="8" t="inlineStr">
         <is>
           <t>황금(속썩은풀 뿌리) 추출, 항염·진정·항산화</t>
         </is>
       </c>
-      <c r="D311" s="8" t="n"/>
-    </row>
-    <row r="312" ht="30" customHeight="1">
-      <c r="A312" s="8" t="inlineStr">
+      <c r="D332" s="8" t="n"/>
+    </row>
+    <row r="333" ht="32" customHeight="1">
+      <c r="A333" s="8" t="inlineStr">
         <is>
           <t>유근피</t>
         </is>
       </c>
-      <c r="B312" s="8" t="inlineStr">
+      <c r="B333" s="8" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="C312" s="8" t="inlineStr">
+      <c r="C333" s="8" t="inlineStr">
         <is>
           <t>유근피(느릅나무 껍질) 추출, 점액질 진정·보습</t>
         </is>
       </c>
-      <c r="D312" s="8" t="n"/>
-    </row>
-    <row r="313" ht="15" customHeight="1">
-      <c r="A313" s="8" t="inlineStr">
+      <c r="D333" s="8" t="n"/>
+    </row>
+    <row r="334" ht="16" customHeight="1">
+      <c r="A334" s="8" t="inlineStr">
         <is>
           <t>금은화</t>
         </is>
       </c>
-      <c r="B313" s="8" t="inlineStr">
+      <c r="B334" s="8" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="C313" s="8" t="inlineStr">
+      <c r="C334" s="8" t="inlineStr">
         <is>
           <t>금은화(인동꽃) 추출, 항염·진정</t>
         </is>
       </c>
-      <c r="D313" s="8" t="n"/>
-    </row>
-    <row r="314" ht="15" customHeight="1">
-      <c r="A314" s="8" t="inlineStr">
+      <c r="D334" s="8" t="n"/>
+    </row>
+    <row r="335" ht="16" customHeight="1">
+      <c r="A335" s="8" t="inlineStr">
         <is>
           <t>감국</t>
         </is>
       </c>
-      <c r="B314" s="8" t="inlineStr">
+      <c r="B335" s="8" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="C314" s="8" t="inlineStr">
+      <c r="C335" s="8" t="inlineStr">
         <is>
           <t>감국(국화) 추출물, 진정·항염</t>
         </is>
       </c>
-      <c r="D314" s="8" t="n"/>
-    </row>
-    <row r="315" ht="15" customHeight="1">
-      <c r="A315" s="8" t="inlineStr">
+      <c r="D335" s="8" t="n"/>
+    </row>
+    <row r="336" ht="16" customHeight="1">
+      <c r="A336" s="8" t="inlineStr">
         <is>
           <t>진피</t>
         </is>
       </c>
-      <c r="B315" s="8" t="inlineStr">
+      <c r="B336" s="8" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="C315" s="8" t="inlineStr">
+      <c r="C336" s="8" t="inlineStr">
         <is>
           <t>진피(귤껍질) 추출, 항산화·수렴</t>
         </is>
       </c>
-      <c r="D315" s="8" t="n"/>
-    </row>
-    <row r="316" ht="30" customHeight="1">
-      <c r="A316" s="8" t="inlineStr">
+      <c r="D336" s="8" t="n"/>
+    </row>
+    <row r="337" ht="32" customHeight="1">
+      <c r="A337" s="8" t="inlineStr">
         <is>
           <t>자초</t>
         </is>
       </c>
-      <c r="B316" s="8" t="inlineStr">
+      <c r="B337" s="8" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="C316" s="8" t="inlineStr">
+      <c r="C337" s="8" t="inlineStr">
         <is>
           <t>자초(지치 뿌리) 추출, 항염·진정(자색소)</t>
         </is>
       </c>
-      <c r="D316" s="8" t="n"/>
-    </row>
-    <row r="317" ht="15" customHeight="1">
-      <c r="A317" s="8" t="inlineStr">
+      <c r="D337" s="8" t="n"/>
+    </row>
+    <row r="338" ht="16" customHeight="1">
+      <c r="A338" s="8" t="inlineStr">
         <is>
           <t>당귀</t>
         </is>
       </c>
-      <c r="B317" s="8" t="inlineStr">
+      <c r="B338" s="8" t="inlineStr">
         <is>
           <t>1.72%</t>
         </is>
       </c>
-      <c r="C317" s="8" t="inlineStr">
+      <c r="C338" s="8" t="inlineStr">
         <is>
           <t>한방 약재, 혈행·보습, 피부 진정</t>
         </is>
       </c>
-      <c r="D317" s="8" t="n"/>
-    </row>
-    <row r="318" ht="75" customHeight="1">
-      <c r="A318" s="8" t="inlineStr">
+      <c r="D338" s="8" t="n"/>
+    </row>
+    <row r="339" ht="80" customHeight="1">
+      <c r="A339" s="8" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B318" s="8" t="inlineStr">
+      <c r="B339" s="8" t="inlineStr">
         <is>
           <t>86.24%</t>
         </is>
       </c>
-      <c r="C318" s="8" t="inlineStr">
+      <c r="C339" s="8" t="inlineStr">
         <is>
           <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
-      <c r="D318" s="8" t="inlineStr">
+      <c r="D339" s="8" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="319" ht="14" customHeight="1">
-      <c r="A319" s="5" t="inlineStr">
+    <row r="340" ht="14" customHeight="1">
+      <c r="A340" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B319" s="6" t="n"/>
-      <c r="C319" s="6" t="n"/>
-      <c r="D319" s="6" t="n"/>
-    </row>
-    <row r="320" ht="15" customHeight="1">
-      <c r="A320" s="9" t="inlineStr">
+      <c r="B340" s="6" t="n"/>
+      <c r="C340" s="6" t="n"/>
+      <c r="D340" s="6" t="n"/>
+    </row>
+    <row r="341" ht="16" customHeight="1">
+      <c r="A341" s="9" t="inlineStr">
         <is>
           <t>* 자운고 한방연고를 만들때 필요한 인퓨즈 오일 제조방법 입니다.</t>
         </is>
       </c>
-      <c r="B320" s="10" t="n"/>
-      <c r="C320" s="10" t="n"/>
-      <c r="D320" s="10" t="n"/>
-    </row>
-    <row r="321" ht="14" customHeight="1">
-      <c r="A321" s="5" t="inlineStr">
+      <c r="B341" s="10" t="n"/>
+      <c r="C341" s="10" t="n"/>
+      <c r="D341" s="10" t="n"/>
+    </row>
+    <row r="342" ht="14" customHeight="1">
+      <c r="A342" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B321" s="6" t="n"/>
-      <c r="C321" s="6" t="n"/>
-      <c r="D321" s="6" t="n"/>
-    </row>
-    <row r="322" ht="120" customHeight="1">
-      <c r="A322" s="9" t="inlineStr">
+      <c r="B342" s="6" t="n"/>
+      <c r="C342" s="6" t="n"/>
+      <c r="D342" s="6" t="n"/>
+    </row>
+    <row r="343" ht="128" customHeight="1">
+      <c r="A343" s="9" t="inlineStr">
         <is>
           <t>만들기 방법
 (정해진 비율은 없구요. 약재가 잠길 정도로 해주시면 되요. 오일을 한가지만 하셔도 되지만 여러가지 오일을 섞어서 사용하셔도 된답니다.)
@@ -9148,247 +9257,247 @@
 3-2. (급속 온침법) 12~24시간 동안 40~50도 정도 온도를 유지하게 슬로우쿠커 등을 이용해 데워주세요. 급하게 재료 성분이 우러납니다.</t>
         </is>
       </c>
-      <c r="B322" s="10" t="n"/>
-      <c r="C322" s="10" t="n"/>
-      <c r="D322" s="10" t="n"/>
-    </row>
-    <row r="323" ht="14" customHeight="1">
-      <c r="A323" s="5" t="inlineStr">
+      <c r="B343" s="10" t="n"/>
+      <c r="C343" s="10" t="n"/>
+      <c r="D343" s="10" t="n"/>
+    </row>
+    <row r="344" ht="14" customHeight="1">
+      <c r="A344" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B323" s="6" t="n"/>
-      <c r="C323" s="6" t="n"/>
-      <c r="D323" s="6" t="n"/>
-    </row>
-    <row r="324" ht="85.5" customHeight="1">
-      <c r="A324" s="10" t="n"/>
-      <c r="B324" s="10" t="n"/>
-      <c r="C324" s="10" t="n"/>
-      <c r="D324" s="10" t="n"/>
-    </row>
-    <row r="325" ht="6" customHeight="1"/>
-    <row r="326" ht="22" customHeight="1">
-      <c r="A326" s="1" t="inlineStr">
+      <c r="B344" s="6" t="n"/>
+      <c r="C344" s="6" t="n"/>
+      <c r="D344" s="6" t="n"/>
+    </row>
+    <row r="345" ht="85.5" customHeight="1">
+      <c r="A345" s="10" t="n"/>
+      <c r="B345" s="10" t="n"/>
+      <c r="C345" s="10" t="n"/>
+      <c r="D345" s="10" t="n"/>
+    </row>
+    <row r="346" ht="6" customHeight="1"/>
+    <row r="347" ht="22" customHeight="1">
+      <c r="A347" s="1" t="inlineStr">
         <is>
           <t>귤베이비오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B326" s="2" t="n"/>
-      <c r="C326" s="2" t="n"/>
-      <c r="D326" s="2" t="n"/>
-    </row>
-    <row r="327" ht="15" customHeight="1">
-      <c r="A327" s="3" t="inlineStr">
+      <c r="B347" s="2" t="n"/>
+      <c r="C347" s="2" t="n"/>
+      <c r="D347" s="2" t="n"/>
+    </row>
+    <row r="348" ht="15" customHeight="1">
+      <c r="A348" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B327" s="3" t="inlineStr">
+      <c r="B348" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C327" s="3" t="inlineStr">
+      <c r="C348" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D327" s="3" t="inlineStr">
+      <c r="D348" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="328" ht="75" customHeight="1">
-      <c r="A328" s="4" t="inlineStr">
+    <row r="349" ht="80" customHeight="1">
+      <c r="A349" s="4" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B328" s="4" t="inlineStr">
+      <c r="B349" s="4" t="inlineStr">
         <is>
           <t>50.36%</t>
         </is>
       </c>
-      <c r="C328" s="4" t="inlineStr">
+      <c r="C349" s="4" t="inlineStr">
         <is>
           <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
-      <c r="D328" s="4" t="inlineStr">
+      <c r="D349" s="4" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="329" ht="30" customHeight="1">
-      <c r="A329" s="4" t="inlineStr">
+    <row r="350" ht="32" customHeight="1">
+      <c r="A350" s="4" t="inlineStr">
         <is>
           <t>달맞이종자오일</t>
         </is>
       </c>
-      <c r="B329" s="4" t="inlineStr">
+      <c r="B350" s="4" t="inlineStr">
         <is>
           <t>25.18%</t>
         </is>
       </c>
-      <c r="C329" s="4" t="inlineStr">
+      <c r="C350" s="4" t="inlineStr">
         <is>
           <t>월견초 종자유, / 감마리놀린산 다량함유,</t>
         </is>
       </c>
-      <c r="D329" s="4" t="inlineStr">
+      <c r="D350" s="4" t="inlineStr">
         <is>
           <t>로즈힙, 아보카도,햄프씨드,보리지오일 등</t>
         </is>
       </c>
     </row>
-    <row r="330" ht="30" customHeight="1">
-      <c r="A330" s="4" t="inlineStr">
+    <row r="351" ht="48" customHeight="1">
+      <c r="A351" s="4" t="inlineStr">
         <is>
           <t>동백오일</t>
         </is>
       </c>
-      <c r="B330" s="4" t="inlineStr">
+      <c r="B351" s="4" t="inlineStr">
         <is>
           <t>20.14%</t>
         </is>
       </c>
-      <c r="C330" s="4" t="inlineStr">
+      <c r="C351" s="4" t="inlineStr">
         <is>
           <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비, / 민감 성피부</t>
         </is>
       </c>
-      <c r="D330" s="4" t="inlineStr">
+      <c r="D351" s="4" t="inlineStr">
         <is>
           <t>아르간오일, 호호바오일, 마카다미아넛오일 등</t>
         </is>
       </c>
     </row>
-    <row r="331" ht="60" customHeight="1">
-      <c r="A331" s="4" t="inlineStr">
+    <row r="352" ht="64" customHeight="1">
+      <c r="A352" s="4" t="inlineStr">
         <is>
           <t>토코페롤</t>
         </is>
       </c>
-      <c r="B331" s="4" t="inlineStr">
+      <c r="B352" s="4" t="inlineStr">
         <is>
           <t>2.01%</t>
         </is>
       </c>
-      <c r="C331" s="4" t="inlineStr">
+      <c r="C352" s="4" t="inlineStr">
         <is>
           <t>토코페롤, 지용성 보존제, 산화방지, 탄력,천연비타민E는 특유의 냄새가 있습니다. 감안하시고 대체해서 사용하세요.</t>
         </is>
       </c>
-      <c r="D331" s="4" t="inlineStr">
+      <c r="D352" s="4" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="332" ht="30" customHeight="1">
-      <c r="A332" s="4" t="inlineStr">
+    <row r="353" ht="32" customHeight="1">
+      <c r="A353" s="4" t="inlineStr">
         <is>
           <t>세라마이드5 컴플렉스</t>
         </is>
       </c>
-      <c r="B332" s="4" t="inlineStr">
+      <c r="B353" s="4" t="inlineStr">
         <is>
           <t>2.01%</t>
         </is>
       </c>
-      <c r="C332" s="4" t="inlineStr">
+      <c r="C353" s="4" t="inlineStr">
         <is>
           <t>5가지 멀티 세라마이드, / 피부 장벽 강화</t>
         </is>
       </c>
-      <c r="D332" s="4" t="inlineStr">
+      <c r="D353" s="4" t="inlineStr">
         <is>
           <t>스쿠알란, / 보르피린</t>
         </is>
       </c>
     </row>
-    <row r="333" ht="60" customHeight="1">
-      <c r="A333" s="4" t="inlineStr">
+    <row r="354" ht="64" customHeight="1">
+      <c r="A354" s="4" t="inlineStr">
         <is>
           <t>라벤더오일</t>
         </is>
       </c>
-      <c r="B333" s="4" t="inlineStr">
+      <c r="B354" s="4" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="C333" s="4" t="inlineStr">
+      <c r="C354" s="4" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="D333" s="4" t="inlineStr">
+      <c r="D354" s="4" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="334" ht="30" customHeight="1">
-      <c r="A334" s="4" t="inlineStr">
+    <row r="355" ht="48" customHeight="1">
+      <c r="A355" s="4" t="inlineStr">
         <is>
           <t>만다린EO</t>
         </is>
       </c>
-      <c r="B334" s="4" t="inlineStr">
+      <c r="B355" s="4" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="C334" s="4" t="inlineStr">
+      <c r="C355" s="4" t="inlineStr">
         <is>
           <t>귤껍질오일, / 임신기간 영아에게 안전하게 사용, / 모든 피부사용</t>
         </is>
       </c>
-      <c r="D334" s="4" t="inlineStr">
+      <c r="D355" s="4" t="inlineStr">
         <is>
           <t>오렌지, 버가못, 그레이프프룻 등 감귤류 오일</t>
         </is>
       </c>
     </row>
-    <row r="335" ht="30" customHeight="1">
-      <c r="A335" s="4" t="inlineStr">
+    <row r="356" ht="32" customHeight="1">
+      <c r="A356" s="4" t="inlineStr">
         <is>
           <t>저먼캐모마일EO</t>
         </is>
       </c>
-      <c r="B335" s="4" t="inlineStr">
+      <c r="B356" s="4" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="C335" s="4" t="inlineStr">
+      <c r="C356" s="4" t="inlineStr">
         <is>
           <t>국화과 허브, 카마쥴렌성분함유, 트러블성</t>
         </is>
       </c>
-      <c r="D335" s="4" t="inlineStr">
+      <c r="D356" s="4" t="inlineStr">
         <is>
           <t>라벤더 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="336" ht="14" customHeight="1">
-      <c r="A336" s="5" t="inlineStr">
+    <row r="357" ht="14" customHeight="1">
+      <c r="A357" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B336" s="6" t="n"/>
-      <c r="C336" s="6" t="n"/>
-      <c r="D336" s="6" t="n"/>
-    </row>
-    <row r="337" ht="75" customHeight="1">
-      <c r="A337" s="7" t="inlineStr">
+      <c r="B357" s="6" t="n"/>
+      <c r="C357" s="6" t="n"/>
+      <c r="D357" s="6" t="n"/>
+    </row>
+    <row r="358" ht="80" customHeight="1">
+      <c r="A358" s="7" t="inlineStr">
         <is>
           <t>참,
 애기랑 사용할 오일이라 에센셜오일 방울수를 적게 넣은 것 아시죠.
@@ -9398,18 +9507,18 @@
         </is>
       </c>
     </row>
-    <row r="338" ht="14" customHeight="1">
-      <c r="A338" s="5" t="inlineStr">
+    <row r="359" ht="14" customHeight="1">
+      <c r="A359" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B338" s="6" t="n"/>
-      <c r="C338" s="6" t="n"/>
-      <c r="D338" s="6" t="n"/>
-    </row>
-    <row r="339" ht="345" customHeight="1">
-      <c r="A339" s="7" t="inlineStr">
+      <c r="B359" s="6" t="n"/>
+      <c r="C359" s="6" t="n"/>
+      <c r="D359" s="6" t="n"/>
+    </row>
+    <row r="360" ht="368" customHeight="1">
+      <c r="A360" s="7" t="inlineStr">
         <is>
           <t>1.건성, 아토피, 모든 피부용 바디오일
 2.헤어트리트먼트(머리가 푸석할 때 다 발랐을 때 조금만 살짝 발라주세요.
@@ -9433,276 +9542,276 @@
         </is>
       </c>
     </row>
-    <row r="340" ht="14" customHeight="1">
-      <c r="A340" s="5" t="inlineStr">
+    <row r="361" ht="14" customHeight="1">
+      <c r="A361" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B340" s="6" t="n"/>
-      <c r="C340" s="6" t="n"/>
-      <c r="D340" s="6" t="n"/>
-    </row>
-    <row r="341" ht="85.5" customHeight="1"/>
-    <row r="342" ht="6" customHeight="1"/>
-    <row r="343" ht="22" customHeight="1">
-      <c r="A343" s="1" t="inlineStr">
+      <c r="B361" s="6" t="n"/>
+      <c r="C361" s="6" t="n"/>
+      <c r="D361" s="6" t="n"/>
+    </row>
+    <row r="362" ht="85.5" customHeight="1"/>
+    <row r="363" ht="6" customHeight="1"/>
+    <row r="364" ht="22" customHeight="1">
+      <c r="A364" s="1" t="inlineStr">
         <is>
           <t>자초 호호바 인퓨즈오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B343" s="2" t="n"/>
-      <c r="C343" s="2" t="n"/>
-      <c r="D343" s="2" t="n"/>
-    </row>
-    <row r="344" ht="15" customHeight="1">
-      <c r="A344" s="3" t="inlineStr">
+      <c r="B364" s="2" t="n"/>
+      <c r="C364" s="2" t="n"/>
+      <c r="D364" s="2" t="n"/>
+    </row>
+    <row r="365" ht="15" customHeight="1">
+      <c r="A365" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B344" s="3" t="inlineStr">
+      <c r="B365" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C344" s="3" t="inlineStr">
+      <c r="C365" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D344" s="3" t="inlineStr">
+      <c r="D365" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="345" ht="30" customHeight="1">
-      <c r="A345" s="8" t="inlineStr">
+    <row r="366" ht="32" customHeight="1">
+      <c r="A366" s="8" t="inlineStr">
         <is>
           <t>자초</t>
         </is>
       </c>
-      <c r="B345" s="8" t="inlineStr">
+      <c r="B366" s="8" t="inlineStr">
         <is>
           <t>18.69%</t>
         </is>
       </c>
-      <c r="C345" s="8" t="inlineStr">
+      <c r="C366" s="8" t="inlineStr">
         <is>
           <t>자초(지치 뿌리) 추출, 항염·진정(자색소)</t>
         </is>
       </c>
-      <c r="D345" s="8" t="n"/>
-    </row>
-    <row r="346" ht="75" customHeight="1">
-      <c r="A346" s="8" t="inlineStr">
+      <c r="D366" s="8" t="n"/>
+    </row>
+    <row r="367" ht="80" customHeight="1">
+      <c r="A367" s="8" t="inlineStr">
         <is>
           <t>호호바오일</t>
         </is>
       </c>
-      <c r="B346" s="8" t="inlineStr">
+      <c r="B367" s="8" t="inlineStr">
         <is>
           <t>81.31%</t>
         </is>
       </c>
-      <c r="C346" s="8" t="inlineStr">
+      <c r="C367" s="8" t="inlineStr">
         <is>
           <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
-      <c r="D346" s="8" t="inlineStr">
+      <c r="D367" s="8" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="347" ht="14" customHeight="1">
-      <c r="A347" s="5" t="inlineStr">
+    <row r="368" ht="14" customHeight="1">
+      <c r="A368" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B347" s="6" t="n"/>
-      <c r="C347" s="6" t="n"/>
-      <c r="D347" s="6" t="n"/>
-    </row>
-    <row r="348" ht="15" customHeight="1">
-      <c r="A348" s="9" t="inlineStr">
+      <c r="B368" s="6" t="n"/>
+      <c r="C368" s="6" t="n"/>
+      <c r="D368" s="6" t="n"/>
+    </row>
+    <row r="369" ht="16" customHeight="1">
+      <c r="A369" s="9" t="inlineStr">
         <is>
           <t>Tip: 2~4주 숙성 뒤 사용하세요.</t>
         </is>
       </c>
-      <c r="B348" s="10" t="n"/>
-      <c r="C348" s="10" t="n"/>
-      <c r="D348" s="10" t="n"/>
-    </row>
-    <row r="349" ht="14" customHeight="1">
-      <c r="A349" s="5" t="inlineStr">
+      <c r="B369" s="10" t="n"/>
+      <c r="C369" s="10" t="n"/>
+      <c r="D369" s="10" t="n"/>
+    </row>
+    <row r="370" ht="14" customHeight="1">
+      <c r="A370" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B349" s="6" t="n"/>
-      <c r="C349" s="6" t="n"/>
-      <c r="D349" s="6" t="n"/>
-    </row>
-    <row r="350" ht="45" customHeight="1">
-      <c r="A350" s="9" t="inlineStr">
+      <c r="B370" s="6" t="n"/>
+      <c r="C370" s="6" t="n"/>
+      <c r="D370" s="6" t="n"/>
+    </row>
+    <row r="371" ht="48" customHeight="1">
+      <c r="A371" s="9" t="inlineStr">
         <is>
           <t>1. 병에 호호바오일을 넣고 자초를 넣어요.
 2. 수시로 흔들어 주세요. 자초오일완성됩니다. (자초 in 호호바) 보존기간은 6개월~1년입니다.</t>
         </is>
       </c>
-      <c r="B350" s="10" t="n"/>
-      <c r="C350" s="10" t="n"/>
-      <c r="D350" s="10" t="n"/>
-    </row>
-    <row r="351" ht="14" customHeight="1">
-      <c r="A351" s="5" t="inlineStr">
+      <c r="B371" s="10" t="n"/>
+      <c r="C371" s="10" t="n"/>
+      <c r="D371" s="10" t="n"/>
+    </row>
+    <row r="372" ht="14" customHeight="1">
+      <c r="A372" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B351" s="6" t="n"/>
-      <c r="C351" s="6" t="n"/>
-      <c r="D351" s="6" t="n"/>
-    </row>
-    <row r="352" ht="85.5" customHeight="1">
-      <c r="A352" s="10" t="n"/>
-      <c r="B352" s="10" t="n"/>
-      <c r="C352" s="10" t="n"/>
-      <c r="D352" s="10" t="n"/>
-    </row>
-    <row r="353" ht="6" customHeight="1"/>
-    <row r="354" ht="22" customHeight="1">
-      <c r="A354" s="1" t="inlineStr">
+      <c r="B372" s="6" t="n"/>
+      <c r="C372" s="6" t="n"/>
+      <c r="D372" s="6" t="n"/>
+    </row>
+    <row r="373" ht="85.5" customHeight="1">
+      <c r="A373" s="10" t="n"/>
+      <c r="B373" s="10" t="n"/>
+      <c r="C373" s="10" t="n"/>
+      <c r="D373" s="10" t="n"/>
+    </row>
+    <row r="374" ht="6" customHeight="1"/>
+    <row r="375" ht="22" customHeight="1">
+      <c r="A375" s="1" t="inlineStr">
         <is>
           <t>트러블 잠잠 롤볼    ↗ 원본</t>
         </is>
       </c>
-      <c r="B354" s="2" t="n"/>
-      <c r="C354" s="2" t="n"/>
-      <c r="D354" s="2" t="n"/>
-    </row>
-    <row r="355" ht="15" customHeight="1">
-      <c r="A355" s="3" t="inlineStr">
+      <c r="B375" s="2" t="n"/>
+      <c r="C375" s="2" t="n"/>
+      <c r="D375" s="2" t="n"/>
+    </row>
+    <row r="376" ht="15" customHeight="1">
+      <c r="A376" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B355" s="3" t="inlineStr">
+      <c r="B376" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C355" s="3" t="inlineStr">
+      <c r="C376" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D355" s="3" t="inlineStr">
+      <c r="D376" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="356" ht="75" customHeight="1">
-      <c r="A356" s="4" t="inlineStr">
+    <row r="377" ht="80" customHeight="1">
+      <c r="A377" s="4" t="inlineStr">
         <is>
           <t>골든호호바오일</t>
         </is>
       </c>
-      <c r="B356" s="4" t="inlineStr">
+      <c r="B377" s="4" t="inlineStr">
         <is>
           <t>8.6g</t>
         </is>
       </c>
-      <c r="C356" s="4" t="inlineStr">
+      <c r="C377" s="4" t="inlineStr">
         <is>
           <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
-      <c r="D356" s="4" t="inlineStr">
+      <c r="D377" s="4" t="inlineStr">
         <is>
           <t>올리브에스터오일</t>
         </is>
       </c>
     </row>
-    <row r="357" ht="60" customHeight="1">
-      <c r="A357" s="4" t="inlineStr">
+    <row r="378" ht="64" customHeight="1">
+      <c r="A378" s="4" t="inlineStr">
         <is>
           <t>살리실산(0.5%)</t>
         </is>
       </c>
-      <c r="B357" s="4" t="inlineStr">
+      <c r="B378" s="4" t="inlineStr">
         <is>
           <t>0.04g</t>
         </is>
       </c>
-      <c r="C357" s="4" t="inlineStr">
+      <c r="C378" s="4" t="inlineStr">
         <is>
           <t>바하, 지용성, 아스피린성분, 두꺼운 각질을 천천히 제거 화장품 성분이 잘 흡수되도록 도와줌, / 식약처 기준은 0.5%</t>
         </is>
       </c>
-      <c r="D357" s="4" t="n"/>
-    </row>
-    <row r="358" ht="45" customHeight="1">
-      <c r="A358" s="4" t="inlineStr">
+      <c r="D378" s="4" t="n"/>
+    </row>
+    <row r="379" ht="48" customHeight="1">
+      <c r="A379" s="4" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B358" s="4" t="inlineStr">
+      <c r="B379" s="4" t="inlineStr">
         <is>
           <t>15방울</t>
         </is>
       </c>
-      <c r="C358" s="4" t="inlineStr">
+      <c r="C379" s="4" t="inlineStr">
         <is>
           <t>7.5% 허브의 여왕, 진정, 항균 등 국소부위의 경우 원액사용가능</t>
         </is>
       </c>
-      <c r="D358" s="4" t="inlineStr">
+      <c r="D379" s="4" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="359" ht="75" customHeight="1">
-      <c r="A359" s="4" t="inlineStr">
+    <row r="380" ht="80" customHeight="1">
+      <c r="A380" s="4" t="inlineStr">
         <is>
           <t>티트리에센셜오일</t>
         </is>
       </c>
-      <c r="B359" s="4" t="inlineStr">
+      <c r="B380" s="4" t="inlineStr">
         <is>
           <t>15방울</t>
         </is>
       </c>
-      <c r="C359" s="4" t="inlineStr">
+      <c r="C380" s="4" t="inlineStr">
         <is>
           <t>7.5% 호주가 원산지, 원주민들은 외상이 있을 때 2차감염 등을 예방하기 위해 사용하고 여드름, 비듬, 가려움 등에 사용할 수 있음. 항균, 국소부위의 경우 원액사용가능.</t>
         </is>
       </c>
-      <c r="D359" s="4" t="inlineStr">
+      <c r="D380" s="4" t="inlineStr">
         <is>
           <t>유칼립투스EO 등</t>
         </is>
       </c>
     </row>
-    <row r="360" ht="14" customHeight="1">
-      <c r="A360" s="5" t="inlineStr">
+    <row r="381" ht="14" customHeight="1">
+      <c r="A381" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B360" s="6" t="n"/>
-      <c r="C360" s="6" t="n"/>
-      <c r="D360" s="6" t="n"/>
-    </row>
-    <row r="361" ht="465" customHeight="1">
-      <c r="A361" s="7" t="inlineStr">
+      <c r="B381" s="6" t="n"/>
+      <c r="C381" s="6" t="n"/>
+      <c r="D381" s="6" t="n"/>
+    </row>
+    <row r="382" ht="384" customHeight="1">
+      <c r="A382" s="7" t="inlineStr">
         <is>
           <t>여름에는
 기온이 1℃올라가면 피지나 땀 등이 10%증가합니다.
@@ -9727,8 +9836,14 @@
 '트러블스팟케어 롤볼 '
 골든호호바오일을 베이스로 이용해 끈적임이 없고 액상왁스라 보존기간도 깁니다.
 또 라벤더에센셜오일과 티트리에센셜오일 함량이 높은데요.
-얼굴 전체적으로 사용하시는 제품이 아니라
-트러블이 있는 부위에 집중적으로 발라주는 제품이라 15% 사용했어요.
+얼굴 전체적으로 사용하시는 제품이 아니라</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="112" customHeight="1">
+      <c r="A383" s="7" t="inlineStr">
+        <is>
+          <t>트러블이 있는 부위에 집중적으로 발라주는 제품이라 15% 사용했어요.
 잘 아시겠지만 라벤더EO와 티트리EO는 국소부위에 한해 원액을 사용하기도 합니다.
 살리실산을 0.5%정도 처방했는데요..
 바하라고도 하고 표면에 각질만 녹이는 아하와는
@@ -9738,18 +9853,18 @@
         </is>
       </c>
     </row>
-    <row r="362" ht="14" customHeight="1">
-      <c r="A362" s="5" t="inlineStr">
+    <row r="384" ht="14" customHeight="1">
+      <c r="A384" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B362" s="6" t="n"/>
-      <c r="C362" s="6" t="n"/>
-      <c r="D362" s="6" t="n"/>
-    </row>
-    <row r="363" ht="240" customHeight="1">
-      <c r="A363" s="7" t="inlineStr">
+      <c r="B384" s="6" t="n"/>
+      <c r="C384" s="6" t="n"/>
+      <c r="D384" s="6" t="n"/>
+    </row>
+    <row r="385" ht="256" customHeight="1">
+      <c r="A385" s="7" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.12ml 블랙캡 롤온 유리용기에 골든호호바오일을 계량하세요. 허브누리 롤볼 기준 높이 7.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml)
@@ -9766,172 +9881,174 @@
         </is>
       </c>
     </row>
-    <row r="364" ht="14" customHeight="1">
-      <c r="A364" s="5" t="inlineStr">
+    <row r="386" ht="14" customHeight="1">
+      <c r="A386" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B364" s="6" t="n"/>
-      <c r="C364" s="6" t="n"/>
-      <c r="D364" s="6" t="n"/>
-    </row>
-    <row r="365" ht="256.5" customHeight="1"/>
-    <row r="366" ht="6" customHeight="1"/>
-    <row r="367" ht="22" customHeight="1">
-      <c r="A367" s="1" t="inlineStr">
+      <c r="B386" s="6" t="n"/>
+      <c r="C386" s="6" t="n"/>
+      <c r="D386" s="6" t="n"/>
+    </row>
+    <row r="387" ht="85.5" customHeight="1"/>
+    <row r="388" ht="85.5" customHeight="1"/>
+    <row r="389" ht="85.5" customHeight="1"/>
+    <row r="390" ht="6" customHeight="1"/>
+    <row r="391" ht="22" customHeight="1">
+      <c r="A391" s="1" t="inlineStr">
         <is>
           <t>튼살예방오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B367" s="2" t="n"/>
-      <c r="C367" s="2" t="n"/>
-      <c r="D367" s="2" t="n"/>
-    </row>
-    <row r="368" ht="15" customHeight="1">
-      <c r="A368" s="3" t="inlineStr">
+      <c r="B391" s="2" t="n"/>
+      <c r="C391" s="2" t="n"/>
+      <c r="D391" s="2" t="n"/>
+    </row>
+    <row r="392" ht="15" customHeight="1">
+      <c r="A392" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B368" s="3" t="inlineStr">
+      <c r="B392" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C368" s="3" t="inlineStr">
+      <c r="C392" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D368" s="3" t="inlineStr">
+      <c r="D392" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="369" ht="75" customHeight="1">
-      <c r="A369" s="8" t="inlineStr">
+    <row r="393" ht="80" customHeight="1">
+      <c r="A393" s="8" t="inlineStr">
         <is>
           <t>마카다미아넛오일</t>
         </is>
       </c>
-      <c r="B369" s="8" t="inlineStr">
+      <c r="B393" s="8" t="inlineStr">
         <is>
           <t>52.36%</t>
         </is>
       </c>
-      <c r="C369" s="8" t="inlineStr">
+      <c r="C393" s="8" t="inlineStr">
         <is>
           <t>나이가 들면 없어지는 성분이고 다른 식물성 오일에는 없는 '팔마톨레익산' 함유, 호호바오일 대용으로도 사용될 만큼 사용감이 가볍고 흡수력이 좋음</t>
         </is>
       </c>
-      <c r="D369" s="8" t="inlineStr">
+      <c r="D393" s="8" t="inlineStr">
         <is>
           <t>골든호호바, / 아르간오일 등</t>
         </is>
       </c>
     </row>
-    <row r="370" ht="45" customHeight="1">
-      <c r="A370" s="8" t="inlineStr">
+    <row r="394" ht="48" customHeight="1">
+      <c r="A394" s="8" t="inlineStr">
         <is>
           <t>로즈힙오일</t>
         </is>
       </c>
-      <c r="B370" s="8" t="inlineStr">
+      <c r="B394" s="8" t="inlineStr">
         <is>
           <t>41.88%</t>
         </is>
       </c>
-      <c r="C370" s="8" t="inlineStr">
+      <c r="C394" s="8" t="inlineStr">
         <is>
           <t>들장미열매 압착 혹은 용매추출, / 주름, 노화피부관리에사용함</t>
         </is>
       </c>
-      <c r="D370" s="8" t="inlineStr">
+      <c r="D394" s="8" t="inlineStr">
         <is>
           <t>아르간,보리지, 푸에라리아오일, 카렌듈라오일 등</t>
         </is>
       </c>
     </row>
-    <row r="371" ht="60" customHeight="1">
-      <c r="A371" s="8" t="inlineStr">
+    <row r="395" ht="64" customHeight="1">
+      <c r="A395" s="8" t="inlineStr">
         <is>
           <t>토코페롤</t>
         </is>
       </c>
-      <c r="B371" s="8" t="inlineStr">
+      <c r="B395" s="8" t="inlineStr">
         <is>
           <t>5.24%</t>
         </is>
       </c>
-      <c r="C371" s="8" t="inlineStr">
+      <c r="C395" s="8" t="inlineStr">
         <is>
           <t>토코페롤, 지용성 보존제, 산화방지, 탄력,천연비타민E는 특유의 냄새가 있습니다. 감안하시고 대체해서 사용하세요.</t>
         </is>
       </c>
-      <c r="D371" s="8" t="inlineStr">
+      <c r="D395" s="8" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="372" ht="75" customHeight="1">
-      <c r="A372" s="8" t="inlineStr">
+    <row r="396" ht="80" customHeight="1">
+      <c r="A396" s="8" t="inlineStr">
         <is>
           <t>네롤리 에센셜오일</t>
         </is>
       </c>
-      <c r="B372" s="8" t="inlineStr">
+      <c r="B396" s="8" t="inlineStr">
         <is>
           <t>0.1%</t>
         </is>
       </c>
-      <c r="C372" s="8" t="inlineStr">
+      <c r="C396" s="8" t="inlineStr">
         <is>
           <t>오렌지블라썸, 비터오렌지꽃에센셜오일, 이탈리아의 네롤리공주가 즐겨 사용했다해서 네롤리에센셜오일라고도 부른다. 재생, 민감 피부사용, 임산부튼살예방관리에도 사용</t>
         </is>
       </c>
-      <c r="D372" s="8" t="inlineStr">
+      <c r="D396" s="8" t="inlineStr">
         <is>
           <t>로즈, 자스민, 프랑킨센스, 로먼캐모마일, 라벤더 등 원하는에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="373" ht="30" customHeight="1">
-      <c r="A373" s="8" t="inlineStr">
+    <row r="397" ht="48" customHeight="1">
+      <c r="A397" s="8" t="inlineStr">
         <is>
           <t>만다린EO</t>
         </is>
       </c>
-      <c r="B373" s="8" t="inlineStr">
+      <c r="B397" s="8" t="inlineStr">
         <is>
           <t>0.42%</t>
         </is>
       </c>
-      <c r="C373" s="8" t="inlineStr">
+      <c r="C397" s="8" t="inlineStr">
         <is>
           <t>귤껍질오일, / 임신기간 영아에게 안전하게 사용, / 모든 피부사용</t>
         </is>
       </c>
-      <c r="D373" s="8" t="inlineStr">
+      <c r="D397" s="8" t="inlineStr">
         <is>
           <t>오렌지, 버가못, 그레이프프룻 등 감귤류 오일</t>
         </is>
       </c>
     </row>
-    <row r="374" ht="14" customHeight="1">
-      <c r="A374" s="5" t="inlineStr">
+    <row r="398" ht="14" customHeight="1">
+      <c r="A398" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B374" s="6" t="n"/>
-      <c r="C374" s="6" t="n"/>
-      <c r="D374" s="6" t="n"/>
-    </row>
-    <row r="375" ht="255" customHeight="1">
-      <c r="A375" s="9" t="inlineStr">
+      <c r="B398" s="6" t="n"/>
+      <c r="C398" s="6" t="n"/>
+      <c r="D398" s="6" t="n"/>
+    </row>
+    <row r="399" ht="272" customHeight="1">
+      <c r="A399" s="9" t="inlineStr">
         <is>
           <t>▶ 튼살은 살이 건조하거나 팽창하면서 튼 피부 표면상의 문제가 아니라 피부 심층인 진피층 이하의 조직 손상으로 인한 피부 흉터로 이해해야 한답니다. 즉, 진피층의 손상으로 인해 탄성조직의 힘몰과 함께 지지조직이 약화되고 손상을 받은 피부 흉터라고 생각하시면 되요. 튼살은 한번 생기면 잘 없어지지가 않는답니다. 임산부들은 임신 후기로 갈수록 급격히 체중이 늘어나 아랫배나 가슴부위에 튼살이 생기기 쉬워요. 처음에는 가늘고 짧은 붉은색이지만 점차 색이 진해지며, 출산 후에도 튼살은 그대로 남게 됩니다. 임신기간 중에 생긴 튼살은 예방이 상책입니다. 임신 5개월부터 뱃속에 애기를 어루만지는 느낌으로 매일 또는 2~3일에 한번씩 자주^^해주세요.
 ▶튼살 예방 7계명
@@ -9944,202 +10061,202 @@
 7. 식단을 조절하며 몸이 붓지 않도록 한다.</t>
         </is>
       </c>
-      <c r="B375" s="10" t="n"/>
-      <c r="C375" s="10" t="n"/>
-      <c r="D375" s="10" t="n"/>
-    </row>
-    <row r="376" ht="14" customHeight="1">
-      <c r="A376" s="5" t="inlineStr">
+      <c r="B399" s="10" t="n"/>
+      <c r="C399" s="10" t="n"/>
+      <c r="D399" s="10" t="n"/>
+    </row>
+    <row r="400" ht="14" customHeight="1">
+      <c r="A400" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B376" s="6" t="n"/>
-      <c r="C376" s="6" t="n"/>
-      <c r="D376" s="6" t="n"/>
-    </row>
-    <row r="377" ht="30" customHeight="1">
-      <c r="A377" s="9" t="inlineStr">
+      <c r="B400" s="6" t="n"/>
+      <c r="C400" s="6" t="n"/>
+      <c r="D400" s="6" t="n"/>
+    </row>
+    <row r="401" ht="32" customHeight="1">
+      <c r="A401" s="9" t="inlineStr">
         <is>
           <t>만들기 방법
 로즈힙, 마카데미아넛 계량하고, 에센셜오일 넣고 저어주기. 용기에 부으면 완성^^</t>
         </is>
       </c>
-      <c r="B377" s="10" t="n"/>
-      <c r="C377" s="10" t="n"/>
-      <c r="D377" s="10" t="n"/>
-    </row>
-    <row r="378" ht="14" customHeight="1">
-      <c r="A378" s="5" t="inlineStr">
+      <c r="B401" s="10" t="n"/>
+      <c r="C401" s="10" t="n"/>
+      <c r="D401" s="10" t="n"/>
+    </row>
+    <row r="402" ht="14" customHeight="1">
+      <c r="A402" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B378" s="6" t="n"/>
-      <c r="C378" s="6" t="n"/>
-      <c r="D378" s="6" t="n"/>
-    </row>
-    <row r="379" ht="85.5" customHeight="1">
-      <c r="A379" s="10" t="n"/>
-      <c r="B379" s="10" t="n"/>
-      <c r="C379" s="10" t="n"/>
-      <c r="D379" s="10" t="n"/>
-    </row>
-    <row r="380" ht="6" customHeight="1"/>
-    <row r="381" ht="22" customHeight="1">
-      <c r="A381" s="1" t="inlineStr">
+      <c r="B402" s="6" t="n"/>
+      <c r="C402" s="6" t="n"/>
+      <c r="D402" s="6" t="n"/>
+    </row>
+    <row r="403" ht="85.5" customHeight="1">
+      <c r="A403" s="10" t="n"/>
+      <c r="B403" s="10" t="n"/>
+      <c r="C403" s="10" t="n"/>
+      <c r="D403" s="10" t="n"/>
+    </row>
+    <row r="404" ht="6" customHeight="1"/>
+    <row r="405" ht="22" customHeight="1">
+      <c r="A405" s="1" t="inlineStr">
         <is>
           <t>스쿠알란 바디오일    ↗ 원본</t>
         </is>
       </c>
-      <c r="B381" s="2" t="n"/>
-      <c r="C381" s="2" t="n"/>
-      <c r="D381" s="2" t="n"/>
-    </row>
-    <row r="382" ht="15" customHeight="1">
-      <c r="A382" s="3" t="inlineStr">
+      <c r="B405" s="2" t="n"/>
+      <c r="C405" s="2" t="n"/>
+      <c r="D405" s="2" t="n"/>
+    </row>
+    <row r="406" ht="15" customHeight="1">
+      <c r="A406" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B382" s="3" t="inlineStr">
+      <c r="B406" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C382" s="3" t="inlineStr">
+      <c r="C406" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D382" s="3" t="inlineStr">
+      <c r="D406" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="383" ht="45" customHeight="1">
-      <c r="A383" s="4" t="inlineStr">
+    <row r="407" ht="48" customHeight="1">
+      <c r="A407" s="4" t="inlineStr">
         <is>
           <t>유기농 스쿠알란</t>
         </is>
       </c>
-      <c r="B383" s="4" t="inlineStr">
+      <c r="B407" s="4" t="inlineStr">
         <is>
           <t>45g</t>
         </is>
       </c>
-      <c r="C383" s="4" t="inlineStr">
+      <c r="C407" s="4" t="inlineStr">
         <is>
           <t>피지의 약 12%를 구성하는 성분, / 스쿠알렌을 수소첨가하여 안정화한 성분</t>
         </is>
       </c>
-      <c r="D383" s="4" t="inlineStr">
+      <c r="D407" s="4" t="inlineStr">
         <is>
           <t>녹차씨오일</t>
         </is>
       </c>
     </row>
-    <row r="384" ht="60" customHeight="1">
-      <c r="A384" s="4" t="inlineStr">
+    <row r="408" ht="64" customHeight="1">
+      <c r="A408" s="4" t="inlineStr">
         <is>
           <t>카프릴릭 카프릭트리글리세라이드 (MCT)</t>
         </is>
       </c>
-      <c r="B384" s="4" t="inlineStr">
+      <c r="B408" s="4" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C384" s="4" t="inlineStr">
+      <c r="C408" s="4" t="inlineStr">
         <is>
           <t>코코넛, 팜 등에서 유래, / 카프릴릭산(C8)와 카프릭산(C10)을 / 글리세린과 합성시켜 만든 원료, / 가볍고 빠른 흡수력</t>
         </is>
       </c>
-      <c r="D384" s="4" t="inlineStr">
+      <c r="D408" s="4" t="inlineStr">
         <is>
           <t>유기농 세티올 / 에스터오일</t>
         </is>
       </c>
     </row>
-    <row r="385" ht="15" customHeight="1">
-      <c r="A385" s="4" t="inlineStr">
+    <row r="409" ht="16" customHeight="1">
+      <c r="A409" s="4" t="inlineStr">
         <is>
           <t>호호바오일(골든)</t>
         </is>
       </c>
-      <c r="B385" s="4" t="inlineStr">
+      <c r="B409" s="4" t="inlineStr">
         <is>
           <t>19.2g</t>
         </is>
       </c>
-      <c r="C385" s="4" t="inlineStr">
+      <c r="C409" s="4" t="inlineStr">
         <is>
           <t>피지성분과 비슷, / 빠른흡수</t>
         </is>
       </c>
-      <c r="D385" s="4" t="inlineStr">
+      <c r="D409" s="4" t="inlineStr">
         <is>
           <t>동백오일, 아르간오일</t>
         </is>
       </c>
     </row>
-    <row r="386" ht="30" customHeight="1">
-      <c r="A386" s="4" t="inlineStr">
+    <row r="410" ht="32" customHeight="1">
+      <c r="A410" s="4" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B386" s="4" t="inlineStr">
+      <c r="B410" s="4" t="inlineStr">
         <is>
           <t>0.5g(10방울)</t>
         </is>
       </c>
-      <c r="C386" s="4" t="inlineStr">
+      <c r="C410" s="4" t="inlineStr">
         <is>
           <t>산화방지</t>
         </is>
       </c>
-      <c r="D386" s="4" t="inlineStr">
+      <c r="D410" s="4" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
     </row>
-    <row r="387" ht="15" customHeight="1">
-      <c r="A387" s="4" t="inlineStr">
+    <row r="411" ht="16" customHeight="1">
+      <c r="A411" s="4" t="inlineStr">
         <is>
           <t>버가못FCF</t>
         </is>
       </c>
-      <c r="B387" s="4" t="inlineStr">
+      <c r="B411" s="4" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C387" s="4" t="inlineStr">
+      <c r="C411" s="4" t="inlineStr">
         <is>
           <t>감귤류, 피부진정, / 광독성 없음</t>
         </is>
       </c>
-      <c r="D387" s="4" t="inlineStr">
+      <c r="D411" s="4" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="388" ht="14" customHeight="1">
-      <c r="A388" s="5" t="inlineStr">
+    <row r="412" ht="14" customHeight="1">
+      <c r="A412" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B388" s="6" t="n"/>
-      <c r="C388" s="6" t="n"/>
-      <c r="D388" s="6" t="n"/>
-    </row>
-    <row r="389" ht="255" customHeight="1">
-      <c r="A389" s="7" t="inlineStr">
+      <c r="B412" s="6" t="n"/>
+      <c r="C412" s="6" t="n"/>
+      <c r="D412" s="6" t="n"/>
+    </row>
+    <row r="413" ht="272" customHeight="1">
+      <c r="A413" s="7" t="inlineStr">
         <is>
           <t>샤워 후 촉촉함 그대로, 끈적임 없는!
 스쿠알란 바디오일
@@ -10161,18 +10278,18 @@
         </is>
       </c>
     </row>
-    <row r="390" ht="14" customHeight="1">
-      <c r="A390" s="5" t="inlineStr">
+    <row r="414" ht="14" customHeight="1">
+      <c r="A414" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B390" s="6" t="n"/>
-      <c r="C390" s="6" t="n"/>
-      <c r="D390" s="6" t="n"/>
-    </row>
-    <row r="391" ht="75" customHeight="1">
-      <c r="A391" s="7" t="inlineStr">
+      <c r="B414" s="6" t="n"/>
+      <c r="C414" s="6" t="n"/>
+      <c r="D414" s="6" t="n"/>
+    </row>
+    <row r="415" ht="80" customHeight="1">
+      <c r="A415" s="7" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 150ml 용기에 모든 재료를 계량해주세요.
@@ -10182,216 +10299,216 @@
         </is>
       </c>
     </row>
-    <row r="392" ht="14" customHeight="1">
-      <c r="A392" s="5" t="inlineStr">
+    <row r="416" ht="14" customHeight="1">
+      <c r="A416" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B392" s="6" t="n"/>
-      <c r="C392" s="6" t="n"/>
-      <c r="D392" s="6" t="n"/>
-    </row>
-    <row r="393" ht="85.5" customHeight="1"/>
-    <row r="394" ht="6" customHeight="1"/>
-    <row r="395" ht="22" customHeight="1">
-      <c r="A395" s="1" t="inlineStr">
+      <c r="B416" s="6" t="n"/>
+      <c r="C416" s="6" t="n"/>
+      <c r="D416" s="6" t="n"/>
+    </row>
+    <row r="417" ht="85.5" customHeight="1"/>
+    <row r="418" ht="6" customHeight="1"/>
+    <row r="419" ht="22" customHeight="1">
+      <c r="A419" s="1" t="inlineStr">
         <is>
           <t>스쿠알란 슬로우 앰플(오일)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B395" s="2" t="n"/>
-      <c r="C395" s="2" t="n"/>
-      <c r="D395" s="2" t="n"/>
-    </row>
-    <row r="396" ht="15" customHeight="1">
-      <c r="A396" s="3" t="inlineStr">
+      <c r="B419" s="2" t="n"/>
+      <c r="C419" s="2" t="n"/>
+      <c r="D419" s="2" t="n"/>
+    </row>
+    <row r="420" ht="15" customHeight="1">
+      <c r="A420" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B396" s="3" t="inlineStr">
+      <c r="B420" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C396" s="3" t="inlineStr">
+      <c r="C420" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D396" s="3" t="inlineStr">
+      <c r="D420" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="397" ht="45" customHeight="1">
-      <c r="A397" s="8" t="inlineStr">
+    <row r="421" ht="48" customHeight="1">
+      <c r="A421" s="8" t="inlineStr">
         <is>
           <t>유기농 스쿠알란</t>
         </is>
       </c>
-      <c r="B397" s="8" t="inlineStr">
+      <c r="B421" s="8" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C397" s="8" t="inlineStr">
+      <c r="C421" s="8" t="inlineStr">
         <is>
           <t>피지의 약 12%를 구성하는 성분, / 스쿠알렌을 수소첨가하여 안정화한 성분</t>
         </is>
       </c>
-      <c r="D397" s="8" t="inlineStr">
+      <c r="D421" s="8" t="inlineStr">
         <is>
           <t>세라마이드(지용성)</t>
         </is>
       </c>
     </row>
-    <row r="398" ht="60" customHeight="1">
-      <c r="A398" s="8" t="inlineStr">
+    <row r="422" ht="64" customHeight="1">
+      <c r="A422" s="8" t="inlineStr">
         <is>
           <t>카프릴릭 카프릭트리글리세라이드 (MCT)</t>
         </is>
       </c>
-      <c r="B398" s="8" t="inlineStr">
+      <c r="B422" s="8" t="inlineStr">
         <is>
           <t>35g</t>
         </is>
       </c>
-      <c r="C398" s="8" t="inlineStr">
+      <c r="C422" s="8" t="inlineStr">
         <is>
           <t>코코넛, 팜 등에서 유래, / 카프릴릭산(C8)와 카프릭산(C10)을 / 글리세린과 합성시켜 만든 원료, / 가볍고 빠른 흡수력</t>
         </is>
       </c>
-      <c r="D398" s="8" t="inlineStr">
+      <c r="D422" s="8" t="inlineStr">
         <is>
           <t>유기농 세티올 / 에스터오일</t>
         </is>
       </c>
     </row>
-    <row r="399" ht="45" customHeight="1">
-      <c r="A399" s="8" t="inlineStr">
+    <row r="423" ht="64" customHeight="1">
+      <c r="A423" s="8" t="inlineStr">
         <is>
           <t>보르피린</t>
         </is>
       </c>
-      <c r="B399" s="8" t="inlineStr">
+      <c r="B423" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C399" s="8" t="inlineStr">
+      <c r="C423" s="8" t="inlineStr">
         <is>
           <t>지모추출, 지방증식 볼륨업</t>
         </is>
       </c>
-      <c r="D399" s="8" t="inlineStr">
+      <c r="D423" s="8" t="inlineStr">
         <is>
           <t>10 g(10%)을 원한다면 로즈워터를 5g 줄여서 40g이 되도록 해주세요.</t>
         </is>
       </c>
     </row>
-    <row r="400" ht="45" customHeight="1">
-      <c r="A400" s="8" t="inlineStr">
+    <row r="424" ht="48" customHeight="1">
+      <c r="A424" s="8" t="inlineStr">
         <is>
           <t>(정제) 호호바오일</t>
         </is>
       </c>
-      <c r="B400" s="8" t="inlineStr">
+      <c r="B424" s="8" t="inlineStr">
         <is>
           <t>19g</t>
         </is>
       </c>
-      <c r="C400" s="8" t="inlineStr">
+      <c r="C424" s="8" t="inlineStr">
         <is>
           <t>피지성분과 비슷, 빠른 흡수 / ※ 호호바오일(골든) 사용 시 완성품이 노란빛을 띨 수 있습니다.</t>
         </is>
       </c>
-      <c r="D400" s="8" t="inlineStr">
+      <c r="D424" s="8" t="inlineStr">
         <is>
           <t>올리브오일, 포도씨, 해바라기 등 다양한 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="401" ht="15" customHeight="1">
-      <c r="A401" s="8" t="inlineStr">
+    <row r="425" ht="16" customHeight="1">
+      <c r="A425" s="8" t="inlineStr">
         <is>
           <t>알파비사보롤</t>
         </is>
       </c>
-      <c r="B401" s="8" t="inlineStr">
+      <c r="B425" s="8" t="inlineStr">
         <is>
           <t>0.2g</t>
         </is>
       </c>
-      <c r="C401" s="8" t="inlineStr">
+      <c r="C425" s="8" t="inlineStr">
         <is>
           <t>식약처 미백고시 원료</t>
         </is>
       </c>
-      <c r="D401" s="8" t="inlineStr">
+      <c r="D425" s="8" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="402" ht="45" customHeight="1">
-      <c r="A402" s="8" t="inlineStr">
+    <row r="426" ht="48" customHeight="1">
+      <c r="A426" s="8" t="inlineStr">
         <is>
           <t>비타민E</t>
         </is>
       </c>
-      <c r="B402" s="8" t="inlineStr">
+      <c r="B426" s="8" t="inlineStr">
         <is>
           <t>0.5g</t>
         </is>
       </c>
-      <c r="C402" s="8" t="inlineStr">
+      <c r="C426" s="8" t="inlineStr">
         <is>
           <t>산화방지</t>
         </is>
       </c>
-      <c r="D402" s="8" t="inlineStr">
+      <c r="D426" s="8" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="403" ht="30" customHeight="1">
-      <c r="A403" s="8" t="inlineStr">
+    <row r="427" ht="32" customHeight="1">
+      <c r="A427" s="8" t="inlineStr">
         <is>
           <t>로즈파워 블렌딩오일</t>
         </is>
       </c>
-      <c r="B403" s="8" t="inlineStr">
+      <c r="B427" s="8" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C403" s="8" t="inlineStr">
+      <c r="C427" s="8" t="inlineStr">
         <is>
           <t>로즈앱솔루트, 로즈제라늄, / 로즈우드, 프랑킨센스 블렌딩오일</t>
         </is>
       </c>
-      <c r="D403" s="8" t="inlineStr">
+      <c r="D427" s="8" t="inlineStr">
         <is>
           <t>원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="404" ht="14" customHeight="1">
-      <c r="A404" s="5" t="inlineStr">
+    <row r="428" ht="14" customHeight="1">
+      <c r="A428" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B404" s="6" t="n"/>
-      <c r="C404" s="6" t="n"/>
-      <c r="D404" s="6" t="n"/>
-    </row>
-    <row r="405" ht="510" customHeight="1">
-      <c r="A405" s="9" t="inlineStr">
+      <c r="B428" s="6" t="n"/>
+      <c r="C428" s="6" t="n"/>
+      <c r="D428" s="6" t="n"/>
+    </row>
+    <row r="429" ht="384" customHeight="1">
+      <c r="A429" s="9" t="inlineStr">
         <is>
           <t>꺼진 볼륨 · 윤광 집중 솔루션
 스쿠알란 슬로우 앰플(오일)
@@ -10416,8 +10533,17 @@
 ▷이마 주름 케어
 이마에 오일 바른 뒤, 검지와 중지로 원을 그리거나
 촘촘한 'X'자 모양을 그리며 근육을 부드럽게 풀어주세요.
-▷눈가 주름 케어
-눈가 주름을 예방하고 개선하려면 피부에 마찰을 주지 않는 것이 핵심입니다.
+▷눈가 주름 케어</t>
+        </is>
+      </c>
+      <c r="B429" s="10" t="n"/>
+      <c r="C429" s="10" t="n"/>
+      <c r="D429" s="10" t="n"/>
+    </row>
+    <row r="430" ht="160" customHeight="1">
+      <c r="A430" s="9" t="inlineStr">
+        <is>
+          <t>눈가 주름을 예방하고 개선하려면 피부에 마찰을 주지 않는 것이 핵심입니다.
 오일을 바른 후, 가장 힘이 약한 약지를 이용해 혈점을 가볍게 누르고
 근육을 부드럽게 풀어주세요
 ▷팔자 주름 케어
@@ -10429,22 +10555,22 @@
 건조한 손/끝과 손톱 부위에 발라 촉촉하게 만들어주세요.</t>
         </is>
       </c>
-      <c r="B405" s="10" t="n"/>
-      <c r="C405" s="10" t="n"/>
-      <c r="D405" s="10" t="n"/>
-    </row>
-    <row r="406" ht="14" customHeight="1">
-      <c r="A406" s="5" t="inlineStr">
+      <c r="B430" s="10" t="n"/>
+      <c r="C430" s="10" t="n"/>
+      <c r="D430" s="10" t="n"/>
+    </row>
+    <row r="431" ht="14" customHeight="1">
+      <c r="A431" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B406" s="6" t="n"/>
-      <c r="C406" s="6" t="n"/>
-      <c r="D406" s="6" t="n"/>
-    </row>
-    <row r="407" ht="75" customHeight="1">
-      <c r="A407" s="9" t="inlineStr">
+      <c r="B431" s="6" t="n"/>
+      <c r="C431" s="6" t="n"/>
+      <c r="D431" s="6" t="n"/>
+    </row>
+    <row r="432" ht="80" customHeight="1">
+      <c r="A432" s="9" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 150ml 용기에 모든 재료를 계량해주세요.
@@ -10453,285 +10579,310 @@
 ※150ml에 내용물을 담으면 가득 차지 않습니다.</t>
         </is>
       </c>
-      <c r="B407" s="10" t="n"/>
-      <c r="C407" s="10" t="n"/>
-      <c r="D407" s="10" t="n"/>
-    </row>
-    <row r="408" ht="14" customHeight="1">
-      <c r="A408" s="5" t="inlineStr">
+      <c r="B432" s="10" t="n"/>
+      <c r="C432" s="10" t="n"/>
+      <c r="D432" s="10" t="n"/>
+    </row>
+    <row r="433" ht="14" customHeight="1">
+      <c r="A433" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B408" s="6" t="n"/>
-      <c r="C408" s="6" t="n"/>
-      <c r="D408" s="6" t="n"/>
-    </row>
-    <row r="409" ht="85.5" customHeight="1">
-      <c r="A409" s="10" t="n"/>
-      <c r="B409" s="10" t="n"/>
-      <c r="C409" s="10" t="n"/>
-      <c r="D409" s="10" t="n"/>
-    </row>
-    <row r="410" ht="6" customHeight="1"/>
+      <c r="B433" s="6" t="n"/>
+      <c r="C433" s="6" t="n"/>
+      <c r="D433" s="6" t="n"/>
+    </row>
+    <row r="434" ht="85.5" customHeight="1">
+      <c r="A434" s="10" t="n"/>
+      <c r="B434" s="10" t="n"/>
+      <c r="C434" s="10" t="n"/>
+      <c r="D434" s="10" t="n"/>
+    </row>
+    <row r="435" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="222">
-    <mergeCell ref="A263:D263"/>
-    <mergeCell ref="A321:D321"/>
+  <mergeCells count="247">
     <mergeCell ref="A303:D303"/>
     <mergeCell ref="A144:D144"/>
     <mergeCell ref="A159:D159"/>
     <mergeCell ref="A122:D122"/>
     <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A224:D224"/>
-    <mergeCell ref="A395:D395"/>
+    <mergeCell ref="A215:D215"/>
+    <mergeCell ref="A386:D386"/>
+    <mergeCell ref="A373:D373"/>
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A134:D134"/>
-    <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A323:D323"/>
-    <mergeCell ref="A348:D348"/>
+    <mergeCell ref="A200:D200"/>
+    <mergeCell ref="A318:D318"/>
+    <mergeCell ref="A81:D81"/>
+    <mergeCell ref="A265:D265"/>
+    <mergeCell ref="A161:D161"/>
     <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A288:D288"/>
+    <mergeCell ref="A357:D357"/>
+    <mergeCell ref="A372:D372"/>
     <mergeCell ref="A249:D249"/>
-    <mergeCell ref="A320:D320"/>
+    <mergeCell ref="A289:D289"/>
+    <mergeCell ref="A202:D202"/>
     <mergeCell ref="A176:D176"/>
     <mergeCell ref="A258:D258"/>
+    <mergeCell ref="A314:D314"/>
+    <mergeCell ref="A329:D329"/>
     <mergeCell ref="A347:D347"/>
+    <mergeCell ref="A412:D412"/>
     <mergeCell ref="A304:D304"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A64:D64"/>
     <mergeCell ref="A186:D186"/>
     <mergeCell ref="A257:D257"/>
     <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A226:D226"/>
     <mergeCell ref="A51:D51"/>
     <mergeCell ref="A107:D107"/>
-    <mergeCell ref="A226:D226"/>
-    <mergeCell ref="A260:D260"/>
-    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A266:D266"/>
     <mergeCell ref="A291:D291"/>
-    <mergeCell ref="A349:D349"/>
+    <mergeCell ref="A358:D358"/>
     <mergeCell ref="A70:D70"/>
     <mergeCell ref="A241:D241"/>
-    <mergeCell ref="A250:D250"/>
+    <mergeCell ref="A315:D315"/>
+    <mergeCell ref="A228:D228"/>
+    <mergeCell ref="A399:D399"/>
+    <mergeCell ref="A54:D54"/>
     <mergeCell ref="A360:D360"/>
     <mergeCell ref="A172:D172"/>
+    <mergeCell ref="A212:D212"/>
+    <mergeCell ref="A243:D243"/>
+    <mergeCell ref="A283:D283"/>
     <mergeCell ref="A305:D305"/>
-    <mergeCell ref="A252:D252"/>
-    <mergeCell ref="A283:D283"/>
-    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A277:D277"/>
     <mergeCell ref="A292:D292"/>
     <mergeCell ref="A108:D108"/>
-    <mergeCell ref="A286:D286"/>
     <mergeCell ref="A375:D375"/>
     <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A236:D236"/>
+    <mergeCell ref="A267:D267"/>
     <mergeCell ref="A149:D149"/>
+    <mergeCell ref="A214:D214"/>
+    <mergeCell ref="A163:D163"/>
     <mergeCell ref="A341:D341"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A223:D223"/>
+    <mergeCell ref="A385:D385"/>
     <mergeCell ref="A294:D294"/>
-    <mergeCell ref="A306:D306"/>
-    <mergeCell ref="A390:D390"/>
-    <mergeCell ref="A195:D195"/>
-    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="A204:D204"/>
     <mergeCell ref="A42:D42"/>
     <mergeCell ref="A269:D269"/>
+    <mergeCell ref="A278:D278"/>
     <mergeCell ref="A361:D361"/>
     <mergeCell ref="A188:D188"/>
+    <mergeCell ref="A126:D126"/>
+    <mergeCell ref="A141:D141"/>
     <mergeCell ref="A259:D259"/>
+    <mergeCell ref="A311:D311"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="A53:D53"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A206:D206"/>
     <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A377:D377"/>
-    <mergeCell ref="A392:D392"/>
+    <mergeCell ref="A433:D433"/>
+    <mergeCell ref="A125:D125"/>
+    <mergeCell ref="A190:D190"/>
     <mergeCell ref="A117:D117"/>
     <mergeCell ref="A199:D199"/>
+    <mergeCell ref="A230:D230"/>
+    <mergeCell ref="A111:D111"/>
+    <mergeCell ref="A401:D401"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A245:D245"/>
     <mergeCell ref="A362:D362"/>
+    <mergeCell ref="A127:D127"/>
     <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A319:D319"/>
+    <mergeCell ref="A232:D232"/>
+    <mergeCell ref="A403:D403"/>
     <mergeCell ref="A142:D142"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A182:D182"/>
-    <mergeCell ref="A98:D98"/>
-    <mergeCell ref="A169:D169"/>
+    <mergeCell ref="A216:D216"/>
+    <mergeCell ref="A191:D191"/>
+    <mergeCell ref="A387:D387"/>
     <mergeCell ref="A225:D225"/>
-    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A296:D296"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A88:D88"/>
+    <mergeCell ref="A359:D359"/>
     <mergeCell ref="A162:D162"/>
+    <mergeCell ref="A218:D218"/>
     <mergeCell ref="A227:D227"/>
+    <mergeCell ref="A316:D316"/>
+    <mergeCell ref="A398:D398"/>
+    <mergeCell ref="A128:D128"/>
+    <mergeCell ref="A429:D429"/>
     <mergeCell ref="A364:D364"/>
-    <mergeCell ref="A208:D208"/>
-    <mergeCell ref="A379:D379"/>
+    <mergeCell ref="A177:D177"/>
+    <mergeCell ref="A90:D90"/>
     <mergeCell ref="A268:D268"/>
+    <mergeCell ref="A413:D413"/>
     <mergeCell ref="A388:D388"/>
-    <mergeCell ref="A282:D282"/>
-    <mergeCell ref="A136:D136"/>
-    <mergeCell ref="A192:D192"/>
-    <mergeCell ref="A74:D74"/>
     <mergeCell ref="A105:D105"/>
     <mergeCell ref="A145:D145"/>
-    <mergeCell ref="A376:D376"/>
+    <mergeCell ref="A428:D428"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="A272:D272"/>
     <mergeCell ref="A210:D210"/>
     <mergeCell ref="A381:D381"/>
-    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A179:D179"/>
+    <mergeCell ref="A302:D302"/>
+    <mergeCell ref="A415:D415"/>
     <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A194:D194"/>
-    <mergeCell ref="A322:D322"/>
-    <mergeCell ref="A374:D374"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A313:D313"/>
+    <mergeCell ref="A307:D307"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A203:D203"/>
     <mergeCell ref="A116:D116"/>
-    <mergeCell ref="A181:D181"/>
     <mergeCell ref="A405:D405"/>
+    <mergeCell ref="A414:D414"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A184:D184"/>
+    <mergeCell ref="A91:D91"/>
     <mergeCell ref="A131:D131"/>
+    <mergeCell ref="A244:D244"/>
     <mergeCell ref="A389:D389"/>
+    <mergeCell ref="A327:D327"/>
+    <mergeCell ref="A140:D140"/>
     <mergeCell ref="A171:D171"/>
     <mergeCell ref="A109:D109"/>
     <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A165:D165"/>
     <mergeCell ref="A324:D324"/>
-    <mergeCell ref="A336:D336"/>
-    <mergeCell ref="A407:D407"/>
+    <mergeCell ref="A342:D342"/>
+    <mergeCell ref="A371:D371"/>
     <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A416:D416"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A115:D115"/>
     <mergeCell ref="A155:D155"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="A68:D68"/>
     <mergeCell ref="A293:D293"/>
-    <mergeCell ref="A308:D308"/>
     <mergeCell ref="A391:D391"/>
+    <mergeCell ref="A102:D102"/>
     <mergeCell ref="A173:D173"/>
     <mergeCell ref="A229:D229"/>
-    <mergeCell ref="A295:D295"/>
+    <mergeCell ref="A344:D344"/>
+    <mergeCell ref="A400:D400"/>
     <mergeCell ref="A77:D77"/>
     <mergeCell ref="A83:D83"/>
-    <mergeCell ref="A352:D352"/>
     <mergeCell ref="A143:D143"/>
+    <mergeCell ref="A276:D276"/>
+    <mergeCell ref="A92:D92"/>
     <mergeCell ref="A157:D157"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="A270:D270"/>
     <mergeCell ref="A279:D279"/>
-    <mergeCell ref="A337:D337"/>
-    <mergeCell ref="A350:D350"/>
+    <mergeCell ref="A368:D368"/>
     <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A402:D402"/>
     <mergeCell ref="A36:D36"/>
-    <mergeCell ref="A207:D207"/>
+    <mergeCell ref="A300:D300"/>
+    <mergeCell ref="A383:D383"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A103:D103"/>
     <mergeCell ref="A343:D343"/>
     <mergeCell ref="A281:D281"/>
-    <mergeCell ref="A339:D339"/>
-    <mergeCell ref="A367:D367"/>
+    <mergeCell ref="A370:D370"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A78:D78"/>
     <mergeCell ref="A256:D256"/>
-    <mergeCell ref="A271:D271"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A354:D354"/>
     <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A363:D363"/>
+    <mergeCell ref="A345:D345"/>
     <mergeCell ref="A133:D133"/>
     <mergeCell ref="A246:D246"/>
     <mergeCell ref="A193:D193"/>
+    <mergeCell ref="A255:D255"/>
+    <mergeCell ref="A369:D369"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A326:D326"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A273:D273"/>
-    <mergeCell ref="A378:D378"/>
     <mergeCell ref="A89:D89"/>
     <mergeCell ref="A120:D120"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A365:D365"/>
-    <mergeCell ref="A248:D248"/>
-    <mergeCell ref="A297:D297"/>
-    <mergeCell ref="A235:D235"/>
-    <mergeCell ref="A406:D406"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="A57:D57"/>
     <mergeCell ref="A247:D247"/>
-    <mergeCell ref="A185:D185"/>
+    <mergeCell ref="A312:D312"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A290:D290"/>
     <mergeCell ref="A106:D106"/>
-    <mergeCell ref="A234:D234"/>
-    <mergeCell ref="A404:D404"/>
     <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A96:D96"/>
     <mergeCell ref="A147:D147"/>
-    <mergeCell ref="A209:D209"/>
     <mergeCell ref="A280:D280"/>
     <mergeCell ref="A156:D156"/>
-    <mergeCell ref="A170:D170"/>
+    <mergeCell ref="A432:D432"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A211:D211"/>
     <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A338:D338"/>
+    <mergeCell ref="A382:D382"/>
     <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A201:D201"/>
     <mergeCell ref="A261:D261"/>
-    <mergeCell ref="A82:D82"/>
-    <mergeCell ref="A275:D275"/>
-    <mergeCell ref="A284:D284"/>
+    <mergeCell ref="A431:D431"/>
     <mergeCell ref="A340:D340"/>
-    <mergeCell ref="A222:D222"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A197:D197"/>
-    <mergeCell ref="A110:D110"/>
+    <mergeCell ref="A325:D325"/>
     <mergeCell ref="A146:D146"/>
-    <mergeCell ref="A237:D237"/>
+    <mergeCell ref="A430:D430"/>
     <mergeCell ref="A119:D119"/>
-    <mergeCell ref="A408:D408"/>
+    <mergeCell ref="A417:D417"/>
+    <mergeCell ref="A187:D187"/>
     <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A196:D196"/>
     <mergeCell ref="A174:D174"/>
-    <mergeCell ref="A183:D183"/>
-    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A419:D419"/>
     <mergeCell ref="A118:D118"/>
     <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A189:D189"/>
     <mergeCell ref="A158:D158"/>
-    <mergeCell ref="A238:D238"/>
-    <mergeCell ref="A351:D351"/>
+    <mergeCell ref="A198:D198"/>
     <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A409:D409"/>
+    <mergeCell ref="A434:D434"/>
     <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A86:D86"/>
-    <mergeCell ref="A239:D239"/>
+    <mergeCell ref="A301:D301"/>
     <mergeCell ref="A213:D213"/>
     <mergeCell ref="A95:D95"/>
-    <mergeCell ref="A393:D393"/>
+    <mergeCell ref="A384:D384"/>
     <mergeCell ref="A160:D160"/>
+    <mergeCell ref="A175:D175"/>
+    <mergeCell ref="A254:D254"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A136" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A188" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A199" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A213" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A229" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A241" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A252" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A263" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A275" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A286" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A297" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A308" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A326" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A343" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A354" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A367" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A381" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A395" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A122" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A149" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A165" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A179" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A206" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A261" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A272" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A283" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A296" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A307" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A318" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A329" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A347" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A364" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A375" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A391" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A405" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A419" r:id="rId32"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId33"/>

--- a/카드_아키타입/07_페이스·바디오일.xlsx
+++ b/카드_아키타입/07_페이스·바디오일.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="4965700"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>24</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="9931400"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="14287500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="14287500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="14287500"/>
     <ext cx="1362075" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>35</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="14287500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="16135350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>35</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="16135350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>35</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="16135350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>35</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="16135350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>35</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="17983200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="25552400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="25552400"/>
     <ext cx="1533525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="25552400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>47</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="25552400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="27400250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="27400250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="27400250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>47</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="27400250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="40068500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="40068500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>59</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="40068500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>68</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="52755800"/>
     <ext cx="1809750" cy="1276350"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>68</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="52755800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>68</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="52755800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>68</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="52755800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>68</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="54603650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>68</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="54603650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>68</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="54603650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>68</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="54603650"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>68</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="56451500"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>68</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="56451500"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>68</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="56451500"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>68</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="56451500"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>68</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="58299350"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="61582300"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="61582300"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="61582300"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="61582300"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="63430150"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>78</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="63430150"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>78</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="63430150"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>78</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="63430150"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="65278000"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>78</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="65278000"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>78</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="65278000"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>78</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="65278000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="68986400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="68986400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="68986400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="74764900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="74764900"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="74764900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>106</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="82981800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>106</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="82981800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>106</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="82981800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>106</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="82981800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>106</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="84829650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>106</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="84829650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>106</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="84829650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>106</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="84829650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>106</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="86677500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>106</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="86677500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>106</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="86677500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>106</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="86677500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>106</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="88525350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="90589100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="90589100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="90589100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>118</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="90589100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="92436950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="92436950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="92436950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>118</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="92436950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>118</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="94284800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>118</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="94284800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>118</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="94284800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>130</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="103886000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>130</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="103886000"/>
     <ext cx="1809750" cy="1543050"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>130</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="103886000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>130</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="103886000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>130</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="105733850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>130</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="105733850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>141</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="114947700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>141</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="114947700"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>141</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="114947700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>141</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="114947700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>141</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="116795550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="121335800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="121335800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="121335800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>153</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="121335800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>153</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="123183650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>153</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="123183650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>153</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="123183650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="128536700"/>
     <ext cx="1809750" cy="1466850"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="128536700"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>173</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="136550400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>173</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="136550400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>173</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="136550400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>173</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="136550400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>185</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="144157700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>185</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="144157700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>185</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="144157700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>185</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="144157700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>200</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="157048200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>200</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="157048200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>200</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="157048200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>200</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="157048200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>210</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="162826700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>210</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="162826700"/>
     <ext cx="1809750" cy="1266825"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>210</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="162826700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>210</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="162826700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>210</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="164674550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>219</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="167995600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>219</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="167995600"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>219</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="167995600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>219</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="167995600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>219</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="169843450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="172758100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="172758100"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="172758100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>228</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="172758100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>228</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="174605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>228</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="174605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>228</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="174605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>228</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="174605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>238</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="180365400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>238</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="180365400"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>238</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="180365400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="184518300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="184518300"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="184518300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="184518300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>247</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="186366150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>256</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="190296800"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>265</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="194881500"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>281</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="201269600"/>
     <ext cx="1114425" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>296</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="212940900"/>
     <ext cx="1181100" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>305</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="216077800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>305</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="216077800"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>305</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="216077800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>305</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="216077800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>305</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="217925650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>305</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="217925650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>305</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="217925650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>305</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="217925650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>305</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="219773500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>305</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="219773500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>305</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="219773500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>317</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="229984300"/>
     <ext cx="1066800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="238810800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="238810800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="238810800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>329</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="238810800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>341</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="246418100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>341</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="246418100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>341</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="246418100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>341</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="246418100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4198,7 +3398,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/07_페이스·바디오일.xlsx
+++ b/카드_아키타입/07_페이스·바디오일.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="4965700"/>
+    <pos x="7391400" y="4965700"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="9931400"/>
+    <pos x="7391400" y="9931400"/>
     <ext cx="1009650" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="14287500"/>
+    <pos x="7391400" y="14287500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="14287500"/>
+    <pos x="9239250" y="14287500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="14287500"/>
+    <pos x="11087100" y="14287500"/>
     <ext cx="1362075" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="14287500"/>
+    <pos x="12934950" y="14287500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="16135350"/>
+    <pos x="7391400" y="16135350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="16135350"/>
+    <pos x="9239250" y="16135350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="16135350"/>
+    <pos x="11087100" y="16135350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="16135350"/>
+    <pos x="12934950" y="16135350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="17983200"/>
+    <pos x="7391400" y="17983200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="25552400"/>
+    <pos x="7391400" y="25552400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="25552400"/>
+    <pos x="9239250" y="25552400"/>
     <ext cx="1533525" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="25552400"/>
+    <pos x="11087100" y="25552400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="25552400"/>
+    <pos x="12934950" y="25552400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="27400250"/>
+    <pos x="7391400" y="27400250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="27400250"/>
+    <pos x="9239250" y="27400250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="27400250"/>
+    <pos x="11087100" y="27400250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="27400250"/>
+    <pos x="12934950" y="27400250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="40068500"/>
+    <pos x="7391400" y="40068500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="40068500"/>
+    <pos x="9239250" y="40068500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="40068500"/>
+    <pos x="11087100" y="40068500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="52755800"/>
+    <pos x="7391400" y="52755800"/>
     <ext cx="1809750" cy="1276350"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="52755800"/>
+    <pos x="9239250" y="52755800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="52755800"/>
+    <pos x="11087100" y="52755800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="52755800"/>
+    <pos x="12934950" y="52755800"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="54603650"/>
+    <pos x="7391400" y="54603650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="54603650"/>
+    <pos x="9239250" y="54603650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="54603650"/>
+    <pos x="11087100" y="54603650"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="54603650"/>
+    <pos x="12934950" y="54603650"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="56451500"/>
+    <pos x="7391400" y="56451500"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="56451500"/>
+    <pos x="9239250" y="56451500"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="56451500"/>
+    <pos x="11087100" y="56451500"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="56451500"/>
+    <pos x="12934950" y="56451500"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="58299350"/>
+    <pos x="7391400" y="58299350"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="61582300"/>
+    <pos x="7391400" y="61582300"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="61582300"/>
+    <pos x="9239250" y="61582300"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="61582300"/>
+    <pos x="11087100" y="61582300"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="61582300"/>
+    <pos x="12934950" y="61582300"/>
     <ext cx="1428750" cy="1295400"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="63430150"/>
+    <pos x="7391400" y="63430150"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="63430150"/>
+    <pos x="9239250" y="63430150"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="63430150"/>
+    <pos x="11087100" y="63430150"/>
     <ext cx="1285875" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="63430150"/>
+    <pos x="12934950" y="63430150"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="65278000"/>
+    <pos x="7391400" y="65278000"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="65278000"/>
+    <pos x="9239250" y="65278000"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="65278000"/>
+    <pos x="11087100" y="65278000"/>
     <ext cx="1428750" cy="1428750"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="65278000"/>
+    <pos x="12934950" y="65278000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="68986400"/>
+    <pos x="7391400" y="68986400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="68986400"/>
+    <pos x="9239250" y="68986400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="68986400"/>
+    <pos x="11087100" y="68986400"/>
     <ext cx="1724025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="74764900"/>
+    <pos x="7391400" y="74764900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="74764900"/>
+    <pos x="9239250" y="74764900"/>
     <ext cx="1809750" cy="1609725"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="74764900"/>
+    <pos x="11087100" y="74764900"/>
     <ext cx="1714500" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="82981800"/>
+    <pos x="7391400" y="82981800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="82981800"/>
+    <pos x="9239250" y="82981800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="82981800"/>
+    <pos x="11087100" y="82981800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="82981800"/>
+    <pos x="12934950" y="82981800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="84829650"/>
+    <pos x="7391400" y="84829650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="84829650"/>
+    <pos x="9239250" y="84829650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="84829650"/>
+    <pos x="11087100" y="84829650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="84829650"/>
+    <pos x="12934950" y="84829650"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="86677500"/>
+    <pos x="7391400" y="86677500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="86677500"/>
+    <pos x="9239250" y="86677500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="86677500"/>
+    <pos x="11087100" y="86677500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="86677500"/>
+    <pos x="12934950" y="86677500"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="88525350"/>
+    <pos x="7391400" y="88525350"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="90589100"/>
+    <pos x="7391400" y="90589100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="90589100"/>
+    <pos x="9239250" y="90589100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="90589100"/>
+    <pos x="11087100" y="90589100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="90589100"/>
+    <pos x="12934950" y="90589100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="92436950"/>
+    <pos x="7391400" y="92436950"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="92436950"/>
+    <pos x="9239250" y="92436950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="92436950"/>
+    <pos x="11087100" y="92436950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="92436950"/>
+    <pos x="12934950" y="92436950"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="94284800"/>
+    <pos x="7391400" y="94284800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="94284800"/>
+    <pos x="9239250" y="94284800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="94284800"/>
+    <pos x="11087100" y="94284800"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="103886000"/>
+    <pos x="7391400" y="103886000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="103886000"/>
+    <pos x="9239250" y="103886000"/>
     <ext cx="1809750" cy="1543050"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="103886000"/>
+    <pos x="11087100" y="103886000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="103886000"/>
+    <pos x="12934950" y="103886000"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="105733850"/>
+    <pos x="7391400" y="105733850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="105733850"/>
+    <pos x="9239250" y="105733850"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="114947700"/>
+    <pos x="7391400" y="114947700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="114947700"/>
+    <pos x="9239250" y="114947700"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="114947700"/>
+    <pos x="11087100" y="114947700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="114947700"/>
+    <pos x="12934950" y="114947700"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="116795550"/>
+    <pos x="7391400" y="116795550"/>
     <ext cx="1238250" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="121335800"/>
+    <pos x="7391400" y="121335800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="121335800"/>
+    <pos x="9239250" y="121335800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="121335800"/>
+    <pos x="11087100" y="121335800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="121335800"/>
+    <pos x="12934950" y="121335800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="123183650"/>
+    <pos x="7391400" y="123183650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="123183650"/>
+    <pos x="9239250" y="123183650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="123183650"/>
+    <pos x="11087100" y="123183650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="128536700"/>
+    <pos x="7391400" y="128536700"/>
     <ext cx="1809750" cy="1466850"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="128536700"/>
+    <pos x="9239250" y="128536700"/>
     <ext cx="1809750" cy="1409700"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="136550400"/>
+    <pos x="7391400" y="136550400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="136550400"/>
+    <pos x="9239250" y="136550400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="136550400"/>
+    <pos x="11087100" y="136550400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="136550400"/>
+    <pos x="12934950" y="136550400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="144157700"/>
+    <pos x="7391400" y="144157700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="144157700"/>
+    <pos x="9239250" y="144157700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="144157700"/>
+    <pos x="11087100" y="144157700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="144157700"/>
+    <pos x="12934950" y="144157700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="157048200"/>
+    <pos x="7391400" y="157048200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="157048200"/>
+    <pos x="9239250" y="157048200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="157048200"/>
+    <pos x="11087100" y="157048200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="157048200"/>
+    <pos x="12934950" y="157048200"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="162826700"/>
+    <pos x="7391400" y="162826700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="162826700"/>
+    <pos x="9239250" y="162826700"/>
     <ext cx="1809750" cy="1266825"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="162826700"/>
+    <pos x="11087100" y="162826700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="162826700"/>
+    <pos x="12934950" y="162826700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="164674550"/>
+    <pos x="7391400" y="164674550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="167995600"/>
+    <pos x="7391400" y="167995600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="167995600"/>
+    <pos x="9239250" y="167995600"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="167995600"/>
+    <pos x="11087100" y="167995600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="167995600"/>
+    <pos x="12934950" y="167995600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="169843450"/>
+    <pos x="7391400" y="169843450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="172758100"/>
+    <pos x="7391400" y="172758100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="172758100"/>
+    <pos x="9239250" y="172758100"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="172758100"/>
+    <pos x="11087100" y="172758100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="172758100"/>
+    <pos x="12934950" y="172758100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="174605950"/>
+    <pos x="7391400" y="174605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="174605950"/>
+    <pos x="9239250" y="174605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="174605950"/>
+    <pos x="11087100" y="174605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="174605950"/>
+    <pos x="12934950" y="174605950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="180365400"/>
+    <pos x="7391400" y="180365400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="180365400"/>
+    <pos x="9239250" y="180365400"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="180365400"/>
+    <pos x="11087100" y="180365400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="184518300"/>
+    <pos x="7391400" y="184518300"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="184518300"/>
+    <pos x="9239250" y="184518300"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="184518300"/>
+    <pos x="11087100" y="184518300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="184518300"/>
+    <pos x="12934950" y="184518300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="186366150"/>
+    <pos x="7391400" y="186366150"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="190296800"/>
+    <pos x="7391400" y="190296800"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="194881500"/>
+    <pos x="7391400" y="194881500"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="201269600"/>
+    <pos x="7391400" y="201269600"/>
     <ext cx="1114425" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="212940900"/>
+    <pos x="7391400" y="212940900"/>
     <ext cx="1181100" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="216077800"/>
+    <pos x="7391400" y="216077800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="216077800"/>
+    <pos x="9239250" y="216077800"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="216077800"/>
+    <pos x="11087100" y="216077800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="216077800"/>
+    <pos x="12934950" y="216077800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="217925650"/>
+    <pos x="7391400" y="217925650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="217925650"/>
+    <pos x="9239250" y="217925650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="217925650"/>
+    <pos x="11087100" y="217925650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="217925650"/>
+    <pos x="12934950" y="217925650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="219773500"/>
+    <pos x="7391400" y="219773500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="219773500"/>
+    <pos x="9239250" y="219773500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="219773500"/>
+    <pos x="11087100" y="219773500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="229984300"/>
+    <pos x="7391400" y="229984300"/>
     <ext cx="1066800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="238810800"/>
+    <pos x="7391400" y="238810800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="238810800"/>
+    <pos x="9239250" y="238810800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="238810800"/>
+    <pos x="11087100" y="238810800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="238810800"/>
+    <pos x="12934950" y="238810800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="246418100"/>
+    <pos x="7391400" y="246418100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="246418100"/>
+    <pos x="9239250" y="246418100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="246418100"/>
+    <pos x="11087100" y="246418100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="246418100"/>
+    <pos x="12934950" y="246418100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3698,7 +3698,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/07_페이스·바디오일.xlsx
+++ b/카드_아키타입/07_페이스·바디오일.xlsx
@@ -2436,7 +2436,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="168452800"/>
+    <pos x="7848600" y="168249600"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2456,7 +2456,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="168452800"/>
+    <pos x="9696450" y="168249600"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2476,7 +2476,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="168452800"/>
+    <pos x="11544300" y="168249600"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2496,7 +2496,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="168452800"/>
+    <pos x="13392150" y="168249600"/>
     <ext cx="1428750" cy="1238250"/>
     <pic>
       <nvPicPr>
@@ -2516,7 +2516,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="174002700"/>
+    <pos x="7848600" y="173799500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2536,7 +2536,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="174002700"/>
+    <pos x="9696450" y="173799500"/>
     <ext cx="1809750" cy="1266825"/>
     <pic>
       <nvPicPr>
@@ -2556,7 +2556,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="174002700"/>
+    <pos x="11544300" y="173799500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2576,7 +2576,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="174002700"/>
+    <pos x="13392150" y="173799500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2596,7 +2596,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="175850550"/>
+    <pos x="7848600" y="175647350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2616,7 +2616,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="179552600"/>
+    <pos x="7848600" y="179349400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2636,7 +2636,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="179552600"/>
+    <pos x="9696450" y="179349400"/>
     <ext cx="1628775" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2656,7 +2656,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="179552600"/>
+    <pos x="11544300" y="179349400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2676,7 +2676,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="179552600"/>
+    <pos x="13392150" y="179349400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2696,7 +2696,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="181400450"/>
+    <pos x="7848600" y="181197250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2716,7 +2716,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="184492900"/>
+    <pos x="7848600" y="184289700"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2736,7 +2736,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="184492900"/>
+    <pos x="9696450" y="184289700"/>
     <ext cx="1809750" cy="1447800"/>
     <pic>
       <nvPicPr>
@@ -2756,7 +2756,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="184492900"/>
+    <pos x="11544300" y="184289700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2776,7 +2776,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="184492900"/>
+    <pos x="13392150" y="184289700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2796,7 +2796,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="186340750"/>
+    <pos x="7848600" y="186137550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2816,7 +2816,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="186340750"/>
+    <pos x="9696450" y="186137550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2836,7 +2836,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="186340750"/>
+    <pos x="11544300" y="186137550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2856,7 +2856,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="186340750"/>
+    <pos x="13392150" y="186137550"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2876,7 +2876,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="192481200"/>
+    <pos x="7848600" y="192278000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2896,7 +2896,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="192481200"/>
+    <pos x="9696450" y="192278000"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -2916,7 +2916,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="192481200"/>
+    <pos x="11544300" y="192278000"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2936,7 +2936,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="197015100"/>
+    <pos x="7848600" y="196811900"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2956,7 +2956,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="197015100"/>
+    <pos x="9696450" y="196811900"/>
     <ext cx="1809750" cy="1419225"/>
     <pic>
       <nvPicPr>
@@ -2976,7 +2976,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="197015100"/>
+    <pos x="11544300" y="196811900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2996,7 +2996,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="197015100"/>
+    <pos x="13392150" y="196811900"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3016,7 +3016,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="198862950"/>
+    <pos x="7848600" y="198659750"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3036,7 +3036,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="203174600"/>
+    <pos x="7848600" y="202971400"/>
     <ext cx="1190625" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3056,7 +3056,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="207962500"/>
+    <pos x="7848600" y="207759300"/>
     <ext cx="1123950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3076,7 +3076,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="215163400"/>
+    <pos x="7848600" y="214960200"/>
     <ext cx="1114425" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3096,7 +3096,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="226631500"/>
+    <pos x="7848600" y="226428300"/>
     <ext cx="1181100" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3116,7 +3116,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="229565200"/>
+    <pos x="7848600" y="229362000"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3136,7 +3136,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="229565200"/>
+    <pos x="9696450" y="229362000"/>
     <ext cx="1809750" cy="1504950"/>
     <pic>
       <nvPicPr>
@@ -3156,7 +3156,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="229565200"/>
+    <pos x="11544300" y="229362000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3176,7 +3176,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="229565200"/>
+    <pos x="13392150" y="229362000"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3196,7 +3196,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="231413050"/>
+    <pos x="7848600" y="231209850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3216,7 +3216,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="231413050"/>
+    <pos x="9696450" y="231209850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3236,7 +3236,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="231413050"/>
+    <pos x="11544300" y="231209850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3256,7 +3256,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="231413050"/>
+    <pos x="13392150" y="231209850"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3276,7 +3276,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="233260900"/>
+    <pos x="7848600" y="233057700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3296,7 +3296,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="233260900"/>
+    <pos x="9696450" y="233057700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3316,7 +3316,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="233260900"/>
+    <pos x="11544300" y="233057700"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3336,7 +3336,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="244055900"/>
+    <pos x="7848600" y="243852700"/>
     <ext cx="1066800" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3356,7 +3356,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="252882400"/>
+    <pos x="7848600" y="252679200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3376,7 +3376,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="252882400"/>
+    <pos x="9696450" y="252679200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3396,7 +3396,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="252882400"/>
+    <pos x="11544300" y="252679200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3416,7 +3416,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="252882400"/>
+    <pos x="13392150" y="252679200"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3436,7 +3436,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="7848600" y="261073900"/>
+    <pos x="7848600" y="260870700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3456,7 +3456,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9696450" y="261073900"/>
+    <pos x="9696450" y="260870700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3476,7 +3476,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11544300" y="261073900"/>
+    <pos x="11544300" y="260870700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3496,7 +3496,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="13392150" y="261073900"/>
+    <pos x="13392150" y="260870700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>제라늄EO, 시나몬EO, / 페파민트EO 등 벌레퇴치효과있는 것</t>
+          <t>제라늄EO, 시나몬EO · 페파민트EO 등 벌레퇴치효과있는 것</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="F22" s="19" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="E24" s="19" t="inlineStr">
         <is>
-          <t>국화과 허브, 진정효과 탁월, 민감 신생아 영유아 사용 / 넣지 않고 사용하면 오트밀오일 자체향.</t>
+          <t>국화과 허브, 진정효과 탁월, 민감 신생아 영유아 사용 · 넣지 않고 사용하면 오트밀오일 자체향.</t>
         </is>
       </c>
       <c r="F24" s="19" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="F25" s="19" t="inlineStr">
         <is>
-          <t>레몬에센셜오일 등 / 원하는 에센셜오일</t>
+          <t>레몬에센셜오일 등 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>바다의 이슬이란 뜻에서 유래, / 혈액순환에 도움</t>
+          <t>바다의 이슬이란 뜻에서 유래 · 혈액순환에 도움</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
@@ -4696,10 +4696,10 @@
       </c>
       <c r="E46" s="19" t="inlineStr">
         <is>
-          <t>비정제오일이라 특이취. / 가볍지만 고보습효과, 고급 필수지방산인 오메가 3,6,9풍부, 비타민A,E함유</t>
-        </is>
-      </c>
-      <c r="F46" s="19" t="n"/>
+          <t>비정제오일이라 특이취. · 가볍지만 고보습효과, 고급 필수지방산인 오메가 3,6,9풍부, 비타민A,E함유</t>
+        </is>
+      </c>
+      <c r="F46" s="19" t="inlineStr"/>
     </row>
     <row r="47" ht="80" customHeight="1">
       <c r="A47" s="19" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="F47" s="19" t="inlineStr">
         <is>
-          <t>골든호호바, / 아르간오일 등</t>
+          <t>골든호호바 · 아르간오일 등</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="E49" s="19" t="inlineStr">
         <is>
-          <t>유향나무에서 수지를 추출, / 증기추출,트러블피부, / 나이든 피부</t>
+          <t>유향나무에서 수지를 추출 · 증기추출,트러블피부 · 나이든 피부</t>
         </is>
       </c>
       <c r="F49" s="19" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="E60" s="10" t="inlineStr">
         <is>
-          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비, / 민감 성피부</t>
+          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비 · 민감 성피부</t>
         </is>
       </c>
       <c r="F60" s="10" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E61" s="10" t="inlineStr">
         <is>
-          <t>국화과 허브, 진정효과 탁월, 민감 신생아 영유아 사용 / 넣지 않고 사용하면 오트밀오일 자체향.</t>
+          <t>국화과 허브, 진정효과 탁월, 민감 신생아 영유아 사용 · 넣지 않고 사용하면 오트밀오일 자체향.</t>
         </is>
       </c>
       <c r="F61" s="10" t="inlineStr">
         <is>
-          <t>라벤더에센셜오일 / 네롤리에센셜오일</t>
+          <t>라벤더에센셜오일 · 네롤리에센셜오일</t>
         </is>
       </c>
     </row>
@@ -5218,10 +5218,10 @@
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>오미자 과육에서 순수 분리된 원형 그대로의 오미자씨를 이용하였습니다. 과육에서 분리된 씨앗의 변질을 막기 위해 냉동 후 냉풍 건조합니다. 유효성분의 변화를 최소화하기 위하며 저온 압착추출 방법으로 추출하였고 / 최소한의 정제과정만을 거친 / extra virgin type oil입니다. / 생오미자 1000kg(1톤)에서 얻을 수 있는 오미자오일은 1~2%정도입니다.</t>
-        </is>
-      </c>
-      <c r="F72" s="19" t="n"/>
+          <t>오미자 과육에서 순수 분리된 원형 그대로의 오미자씨를 이용하였습니다. 과육에서 분리된 씨앗의 변질을 막기 위해 냉동 후 냉풍 건조합니다. 유효성분의 변화를 최소화하기 위하며 저온 압착추출 방법으로 추출하였고 · 최소한의 정제과정만을 거친 · extra virgin type oil입니다. · 생오미자 1000kg(1톤)에서 얻을 수 있는 오미자오일은 1~2%정도입니다.</t>
+        </is>
+      </c>
+      <c r="F72" s="19" t="inlineStr"/>
     </row>
     <row r="73" ht="14" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="F94" s="19" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -5836,12 +5836,12 @@
       </c>
       <c r="E104" s="10" t="inlineStr">
         <is>
-          <t>제주산 발효 마유, / 마유 중 비중이 가벼운 부분 , / 팔마톨레익산 등 불포화지방산 풍부, / 특이취 거의 없음</t>
+          <t>제주산 발효 마유 · 마유 중 비중이 가벼운 부분 · 팔마톨레익산 등 불포화지방산 풍부 · 특이취 거의 없음</t>
         </is>
       </c>
       <c r="F104" s="10" t="inlineStr">
         <is>
-          <t>호호바오일, 동백오일 / 아르간오일 등</t>
+          <t>호호바오일, 동백오일 · 아르간오일 등</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E105" s="10" t="inlineStr">
         <is>
-          <t>오렌지꽃오일, 수증기 증류법으로 / 추출, 고농축, 민감, 노화피부에 사용</t>
+          <t>오렌지꽃오일, 수증기 증류법으로 · 추출, 고농축, 민감, 노화피부에 사용</t>
         </is>
       </c>
       <c r="F105" s="10" t="inlineStr">
         <is>
-          <t>로즈, 자스민 / 에센셜오일등</t>
+          <t>로즈, 자스민 · 에센셜오일등</t>
         </is>
       </c>
     </row>
@@ -6007,7 +6007,7 @@
       </c>
       <c r="E114" s="19" t="inlineStr">
         <is>
-          <t>주성분 라우릭산(Lauric Acid), / 중사슬 지방산인 분자구조가 단순해 / 끈적임이 없습니다.</t>
+          <t>주성분 라우릭산(Lauric Acid) · 중사슬 지방산인 분자구조가 단순해 · 끈적임이 없습니다.</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
@@ -6185,7 +6185,7 @@
           <t>자초(식물)의 뿌리를 오일에 우려냄,민감, 트러블 피부 관리에 효과, 지용성 천연 붉은 색소 함유.</t>
         </is>
       </c>
-      <c r="F124" s="10" t="n"/>
+      <c r="F124" s="10" t="inlineStr"/>
     </row>
     <row r="125" ht="32" customHeight="1">
       <c r="A125" s="10" t="inlineStr">
@@ -6245,7 +6245,7 @@
           <t>석유계 바세린 대체, 유기농 인증, 해바라기오일 주성분. 젤타입.</t>
         </is>
       </c>
-      <c r="F126" s="10" t="n"/>
+      <c r="F126" s="10" t="inlineStr"/>
     </row>
     <row r="127" ht="64" customHeight="1">
       <c r="A127" s="10" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="F127" s="10" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="E128" s="10" t="inlineStr">
         <is>
-          <t>넣지 않으면 코코넛향이 은은함 / 강한 향을 원하면 원하는 식향을 추가</t>
+          <t>넣지 않으면 코코넛향이 은은함 · 강한 향을 원하면 원하는 식향을 추가</t>
         </is>
       </c>
       <c r="F128" s="10" t="inlineStr">
         <is>
-          <t>원하는 / 에센셜오일</t>
+          <t>원하는 · 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="E137" s="19" t="inlineStr">
         <is>
-          <t>피지 성분 비슷. / 콩과식물, 액상왁스구조</t>
+          <t>피지 성분 비슷. · 콩과식물, 액상왁스구조</t>
         </is>
       </c>
       <c r="F137" s="19" t="inlineStr">
@@ -6509,7 +6509,7 @@
           <t>해바라기오일로 만든 젤타입 . 석유계 바세린 대체</t>
         </is>
       </c>
-      <c r="F139" s="19" t="n"/>
+      <c r="F139" s="19" t="inlineStr"/>
     </row>
     <row r="140" ht="48" customHeight="1">
       <c r="A140" s="19" t="inlineStr">
@@ -6534,7 +6534,7 @@
       </c>
       <c r="E140" s="19" t="inlineStr">
         <is>
-          <t>감귤류 버가못 껍질오일. / 감광성 무(버갑텐프리)</t>
+          <t>감귤류 버가못 껍질오일. · 감광성 무(버갑텐프리)</t>
         </is>
       </c>
       <c r="F140" s="19" t="inlineStr">
@@ -6732,7 +6732,7 @@
           <t>석유계 바세린 대체, 유기농 인증, 해바라기오일 주성분. 젤타입.</t>
         </is>
       </c>
-      <c r="F150" s="10" t="n"/>
+      <c r="F150" s="10" t="inlineStr"/>
     </row>
     <row r="151" ht="16" customHeight="1">
       <c r="A151" s="10" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="E153" s="10" t="inlineStr">
         <is>
-          <t>허브의 고농축오일, / 시원, 커피와 시너지효과</t>
+          <t>허브의 고농축오일 · 시원, 커피와 시너지효과</t>
         </is>
       </c>
       <c r="F153" s="10" t="inlineStr">
         <is>
-          <t>티트리(항균), / 스피아민트 등</t>
+          <t>티트리(항균) · 스피아민트 등</t>
         </is>
       </c>
     </row>
@@ -6963,7 +6963,7 @@
       </c>
       <c r="E161" s="19" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, / 빠른흡수</t>
+          <t>피지성분과 비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F161" s="19" t="inlineStr">
@@ -7000,7 +7000,7 @@
       </c>
       <c r="F162" s="19" t="inlineStr">
         <is>
-          <t>버가못에센셜오일, / 레몬쥬스블렌딩오일</t>
+          <t>버가못에센셜오일 · 레몬쥬스블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="F163" s="19" t="inlineStr">
         <is>
-          <t>브라이트닝. / 로즈파워 블렌딩오일</t>
+          <t>브라이트닝. · 로즈파워 블렌딩오일</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="F164" s="19" t="inlineStr">
         <is>
-          <t>브라이트닝 / 블랜딩오일 등</t>
+          <t>브라이트닝 · 블랜딩오일 등</t>
         </is>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
       </c>
       <c r="E174" s="10" t="inlineStr">
         <is>
-          <t>모유에 들어있는 라우릭산이 / 자연식품 중에서는 가장 많이 들어있음. 달콤한 향</t>
+          <t>모유에 들어있는 라우릭산이 · 자연식품 중에서는 가장 많이 들어있음. 달콤한 향</t>
         </is>
       </c>
       <c r="F174" s="10" t="inlineStr">
@@ -7305,10 +7305,10 @@
       </c>
       <c r="E176" s="10" t="inlineStr">
         <is>
-          <t>석유계 바세린 대체, / 해바라기오일 주성분. 젤타입.</t>
-        </is>
-      </c>
-      <c r="F176" s="10" t="n"/>
+          <t>석유계 바세린 대체 · 해바라기오일 주성분. 젤타입.</t>
+        </is>
+      </c>
+      <c r="F176" s="10" t="inlineStr"/>
     </row>
     <row r="177" ht="14" customHeight="1">
       <c r="A177" s="14" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="E196" s="10" t="inlineStr">
         <is>
-          <t>피지의 약 12%를 구성하는 성분, / 스쿠알렌을 수소첨가하여 안정화한 성분</t>
+          <t>피지의 약 12%를 구성하는 성분 · 스쿠알렌을 수소첨가하여 안정화한 성분</t>
         </is>
       </c>
       <c r="F196" s="10" t="inlineStr">
@@ -7690,12 +7690,12 @@
       </c>
       <c r="E197" s="10" t="inlineStr">
         <is>
-          <t>코코넛, 팜 등에서 유래, / 카프릴릭산(C8)와 카프릭산(C10)을 / 글리세린과 합성시켜 만든 원료, / 가볍고 빠른 흡수력</t>
+          <t>코코넛, 팜 등에서 유래 · 카프릴릭산(C8)와 카프릭산(C10)을 · 글리세린과 합성시켜 만든 원료 · 가볍고 빠른 흡수력</t>
         </is>
       </c>
       <c r="F197" s="10" t="inlineStr">
         <is>
-          <t>유기농 세티올 / 에스터오일</t>
+          <t>유기농 세티올 · 에스터오일</t>
         </is>
       </c>
     </row>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="E198" s="10" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, / 빠른흡수</t>
+          <t>피지성분과 비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F198" s="10" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="E200" s="10" t="inlineStr">
         <is>
-          <t>감귤류, 피부진정, / 광독성 없음</t>
+          <t>감귤류, 피부진정 · 광독성 없음</t>
         </is>
       </c>
       <c r="F200" s="10" t="inlineStr">
@@ -7933,7 +7933,7 @@
       </c>
       <c r="E209" s="19" t="inlineStr">
         <is>
-          <t>피지의 약 12%를 구성하는 성분, / 스쿠알렌을 수소첨가하여 안정화한 성분</t>
+          <t>피지의 약 12%를 구성하는 성분 · 스쿠알렌을 수소첨가하여 안정화한 성분</t>
         </is>
       </c>
       <c r="F209" s="19" t="inlineStr">
@@ -7965,12 +7965,12 @@
       </c>
       <c r="E210" s="19" t="inlineStr">
         <is>
-          <t>코코넛, 팜 등에서 유래, / 카프릴릭산(C8)와 카프릭산(C10)을 / 글리세린과 합성시켜 만든 원료, / 가볍고 빠른 흡수력</t>
+          <t>코코넛, 팜 등에서 유래 · 카프릴릭산(C8)와 카프릭산(C10)을 · 글리세린과 합성시켜 만든 원료 · 가볍고 빠른 흡수력</t>
         </is>
       </c>
       <c r="F210" s="19" t="inlineStr">
         <is>
-          <t>유기농 세티올 / 에스터오일</t>
+          <t>유기농 세티올 · 에스터오일</t>
         </is>
       </c>
     </row>
@@ -8029,7 +8029,7 @@
       </c>
       <c r="E212" s="19" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, 빠른 흡수 / ※ 호호바오일(골든) 사용 시 완성품이 노란빛을 띨 수 있습니다.</t>
+          <t>피지성분과 비슷, 빠른 흡수 · ※ 호호바오일(골든) 사용 시 완성품이 노란빛을 띨 수 있습니다.</t>
         </is>
       </c>
       <c r="F212" s="19" t="inlineStr">
@@ -8098,11 +8098,11 @@
       </c>
       <c r="F214" s="19" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="48" customHeight="1">
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="32" customHeight="1">
       <c r="A215" s="19" t="inlineStr">
         <is>
           <t>로즈파워 블렌딩오일</t>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="E215" s="19" t="inlineStr">
         <is>
-          <t>로즈앱솔루트, 로즈제라늄, / 로즈우드, 프랑킨센스 블렌딩오일</t>
+          <t>로즈앱솔루트, 로즈제라늄 · 로즈우드, 프랑킨센스 블렌딩오일</t>
         </is>
       </c>
       <c r="F215" s="19" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="F246" s="10" t="inlineStr">
         <is>
-          <t>아보카도, / 골든 호호바등</t>
+          <t>아보카도 · 골든 호호바등</t>
         </is>
       </c>
     </row>
@@ -8718,7 +8718,7 @@
       </c>
       <c r="E247" s="10" t="inlineStr">
         <is>
-          <t>영유아임산부도 사용가능, / 모든피부연령, / 아로마테라피의 기본</t>
+          <t>영유아임산부도 사용가능 · 모든피부연령 · 아로마테라피의 기본</t>
         </is>
       </c>
       <c r="F247" s="10" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="E277" s="19" t="inlineStr">
         <is>
-          <t>보습성분인 올레인산, / 리놀렌산이 다량함유.</t>
+          <t>보습성분인 올레인산 · 리놀렌산이 다량함유.</t>
         </is>
       </c>
       <c r="F277" s="19" t="inlineStr">
         <is>
-          <t>동백, 마카다미아넛오일 등 / 식물성오일이면 OK</t>
+          <t>동백, 마카다미아넛오일 등 · 식물성오일이면 OK</t>
         </is>
       </c>
     </row>
@@ -9281,12 +9281,12 @@
       </c>
       <c r="E278" s="19" t="inlineStr">
         <is>
-          <t>허브의 여왕, 몸과 마음을 진정, / 영유아 민감트러블피부에 사용</t>
+          <t>허브의 여왕, 몸과 마음을 진정 · 영유아 민감트러블피부에 사용</t>
         </is>
       </c>
       <c r="F278" s="19" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -9457,7 +9457,7 @@
       </c>
       <c r="E288" s="10" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F288" s="10" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="E289" s="10" t="inlineStr">
         <is>
-          <t>장미향 나는 제라늄, 균형의 오일 / 피지균형 등 모든 피부</t>
+          <t>장미향 나는 제라늄, 균형의 오일 · 피지균형 등 모든 피부</t>
         </is>
       </c>
       <c r="F289" s="10" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="E290" s="10" t="inlineStr">
         <is>
-          <t>국화과 허브, 진정효과 탁월, 민감 신생아 영유아 사용 / 넣지 않고 사용하면 오트밀오일 자체향.</t>
+          <t>국화과 허브, 진정효과 탁월, 민감 신생아 영유아 사용 · 넣지 않고 사용하면 오트밀오일 자체향.</t>
         </is>
       </c>
       <c r="F290" s="10" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="E296" s="19" t="inlineStr">
         <is>
-          <t>감초의 수/지용성성분추출물.</t>
+          <t>감초의 수 · 지용성성분추출물.</t>
         </is>
       </c>
       <c r="F296" s="19" t="inlineStr">
@@ -9639,7 +9639,7 @@
           <t>황금(속썩은풀 뿌리) 추출, 항염·진정·항산화</t>
         </is>
       </c>
-      <c r="F297" s="19" t="n"/>
+      <c r="F297" s="19" t="inlineStr"/>
     </row>
     <row r="298" ht="32" customHeight="1">
       <c r="A298" s="19" t="inlineStr">
@@ -9663,7 +9663,7 @@
           <t>유근피(느릅나무 껍질) 추출, 점액질 진정·보습</t>
         </is>
       </c>
-      <c r="F298" s="19" t="n"/>
+      <c r="F298" s="19" t="inlineStr"/>
     </row>
     <row r="299" ht="32" customHeight="1">
       <c r="A299" s="19" t="inlineStr">
@@ -9687,7 +9687,7 @@
           <t>금은화(인동꽃) 추출, 항염·진정</t>
         </is>
       </c>
-      <c r="F299" s="19" t="n"/>
+      <c r="F299" s="19" t="inlineStr"/>
     </row>
     <row r="300" ht="16" customHeight="1">
       <c r="A300" s="19" t="inlineStr">
@@ -9711,7 +9711,7 @@
           <t>감국(국화) 추출물, 진정·항염</t>
         </is>
       </c>
-      <c r="F300" s="19" t="n"/>
+      <c r="F300" s="19" t="inlineStr"/>
     </row>
     <row r="301" ht="32" customHeight="1">
       <c r="A301" s="19" t="inlineStr">
@@ -9735,7 +9735,7 @@
           <t>진피(귤껍질) 추출, 항산화·수렴</t>
         </is>
       </c>
-      <c r="F301" s="19" t="n"/>
+      <c r="F301" s="19" t="inlineStr"/>
     </row>
     <row r="302" ht="32" customHeight="1">
       <c r="A302" s="19" t="inlineStr">
@@ -9759,7 +9759,7 @@
           <t>자초(지치 뿌리) 추출, 항염·진정(자색소)</t>
         </is>
       </c>
-      <c r="F302" s="19" t="n"/>
+      <c r="F302" s="19" t="inlineStr"/>
     </row>
     <row r="303" ht="32" customHeight="1">
       <c r="A303" s="19" t="inlineStr">
@@ -9783,7 +9783,7 @@
           <t>한방 약재, 혈행·보습, 피부 진정</t>
         </is>
       </c>
-      <c r="F303" s="19" t="n"/>
+      <c r="F303" s="19" t="inlineStr"/>
     </row>
     <row r="304" ht="80" customHeight="1">
       <c r="A304" s="19" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="E304" s="19" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F304" s="19" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="E312" s="10" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F312" s="10" t="inlineStr">
@@ -9958,7 +9958,7 @@
       </c>
       <c r="E313" s="10" t="inlineStr">
         <is>
-          <t>월견초 종자유, / 감마리놀린산 다량함유,</t>
+          <t>월견초 종자유 · 감마리놀린산 다량함유</t>
         </is>
       </c>
       <c r="F313" s="10" t="inlineStr">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="E314" s="10" t="inlineStr">
         <is>
-          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비, / 민감 성피부</t>
+          <t>올레인산 다량함유, 피부장벽강화, 항산화효과 베이비 · 민감 성피부</t>
         </is>
       </c>
       <c r="F314" s="10" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="F315" s="10" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="E316" s="10" t="inlineStr">
         <is>
-          <t>5가지 멀티 세라마이드, / 피부 장벽 강화</t>
+          <t>5가지 멀티 세라마이드 · 피부 장벽 강화</t>
         </is>
       </c>
       <c r="F316" s="10" t="inlineStr">
         <is>
-          <t>스쿠알란, / 보르피린</t>
+          <t>스쿠알란 · 보르피린</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="F317" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="E318" s="10" t="inlineStr">
         <is>
-          <t>귤껍질오일, / 임신기간 영아에게 안전하게 사용, / 모든 피부사용</t>
+          <t>귤껍질오일 · 임신기간 영아에게 안전하게 사용 · 모든 피부사용</t>
         </is>
       </c>
       <c r="F318" s="10" t="inlineStr">
@@ -10262,7 +10262,7 @@
           <t>자초(지치 뿌리) 추출, 항염·진정(자색소)</t>
         </is>
       </c>
-      <c r="F327" s="19" t="n"/>
+      <c r="F327" s="19" t="inlineStr"/>
     </row>
     <row r="328" ht="80" customHeight="1">
       <c r="A328" s="19" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="E328" s="19" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F328" s="19" t="inlineStr">
@@ -10409,7 +10409,7 @@
       </c>
       <c r="E336" s="10" t="inlineStr">
         <is>
-          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) / 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
+          <t>롤볼 기준 높이 5.5cm까지 골든 호호바오일을 넣어주시면 8.6g(=10ml) · 골든 호호바오일,사람피지성분과 비슷, 끈적임없이 흡수, 액상왁스, 비타민E함유.</t>
         </is>
       </c>
       <c r="F336" s="10" t="inlineStr">
@@ -10441,10 +10441,10 @@
       </c>
       <c r="E337" s="10" t="inlineStr">
         <is>
-          <t>바하, 지용성, 아스피린성분, 두꺼운 각질을 천천히 제거 화장품 성분이 잘 흡수되도록 도와줌, / 식약처 기준은 0.5%</t>
-        </is>
-      </c>
-      <c r="F337" s="10" t="n"/>
+          <t>바하, 지용성, 아스피린성분, 두꺼운 각질을 천천히 제거 화장품 성분이 잘 흡수되도록 도와줌 · 식약처 기준은 0.5%</t>
+        </is>
+      </c>
+      <c r="F337" s="10" t="inlineStr"/>
     </row>
     <row r="338" ht="64" customHeight="1">
       <c r="A338" s="10" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="F338" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       </c>
       <c r="F349" s="19" t="inlineStr">
         <is>
-          <t>골든호호바, / 아르간오일 등</t>
+          <t>골든호호바 · 아르간오일 등</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="E350" s="19" t="inlineStr">
         <is>
-          <t>들장미열매 압착 혹은 용매추출, / 주름, 노화피부관리에사용함</t>
+          <t>들장미열매 압착 혹은 용매추출 · 주름, 노화피부관리에사용함</t>
         </is>
       </c>
       <c r="F350" s="19" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="F351" s="19" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -10783,7 +10783,7 @@
       </c>
       <c r="E353" s="19" t="inlineStr">
         <is>
-          <t>귤껍질오일, / 임신기간 영아에게 안전하게 사용, / 모든 피부사용</t>
+          <t>귤껍질오일 · 임신기간 영아에게 안전하게 사용 · 모든 피부사용</t>
         </is>
       </c>
       <c r="F353" s="19" t="inlineStr">
@@ -10917,7 +10917,7 @@
       </c>
       <c r="E361" s="10" t="inlineStr">
         <is>
-          <t>피지의 약 12%를 구성하는 성분, / 스쿠알렌을 수소첨가하여 안정화한 성분</t>
+          <t>피지의 약 12%를 구성하는 성분 · 스쿠알렌을 수소첨가하여 안정화한 성분</t>
         </is>
       </c>
       <c r="F361" s="10" t="inlineStr">
@@ -10949,12 +10949,12 @@
       </c>
       <c r="E362" s="10" t="inlineStr">
         <is>
-          <t>코코넛, 팜 등에서 유래, / 카프릴릭산(C8)와 카프릭산(C10)을 / 글리세린과 합성시켜 만든 원료, / 가볍고 빠른 흡수력</t>
+          <t>코코넛, 팜 등에서 유래 · 카프릴릭산(C8)와 카프릭산(C10)을 · 글리세린과 합성시켜 만든 원료 · 가볍고 빠른 흡수력</t>
         </is>
       </c>
       <c r="F362" s="10" t="inlineStr">
         <is>
-          <t>유기농 세티올 / 에스터오일</t>
+          <t>유기농 세티올 · 에스터오일</t>
         </is>
       </c>
     </row>
@@ -10981,7 +10981,7 @@
       </c>
       <c r="E363" s="10" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, / 빠른흡수</t>
+          <t>피지성분과 비슷 · 빠른흡수</t>
         </is>
       </c>
       <c r="F363" s="10" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="E365" s="10" t="inlineStr">
         <is>
-          <t>감귤류, 피부진정, / 광독성 없음</t>
+          <t>감귤류, 피부진정 · 광독성 없음</t>
         </is>
       </c>
       <c r="F365" s="10" t="inlineStr">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="E374" s="19" t="inlineStr">
         <is>
-          <t>피지의 약 12%를 구성하는 성분, / 스쿠알렌을 수소첨가하여 안정화한 성분</t>
+          <t>피지의 약 12%를 구성하는 성분 · 스쿠알렌을 수소첨가하여 안정화한 성분</t>
         </is>
       </c>
       <c r="F374" s="19" t="inlineStr">
@@ -11224,12 +11224,12 @@
       </c>
       <c r="E375" s="19" t="inlineStr">
         <is>
-          <t>코코넛, 팜 등에서 유래, / 카프릴릭산(C8)와 카프릭산(C10)을 / 글리세린과 합성시켜 만든 원료, / 가볍고 빠른 흡수력</t>
+          <t>코코넛, 팜 등에서 유래 · 카프릴릭산(C8)와 카프릭산(C10)을 · 글리세린과 합성시켜 만든 원료 · 가볍고 빠른 흡수력</t>
         </is>
       </c>
       <c r="F375" s="19" t="inlineStr">
         <is>
-          <t>유기농 세티올 / 에스터오일</t>
+          <t>유기농 세티올 · 에스터오일</t>
         </is>
       </c>
     </row>
@@ -11288,7 +11288,7 @@
       </c>
       <c r="E377" s="19" t="inlineStr">
         <is>
-          <t>피지성분과 비슷, 빠른 흡수 / ※ 호호바오일(골든) 사용 시 완성품이 노란빛을 띨 수 있습니다.</t>
+          <t>피지성분과 비슷, 빠른 흡수 · ※ 호호바오일(골든) 사용 시 완성품이 노란빛을 띨 수 있습니다.</t>
         </is>
       </c>
       <c r="F377" s="19" t="inlineStr">
@@ -11357,11 +11357,11 @@
       </c>
       <c r="F379" s="19" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
-        </is>
-      </c>
-    </row>
-    <row r="380" ht="48" customHeight="1">
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="32" customHeight="1">
       <c r="A380" s="19" t="inlineStr">
         <is>
           <t>로즈파워 블렌딩오일</t>
@@ -11384,7 +11384,7 @@
       </c>
       <c r="E380" s="19" t="inlineStr">
         <is>
-          <t>로즈앱솔루트, 로즈제라늄, / 로즈우드, 프랑킨센스 블렌딩오일</t>
+          <t>로즈앱솔루트, 로즈제라늄 · 로즈우드, 프랑킨센스 블렌딩오일</t>
         </is>
       </c>
       <c r="F380" s="19" t="inlineStr">
